--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526AB04A-76CE-4C14-832B-5D9F162F9DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D22CF3B-F820-42AF-A8A3-53BAF7121C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="282">
   <si>
     <t>TAG</t>
   </si>
@@ -880,6 +880,18 @@
   </si>
   <si>
     <t>REDUTOR VÁLVULA ROTATIVA 7 - CSC 3</t>
+  </si>
+  <si>
+    <t>ME-601244</t>
+  </si>
+  <si>
+    <t>ME-601243</t>
+  </si>
+  <si>
+    <t>ME-601252</t>
+  </si>
+  <si>
+    <t>assets/img/ME-601035.jpg</t>
   </si>
 </sst>
 </file>
@@ -1104,7 +1116,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:S81" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
-  <autoFilter ref="A1:S81" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+  <autoFilter ref="A1:S81" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="ME-601035"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R73">
     <sortCondition ref="A1:A73"/>
   </sortState>
@@ -1370,7 +1388,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="28.5">
+    <row r="2" spans="1:19" ht="28.5" hidden="1">
       <c r="A2" s="4" t="s">
         <v>138</v>
       </c>
@@ -1417,7 +1435,7 @@
         <v>5920</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="42.75">
+    <row r="3" spans="1:19" ht="42.75" hidden="1">
       <c r="A3" s="3" t="s">
         <v>80</v>
       </c>
@@ -1468,7 +1486,7 @@
         <v>5900</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="42.75">
+    <row r="4" spans="1:19" ht="42.75" hidden="1">
       <c r="A4" s="3" t="s">
         <v>85</v>
       </c>
@@ -1519,7 +1537,7 @@
         <v>5922</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="42.75">
+    <row r="5" spans="1:19" ht="42.75" hidden="1">
       <c r="A5" s="3" t="s">
         <v>86</v>
       </c>
@@ -1570,7 +1588,7 @@
         <v>5942</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="42.75">
+    <row r="6" spans="1:19" ht="42.75" hidden="1">
       <c r="A6" s="3" t="s">
         <v>87</v>
       </c>
@@ -1621,7 +1639,7 @@
         <v>5894</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="42.75">
+    <row r="7" spans="1:19" ht="42.75" hidden="1">
       <c r="A7" s="3" t="s">
         <v>88</v>
       </c>
@@ -1672,7 +1690,7 @@
         <v>5952</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="42.75">
+    <row r="8" spans="1:19" ht="42.75" hidden="1">
       <c r="A8" s="3" t="s">
         <v>89</v>
       </c>
@@ -1723,7 +1741,7 @@
         <v>5946</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="42.75">
+    <row r="9" spans="1:19" ht="42.75" hidden="1">
       <c r="A9" s="3" t="s">
         <v>90</v>
       </c>
@@ -1774,7 +1792,7 @@
         <v>5904</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="42.75">
+    <row r="10" spans="1:19" ht="42.75" hidden="1">
       <c r="A10" s="3" t="s">
         <v>91</v>
       </c>
@@ -1825,7 +1843,7 @@
         <v>5913</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="42.75">
+    <row r="11" spans="1:19" ht="42.75" hidden="1">
       <c r="A11" s="3" t="s">
         <v>92</v>
       </c>
@@ -1876,7 +1894,7 @@
         <v>5941</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="57">
+    <row r="12" spans="1:19" ht="57" hidden="1">
       <c r="A12" s="3" t="s">
         <v>154</v>
       </c>
@@ -1923,7 +1941,7 @@
         <v>6047</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="28.5">
+    <row r="13" spans="1:19" ht="28.5" hidden="1">
       <c r="A13" s="3" t="s">
         <v>107</v>
       </c>
@@ -1970,7 +1988,7 @@
         <v>5903</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="28.5">
+    <row r="14" spans="1:19" ht="28.5" hidden="1">
       <c r="A14" s="3" t="s">
         <v>102</v>
       </c>
@@ -2017,7 +2035,7 @@
         <v>5898</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="28.5">
+    <row r="15" spans="1:19" ht="28.5" hidden="1">
       <c r="A15" s="3" t="s">
         <v>135</v>
       </c>
@@ -2064,7 +2082,7 @@
         <v>5924</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="28.5">
+    <row r="16" spans="1:19" ht="28.5" hidden="1">
       <c r="A16" s="3" t="s">
         <v>130</v>
       </c>
@@ -2109,7 +2127,7 @@
         <v>5938</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="42.75">
+    <row r="17" spans="1:19" ht="42.75" hidden="1">
       <c r="A17" s="3" t="s">
         <v>142</v>
       </c>
@@ -2156,7 +2174,7 @@
         <v>6049</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="28.5">
+    <row r="18" spans="1:19" ht="28.5" hidden="1">
       <c r="A18" s="3" t="s">
         <v>140</v>
       </c>
@@ -2201,7 +2219,7 @@
         <v>5962</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="28.5">
+    <row r="19" spans="1:19" ht="28.5" hidden="1">
       <c r="A19" s="3" t="s">
         <v>53</v>
       </c>
@@ -2252,7 +2270,7 @@
         <v>5863</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="60" customHeight="1">
+    <row r="20" spans="1:19" ht="60" hidden="1" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>44</v>
       </c>
@@ -2303,7 +2321,7 @@
         <v>5874</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="28.5">
+    <row r="21" spans="1:19" ht="28.5" hidden="1">
       <c r="A21" s="3" t="s">
         <v>52</v>
       </c>
@@ -2354,7 +2372,7 @@
         <v>5880</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="28.5">
+    <row r="22" spans="1:19" ht="28.5" hidden="1">
       <c r="A22" s="3" t="s">
         <v>58</v>
       </c>
@@ -2405,7 +2423,7 @@
         <v>5882</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="28.5">
+    <row r="23" spans="1:19" ht="28.5" hidden="1">
       <c r="A23" s="3" t="s">
         <v>69</v>
       </c>
@@ -2456,7 +2474,7 @@
         <v>5865</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="28.5">
+    <row r="24" spans="1:19" ht="28.5" hidden="1">
       <c r="A24" s="3" t="s">
         <v>73</v>
       </c>
@@ -2507,7 +2525,7 @@
         <v>5870</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="28.5">
+    <row r="25" spans="1:19" ht="28.5" hidden="1">
       <c r="A25" s="3" t="s">
         <v>76</v>
       </c>
@@ -2558,7 +2576,7 @@
         <v>5878</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="28.5">
+    <row r="26" spans="1:19" ht="28.5" hidden="1">
       <c r="A26" s="3" t="s">
         <v>39</v>
       </c>
@@ -2609,7 +2627,7 @@
         <v>5861</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="57">
+    <row r="27" spans="1:19" ht="57" hidden="1">
       <c r="A27" s="3" t="s">
         <v>111</v>
       </c>
@@ -2656,7 +2674,7 @@
         <v>5960</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="28.5">
+    <row r="28" spans="1:19" ht="28.5" hidden="1">
       <c r="A28" s="3" t="s">
         <v>111</v>
       </c>
@@ -2707,7 +2725,7 @@
         <v>5867</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="42.75">
+    <row r="29" spans="1:19" ht="42.75" hidden="1">
       <c r="A29" s="3" t="s">
         <v>117</v>
       </c>
@@ -2754,7 +2772,7 @@
         <v>5957</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="28.5">
+    <row r="30" spans="1:19" ht="28.5" hidden="1">
       <c r="A30" s="3" t="s">
         <v>61</v>
       </c>
@@ -2805,7 +2823,7 @@
         <v>5872</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="42.75">
+    <row r="31" spans="1:19" ht="42.75" hidden="1">
       <c r="A31" s="3" t="s">
         <v>126</v>
       </c>
@@ -2850,7 +2868,7 @@
         <v>5876</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="28.5">
+    <row r="32" spans="1:19" ht="28.5" hidden="1">
       <c r="A32" s="3" t="s">
         <v>151</v>
       </c>
@@ -2897,7 +2915,7 @@
         <v>6056</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="28.5">
+    <row r="33" spans="1:19" ht="28.5" hidden="1">
       <c r="A33" s="3" t="s">
         <v>151</v>
       </c>
@@ -2944,7 +2962,7 @@
         <v>6040</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="28.5">
+    <row r="34" spans="1:19" ht="28.5" hidden="1">
       <c r="A34" s="3" t="s">
         <v>151</v>
       </c>
@@ -2991,7 +3009,7 @@
         <v>6037</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="28.5">
+    <row r="35" spans="1:19" ht="28.5" hidden="1">
       <c r="A35" s="3" t="s">
         <v>151</v>
       </c>
@@ -3038,7 +3056,7 @@
         <v>6039</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="28.5">
+    <row r="36" spans="1:19" ht="28.5" hidden="1">
       <c r="A36" s="4" t="s">
         <v>151</v>
       </c>
@@ -3085,7 +3103,7 @@
         <v>6046</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="28.5">
+    <row r="37" spans="1:19" ht="28.5" hidden="1">
       <c r="A37" s="3" t="s">
         <v>151</v>
       </c>
@@ -3128,7 +3146,7 @@
         <v>6036</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="42.75">
+    <row r="38" spans="1:19" ht="42.75" hidden="1">
       <c r="A38" s="3" t="s">
         <v>164</v>
       </c>
@@ -3175,7 +3193,7 @@
         <v>5995</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="28.5">
+    <row r="39" spans="1:19" ht="28.5" hidden="1">
       <c r="A39" s="3" t="s">
         <v>151</v>
       </c>
@@ -3222,7 +3240,7 @@
         <v>5993</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="28.5">
+    <row r="40" spans="1:19" ht="28.5" hidden="1">
       <c r="A40" s="3" t="s">
         <v>151</v>
       </c>
@@ -3269,7 +3287,7 @@
         <v>5991</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="71.25">
+    <row r="41" spans="1:19" ht="71.25" hidden="1">
       <c r="A41" s="3" t="s">
         <v>171</v>
       </c>
@@ -3316,7 +3334,7 @@
         <v>5989</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="28.5">
+    <row r="42" spans="1:19" ht="28.5" hidden="1">
       <c r="A42" s="3" t="s">
         <v>151</v>
       </c>
@@ -3363,7 +3381,7 @@
         <v>5987</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="28.5">
+    <row r="43" spans="1:19" ht="28.5" hidden="1">
       <c r="A43" s="3" t="s">
         <v>151</v>
       </c>
@@ -3410,7 +3428,7 @@
         <v>5985</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="28.5">
+    <row r="44" spans="1:19" ht="28.5" hidden="1">
       <c r="A44" s="3" t="s">
         <v>151</v>
       </c>
@@ -3457,7 +3475,7 @@
         <v>5983</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="28.5">
+    <row r="45" spans="1:19" ht="28.5" hidden="1">
       <c r="A45" s="3" t="s">
         <v>151</v>
       </c>
@@ -3504,7 +3522,7 @@
         <v>5981</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="42.75">
+    <row r="46" spans="1:19" ht="42.75" hidden="1">
       <c r="A46" s="3" t="s">
         <v>173</v>
       </c>
@@ -3551,7 +3569,7 @@
         <v>5979</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="42.75">
+    <row r="47" spans="1:19" ht="42.75" hidden="1">
       <c r="A47" s="3" t="s">
         <v>175</v>
       </c>
@@ -3598,7 +3616,7 @@
         <v>5977</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="28.5">
+    <row r="48" spans="1:19" ht="28.5" hidden="1">
       <c r="A48" s="3" t="s">
         <v>151</v>
       </c>
@@ -3645,7 +3663,7 @@
         <v>5975</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="28.5">
+    <row r="49" spans="1:19" ht="28.5" hidden="1">
       <c r="A49" s="3" t="s">
         <v>151</v>
       </c>
@@ -3692,7 +3710,7 @@
         <v>5973</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="28.5">
+    <row r="50" spans="1:19" ht="28.5" hidden="1">
       <c r="A50" s="3" t="s">
         <v>151</v>
       </c>
@@ -3739,7 +3757,7 @@
         <v>5971</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="28.5">
+    <row r="51" spans="1:19" ht="28.5" hidden="1">
       <c r="A51" s="3" t="s">
         <v>151</v>
       </c>
@@ -3786,7 +3804,7 @@
         <v>5969</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="28.5">
+    <row r="52" spans="1:19" ht="28.5" hidden="1">
       <c r="A52" s="3" t="s">
         <v>151</v>
       </c>
@@ -3867,7 +3885,9 @@
       <c r="L53" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="M53" s="3"/>
+      <c r="M53" s="3" t="s">
+        <v>281</v>
+      </c>
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
       <c r="P53" s="3"/>
@@ -3880,7 +3900,7 @@
         <v>5965</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="28.5">
+    <row r="54" spans="1:19" ht="28.5" hidden="1">
       <c r="A54" s="3" t="s">
         <v>140</v>
       </c>
@@ -3925,7 +3945,7 @@
         <v>6030</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="28.5">
+    <row r="55" spans="1:19" ht="28.5" hidden="1">
       <c r="A55" s="3" t="s">
         <v>151</v>
       </c>
@@ -3968,7 +3988,7 @@
         <v>6054</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="28.5">
+    <row r="56" spans="1:19" ht="28.5" hidden="1">
       <c r="A56" s="3" t="s">
         <v>151</v>
       </c>
@@ -4009,7 +4029,7 @@
         <v>6028</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="28.5">
+    <row r="57" spans="1:19" ht="28.5" hidden="1">
       <c r="A57" s="3" t="s">
         <v>151</v>
       </c>
@@ -4054,7 +4074,7 @@
         <v>6023</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="57">
+    <row r="58" spans="1:19" ht="57" hidden="1">
       <c r="A58" s="3" t="s">
         <v>213</v>
       </c>
@@ -4099,7 +4119,7 @@
         <v>6016</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="57">
+    <row r="59" spans="1:19" ht="57" hidden="1">
       <c r="A59" s="3" t="s">
         <v>218</v>
       </c>
@@ -4144,7 +4164,7 @@
         <v>6021</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="57">
+    <row r="60" spans="1:19" ht="57" hidden="1">
       <c r="A60" s="3" t="s">
         <v>221</v>
       </c>
@@ -4189,7 +4209,7 @@
         <v>6011</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="71.25">
+    <row r="61" spans="1:19" ht="71.25" hidden="1">
       <c r="A61" s="3" t="s">
         <v>224</v>
       </c>
@@ -4234,7 +4254,7 @@
         <v>6020</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="71.25">
+    <row r="62" spans="1:19" ht="71.25" hidden="1">
       <c r="A62" s="3" t="s">
         <v>229</v>
       </c>
@@ -4277,7 +4297,7 @@
         <v>6013</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="57">
+    <row r="63" spans="1:19" ht="57" hidden="1">
       <c r="A63" s="3" t="s">
         <v>228</v>
       </c>
@@ -4326,7 +4346,7 @@
         <v>6025</v>
       </c>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" hidden="1">
       <c r="A64" s="3" t="s">
         <v>230</v>
       </c>
@@ -4369,7 +4389,7 @@
         <v>6034</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="28.5">
+    <row r="65" spans="1:19" ht="28.5" hidden="1">
       <c r="A65" s="3" t="s">
         <v>151</v>
       </c>
@@ -4416,7 +4436,7 @@
         <v>5911</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="28.5">
+    <row r="66" spans="1:19" ht="28.5" hidden="1">
       <c r="A66" s="3" t="s">
         <v>151</v>
       </c>
@@ -4465,9 +4485,9 @@
         <v>5927</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="42.75">
-      <c r="A67" s="3">
-        <v>601244</v>
+    <row r="67" spans="1:19" ht="42.75" hidden="1">
+      <c r="A67" s="3" t="s">
+        <v>278</v>
       </c>
       <c r="B67" s="3" t="str">
         <f>RIGHT(TabelaEquipamentos[[#This Row],[TAG]],6)</f>
@@ -4516,9 +4536,9 @@
         <v>5929</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="57">
-      <c r="A68" s="3">
-        <v>601243</v>
+    <row r="68" spans="1:19" ht="57" hidden="1">
+      <c r="A68" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="B68" s="3" t="str">
         <f>RIGHT(TabelaEquipamentos[[#This Row],[TAG]],6)</f>
@@ -4567,9 +4587,9 @@
         <v>5931</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="28.5">
-      <c r="A69" s="3">
-        <v>601252</v>
+    <row r="69" spans="1:19" ht="28.5" hidden="1">
+      <c r="A69" s="3" t="s">
+        <v>280</v>
       </c>
       <c r="B69" s="3" t="str">
         <f>RIGHT(TabelaEquipamentos[[#This Row],[TAG]],6)</f>
@@ -4616,7 +4636,7 @@
         <v>5934</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="28.5">
+    <row r="70" spans="1:19" ht="28.5" hidden="1">
       <c r="A70" s="3" t="s">
         <v>276</v>
       </c>
@@ -4663,7 +4683,7 @@
         <v>5936</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="28.5">
+    <row r="71" spans="1:19" ht="28.5" hidden="1">
       <c r="A71" s="3" t="s">
         <v>151</v>
       </c>
@@ -4712,7 +4732,7 @@
         <v>5954</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="28.5">
+    <row r="72" spans="1:19" ht="28.5" hidden="1">
       <c r="A72" s="3" t="s">
         <v>151</v>
       </c>
@@ -4747,7 +4767,7 @@
         <v>5964</v>
       </c>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" hidden="1">
       <c r="A73" s="3" t="s">
         <v>151</v>
       </c>
@@ -4780,7 +4800,7 @@
         <v>6052</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="28.5">
+    <row r="74" spans="1:19" ht="28.5" hidden="1">
       <c r="A74" s="3" t="s">
         <v>151</v>
       </c>
@@ -4821,7 +4841,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="28.5">
+    <row r="75" spans="1:19" ht="28.5" hidden="1">
       <c r="A75" s="3" t="s">
         <v>151</v>
       </c>
@@ -4864,7 +4884,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="57">
+    <row r="76" spans="1:19" ht="57" hidden="1">
       <c r="A76" s="3" t="s">
         <v>213</v>
       </c>
@@ -4907,7 +4927,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="57">
+    <row r="77" spans="1:19" ht="57" hidden="1">
       <c r="A77" s="3" t="s">
         <v>218</v>
       </c>
@@ -4950,7 +4970,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="57">
+    <row r="78" spans="1:19" ht="57" hidden="1">
       <c r="A78" s="3" t="s">
         <v>221</v>
       </c>
@@ -4993,7 +5013,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="71.25">
+    <row r="79" spans="1:19" ht="71.25" hidden="1">
       <c r="A79" s="3" t="s">
         <v>224</v>
       </c>
@@ -5036,7 +5056,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="71.25">
+    <row r="80" spans="1:19" ht="71.25" hidden="1">
       <c r="A80" s="3" t="s">
         <v>229</v>
       </c>
@@ -5079,7 +5099,7 @@
         <v>6013</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="28.5">
+    <row r="81" spans="1:19" ht="28.5" hidden="1">
       <c r="A81" s="3" t="s">
         <v>151</v>
       </c>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1F6EB5-DC61-40E5-AF57-3A46A6BCDBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2965E39-5C84-4C25-811C-6755A00F54E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipamentos" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="136">
   <si>
     <t>TAG</t>
   </si>
@@ -343,6 +343,108 @@
   </si>
   <si>
     <t>assets/img/vertimax.jpg</t>
+  </si>
+  <si>
+    <t>RE-601011</t>
+  </si>
+  <si>
+    <t>RE-601012</t>
+  </si>
+  <si>
+    <t>RE-601013</t>
+  </si>
+  <si>
+    <t>RE-601014</t>
+  </si>
+  <si>
+    <t>RE-601015</t>
+  </si>
+  <si>
+    <t>RE-601016</t>
+  </si>
+  <si>
+    <t>RE-601017</t>
+  </si>
+  <si>
+    <t>RE-601018</t>
+  </si>
+  <si>
+    <t>RE-601019</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> C10 - 3</t>
+  </si>
+  <si>
+    <t>MOTOR 5 CV 4 POLOS</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>13,5 L</t>
+  </si>
+  <si>
+    <t>DOSADOR DE CAVACO 1</t>
+  </si>
+  <si>
+    <t>assets/img/redutorc10.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/Desenho_C09C16_PT.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/manualcoaxial.pdf</t>
+  </si>
+  <si>
+    <t>DOSADOR DE CAVACO 2</t>
+  </si>
+  <si>
+    <t>DOSADOR DE CAVACO 3</t>
+  </si>
+  <si>
+    <t>DOSADOR DE CAVACO 4</t>
+  </si>
+  <si>
+    <t>DOSADOR DE CAVACO 5</t>
+  </si>
+  <si>
+    <t>DOSADOR DE CAVACO 6</t>
+  </si>
+  <si>
+    <t>DOSADOR DE CAVACO 7</t>
+  </si>
+  <si>
+    <t>DOSADOR DE CAVACO 8</t>
+  </si>
+  <si>
+    <t>DOSADOR DE CAVACO 9</t>
+  </si>
+  <si>
+    <t>OS Nº 5922 - GOLD</t>
+  </si>
+  <si>
+    <t>OS Nº 5942 - GOLD</t>
+  </si>
+  <si>
+    <t>OS Nº 5894 - GOLD</t>
+  </si>
+  <si>
+    <t>OS Nº 5952 - GOLD</t>
+  </si>
+  <si>
+    <t>OS Nº 5946 - GOLD</t>
+  </si>
+  <si>
+    <t>OS Nº 5904 - GOLD</t>
+  </si>
+  <si>
+    <t>OS Nº 5913 - GOLD</t>
+  </si>
+  <si>
+    <t>OS Nº 5941 - GOLD</t>
+  </si>
+  <si>
+    <t>OS Nº 5900 - GOLD</t>
   </si>
 </sst>
 </file>
@@ -428,7 +530,37 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -564,27 +696,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R11" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
-  <autoFilter ref="A1:R11" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R20" headerRowDxfId="26" dataDxfId="25" totalsRowDxfId="24">
+  <autoFilter ref="A1:R20" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Certificado" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="OS Nº" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="23"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Certificado" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="OS Nº" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -739,7 +871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="25.375" style="2" bestFit="1" customWidth="1"/>
@@ -1339,16 +1471,460 @@
         <v>92</v>
       </c>
     </row>
+    <row r="12" spans="1:18" ht="57">
+      <c r="A12" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="4">
+        <v>180.35</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="57">
+      <c r="A13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" s="4">
+        <v>180.35</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="57">
+      <c r="A14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="4">
+        <v>180.35</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="57">
+      <c r="A15" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" s="4">
+        <v>180.35</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="57">
+      <c r="A16" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" s="4">
+        <v>180.35</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="57">
+      <c r="A17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="4">
+        <v>180.35</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="57">
+      <c r="A18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="4">
+        <v>180.35</v>
+      </c>
+      <c r="G18" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="57">
+      <c r="A19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="4">
+        <v>180.35</v>
+      </c>
+      <c r="G19" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="57">
+      <c r="A20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="4">
+        <v>180.35</v>
+      </c>
+      <c r="G20" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B12:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+  <conditionalFormatting sqref="B21:B1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R11">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q12:Q20">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2965E39-5C84-4C25-811C-6755A00F54E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2582EE71-78BA-4A88-A786-34F438D5167D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipamentos" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="135">
   <si>
     <t>TAG</t>
   </si>
@@ -148,9 +148,6 @@
   </si>
   <si>
     <t>WEG CESTARI</t>
-  </si>
-  <si>
-    <t>MOTOREDUTOR</t>
   </si>
   <si>
     <t>ISO VG 220</t>
@@ -530,27 +527,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -696,27 +673,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R20" headerRowDxfId="26" dataDxfId="25" totalsRowDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R20" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
   <autoFilter ref="A1:R20" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="23"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="10"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Certificado" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="8"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="7"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="OS Nº" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="21"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="19">
+      <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Certificado" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="OS Nº" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -875,8 +854,8 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="25.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.125" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.625" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.625" style="2" customWidth="1"/>
@@ -948,24 +927,25 @@
         <v>16</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="57">
       <c r="A2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>37</v>
+      <c r="C2" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="F2" s="4">
         <v>41.4</v>
@@ -974,50 +954,51 @@
         <v>1750</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="L2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="N2" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="57">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>37</v>
+      <c r="C3" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="F3" s="4">
         <v>41.4</v>
@@ -1026,50 +1007,51 @@
         <v>1750</v>
       </c>
       <c r="H3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="K3" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="57">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>37</v>
+      <c r="C4" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="F4" s="4">
         <v>41.4</v>
@@ -1078,50 +1060,51 @@
         <v>1750</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="K4" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="57">
       <c r="A5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>37</v>
+      <c r="C5" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="F5" s="4">
         <v>41.4</v>
@@ -1130,50 +1113,51 @@
         <v>1750</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="K5" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="57">
       <c r="A6" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>37</v>
+      <c r="C6" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="F6" s="4">
         <v>43.65</v>
@@ -1182,50 +1166,51 @@
         <v>1750</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="L6" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="57">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>37</v>
+      <c r="C7" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="F7" s="4">
         <v>43.65</v>
@@ -1234,50 +1219,51 @@
         <v>1750</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="R7" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="57">
       <c r="A8" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>37</v>
+      <c r="C8" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="F8" s="4">
         <v>41.4</v>
@@ -1286,50 +1272,51 @@
         <v>1750</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="K8" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="R8" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="57">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>37</v>
+      <c r="C9" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="F9" s="4">
         <v>43.65</v>
@@ -1338,50 +1325,51 @@
         <v>1750</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="57">
       <c r="A10" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>37</v>
+      <c r="C10" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F10" s="4">
         <v>43.65</v>
@@ -1390,50 +1378,51 @@
         <v>1750</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="R10" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="57">
       <c r="A11" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>37</v>
+      <c r="C11" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F11" s="4">
         <v>41.4</v>
@@ -1442,50 +1431,51 @@
         <v>1750</v>
       </c>
       <c r="H11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="K11" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="R11" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="57">
       <c r="A12" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>37</v>
+      <c r="C12" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="F12" s="4">
         <v>180.35</v>
@@ -1494,47 +1484,48 @@
         <v>1750</v>
       </c>
       <c r="H12" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J12" s="4" t="s">
+      <c r="K12" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="L12" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="M12" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="N12" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="57">
       <c r="A13" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>37</v>
+      <c r="C13" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="F13" s="4">
         <v>180.35</v>
@@ -1543,47 +1534,48 @@
         <v>1750</v>
       </c>
       <c r="H13" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="K13" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L13" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="M13" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="N13" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="57">
       <c r="A14" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>37</v>
+      <c r="C14" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="F14" s="4">
         <v>180.35</v>
@@ -1592,47 +1584,48 @@
         <v>1750</v>
       </c>
       <c r="H14" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="K14" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L14" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="M14" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="M14" s="4" t="s">
+      <c r="N14" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="57">
       <c r="A15" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>37</v>
+      <c r="C15" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="F15" s="4">
         <v>180.35</v>
@@ -1641,47 +1634,48 @@
         <v>1750</v>
       </c>
       <c r="H15" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="K15" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L15" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="M15" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="N15" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="57">
       <c r="A16" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>37</v>
+      <c r="C16" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="F16" s="4">
         <v>180.35</v>
@@ -1690,47 +1684,48 @@
         <v>1750</v>
       </c>
       <c r="H16" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="K16" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L16" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="M16" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="N16" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="57">
       <c r="A17" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>37</v>
+      <c r="C17" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="F17" s="4">
         <v>180.35</v>
@@ -1739,47 +1734,48 @@
         <v>1750</v>
       </c>
       <c r="H17" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="K17" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L17" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="M17" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="N17" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="57">
       <c r="A18" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>37</v>
+      <c r="C18" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="F18" s="4">
         <v>180.35</v>
@@ -1788,47 +1784,48 @@
         <v>1750</v>
       </c>
       <c r="H18" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="K18" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L18" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="M18" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="M18" s="4" t="s">
+      <c r="N18" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="57">
       <c r="A19" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>37</v>
+      <c r="C19" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="F19" s="4">
         <v>180.35</v>
@@ -1837,47 +1834,48 @@
         <v>1750</v>
       </c>
       <c r="H19" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J19" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="K19" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L19" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="M19" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="M19" s="4" t="s">
+      <c r="N19" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="57">
       <c r="A20" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>37</v>
+      <c r="C20" s="4" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="F20" s="4">
         <v>180.35</v>
@@ -1886,45 +1884,45 @@
         <v>1750</v>
       </c>
       <c r="H20" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J20" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="K20" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L20" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="M20" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="M20" s="4" t="s">
+      <c r="N20" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B21:B1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q12:Q20">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R11">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q12:Q20">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2582EE71-78BA-4A88-A786-34F438D5167D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E733EA-C2FC-40E0-88B7-FECACB51AE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipamentos" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="189">
   <si>
     <t>TAG</t>
   </si>
@@ -153,9 +153,6 @@
     <t>ISO VG 220</t>
   </si>
   <si>
-    <t>OS Nº</t>
-  </si>
-  <si>
     <t xml:space="preserve"> assets/pdf/manualvertimax.pdf</t>
   </si>
   <si>
@@ -442,6 +439,171 @@
   </si>
   <si>
     <t>OS Nº 5900 - GOLD</t>
+  </si>
+  <si>
+    <t>TAG Nº</t>
+  </si>
+  <si>
+    <t>PROMOEN</t>
+  </si>
+  <si>
+    <t>SRRP - P2</t>
+  </si>
+  <si>
+    <t>MOTOR 1,5 CV 4 POLOS</t>
+  </si>
+  <si>
+    <t>S/I</t>
+  </si>
+  <si>
+    <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-09 LE FEIXE</t>
+  </si>
+  <si>
+    <t>OS Nº 5995 - GOLD</t>
+  </si>
+  <si>
+    <t>EM FASE DE CONCLUSÃO</t>
+  </si>
+  <si>
+    <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-01 LD - SUPER SEC</t>
+  </si>
+  <si>
+    <t>OS Nº 5993 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-01 LE - SUPER SEC</t>
+  </si>
+  <si>
+    <t>OS Nº 5991 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-08 LD FEIXE</t>
+  </si>
+  <si>
+    <t>OS Nº 5989 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-02 LD - SUPER SEC</t>
+  </si>
+  <si>
+    <t>OS Nº 5987 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-02 LE - SUPER SEC</t>
+  </si>
+  <si>
+    <t>OS Nº 5985 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-07 LE SCREEN</t>
+  </si>
+  <si>
+    <t>OS Nº 5983 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-08 LE FEIXE</t>
+  </si>
+  <si>
+    <t>OS Nº 5981 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-07 LD SCREEN</t>
+  </si>
+  <si>
+    <t>OS Nº 5979 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-06 LE SCREEN</t>
+  </si>
+  <si>
+    <t>OS Nº 5977 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-06 LD SCREEN</t>
+  </si>
+  <si>
+    <t>OS Nº 5975 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-09 LD FEIXE</t>
+  </si>
+  <si>
+    <t>OS Nº 5973 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR DE FULIGEM RETRÁTIL SF-04 LE - SUPER SEC / PRIM</t>
+  </si>
+  <si>
+    <t>OS Nº 5971 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR DE FULIGEM RETRÁTIL SF-05 LE - SUPER SEC / PRIM</t>
+  </si>
+  <si>
+    <t>OS Nº 5969 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR DE FULIGEM RETRÁTIL SF-05 LD - SUPER SEC / PRIM</t>
+  </si>
+  <si>
+    <t>OS Nº 5967 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-04 LD - SUPER SEC / PRIM</t>
+  </si>
+  <si>
+    <t>OS Nº 5965 - GOLD</t>
+  </si>
+  <si>
+    <t>assets/img/promen.jpg</t>
+  </si>
+  <si>
+    <t>RE-601046</t>
+  </si>
+  <si>
+    <t>RE-601029</t>
+  </si>
+  <si>
+    <t>RE-601030</t>
+  </si>
+  <si>
+    <t>RE-601043</t>
+  </si>
+  <si>
+    <t>RE-601031</t>
+  </si>
+  <si>
+    <t>RE-601032</t>
+  </si>
+  <si>
+    <t>RE-601042</t>
+  </si>
+  <si>
+    <t>RE-601044</t>
+  </si>
+  <si>
+    <t>RE-601041</t>
+  </si>
+  <si>
+    <t>RE-601040</t>
+  </si>
+  <si>
+    <t>RE-601039</t>
+  </si>
+  <si>
+    <t>RE-601045</t>
+  </si>
+  <si>
+    <t>RE-601036</t>
+  </si>
+  <si>
+    <t>RE-601038</t>
+  </si>
+  <si>
+    <t>RE-601037</t>
+  </si>
+  <si>
+    <t>RE-601035</t>
   </si>
 </sst>
 </file>
@@ -470,7 +632,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -487,12 +649,6 @@
         <fgColor rgb="FFD4AF37"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -506,16 +662,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -673,8 +826,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R20" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
-  <autoFilter ref="A1:R20" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R36" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+  <autoFilter ref="A1:R36" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="21"/>
     <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="20"/>
@@ -695,7 +848,7 @@
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Certificado" dataDxfId="7"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="6"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="OS Nº" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -850,25 +1003,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R20"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="25.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.5" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.125" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14" style="2" customWidth="1"/>
     <col min="7" max="7" width="12.125" style="2" customWidth="1"/>
     <col min="8" max="8" width="8.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="21.875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="16.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="2.375" style="2" customWidth="1"/>
     <col min="17" max="17" width="20.125" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="32" style="2" customWidth="1"/>
     <col min="19" max="16384" width="9" style="2"/>
@@ -927,1005 +1082,1813 @@
         <v>16</v>
       </c>
       <c r="R1" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="57">
+      <c r="A2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3">
+        <v>41.4</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="57">
-      <c r="A2" s="4" t="s">
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="57">
+      <c r="A3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="4" t="str">
+      <c r="C3" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F3" s="3">
+        <v>41.4</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="4">
+      <c r="I3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="57">
+      <c r="A4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3">
         <v>41.4</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G4" s="3">
         <v>1750</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="K4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="57">
+      <c r="A5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="3">
+        <v>41.4</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="L2" s="4" t="s">
+      <c r="J5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="57">
-      <c r="A3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="N5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="57">
+      <c r="A6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="4" t="str">
+      <c r="C6" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="3">
+        <v>43.65</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="4">
+      <c r="I6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="57">
+      <c r="A7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="3">
+        <v>43.65</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="57">
+      <c r="A8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="3">
         <v>41.4</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G8" s="3">
         <v>1750</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="K8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="57">
+      <c r="A9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="3">
+        <v>43.65</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="57">
-      <c r="A4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="J9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="57">
+      <c r="A10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="4" t="str">
+      <c r="C10" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="3">
+        <v>43.65</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="4">
-        <v>41.4</v>
-      </c>
-      <c r="G4" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="57">
-      <c r="A5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="4" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
-        <v>MOTOREDUTOR WEG CESTARI</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="4">
-        <v>41.4</v>
-      </c>
-      <c r="G5" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="57">
-      <c r="A6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="4" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
-        <v>MOTOREDUTOR WEG CESTARI</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="4">
-        <v>43.65</v>
-      </c>
-      <c r="G6" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="57">
-      <c r="A7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="4" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
-        <v>MOTOREDUTOR WEG CESTARI</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="4">
-        <v>43.65</v>
-      </c>
-      <c r="G7" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" s="4" t="s">
+      <c r="K10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="M7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="57">
-      <c r="A8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="4" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
-        <v>MOTOREDUTOR WEG CESTARI</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="4">
-        <v>41.4</v>
-      </c>
-      <c r="G8" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="57">
-      <c r="A9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="4" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
-        <v>MOTOREDUTOR WEG CESTARI</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="4">
-        <v>43.65</v>
-      </c>
-      <c r="G9" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="57">
-      <c r="A10" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="4" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
-        <v>MOTOREDUTOR WEG CESTARI</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F10" s="4">
-        <v>43.65</v>
-      </c>
-      <c r="G10" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="K10" s="4" t="s">
+      <c r="M10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L10" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4" t="s">
+      <c r="R10" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="57">
       <c r="A11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="3">
+        <v>41.4</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="4" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
-        <v>MOTOREDUTOR WEG CESTARI</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" s="4">
-        <v>41.4</v>
-      </c>
-      <c r="G11" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" s="4" t="s">
+      <c r="L11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="L11" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4" t="s">
+      <c r="R11" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="57">
       <c r="A12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="4" t="str">
+      <c r="C12" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="3">
+        <v>180.35</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F12" s="4">
-        <v>180.35</v>
-      </c>
-      <c r="G12" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="L12" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="M12" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="N12" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="N12" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="2" t="s">
-        <v>134</v>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="R12" s="2">
+        <v>4388707</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="57">
       <c r="A13" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B13" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="4" t="str">
+      <c r="C13" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="3">
+        <v>180.35</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F13" s="4">
-        <v>180.35</v>
-      </c>
-      <c r="G13" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="I13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="L13" s="4" t="s">
+      <c r="K13" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M13" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="N13" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="N13" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="2" t="s">
-        <v>126</v>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="R13" s="2">
+        <v>4388753</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="57">
       <c r="A14" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="4" t="str">
+      <c r="C14" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="3">
+        <v>180.35</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F14" s="4">
-        <v>180.35</v>
-      </c>
-      <c r="G14" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H14" s="4" t="s">
+      <c r="I14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="L14" s="4" t="s">
+      <c r="K14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="M14" s="4" t="s">
+      <c r="N14" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="N14" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="2" t="s">
-        <v>127</v>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="R14" s="2">
+        <v>4388779</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="57">
       <c r="A15" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="4" t="str">
+      <c r="C15" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="3">
+        <v>180.35</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F15" s="4">
-        <v>180.35</v>
-      </c>
-      <c r="G15" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H15" s="4" t="s">
+      <c r="I15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="L15" s="4" t="s">
+      <c r="K15" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="N15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="N15" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="2" t="s">
-        <v>128</v>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="R15" s="2">
+        <v>4388718</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="57">
       <c r="A16" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="3">
+        <v>180.35</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="R16" s="2">
+        <v>4388775</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="57">
+      <c r="A17" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="4" t="str">
+      <c r="C17" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D17" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F17" s="3">
+        <v>180.35</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F16" s="4">
+      <c r="I17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="R17" s="2">
+        <v>4388796</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="57">
+      <c r="A18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="3">
         <v>180.35</v>
       </c>
-      <c r="G16" s="4">
+      <c r="G18" s="3">
         <v>1750</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="K18" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="R18" s="2">
+        <v>4390658</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="57">
+      <c r="A19" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" s="3">
+        <v>180.35</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="L16" s="4" t="s">
+      <c r="J19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="N19" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="N16" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="57">
-      <c r="A17" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="R19" s="2">
+        <v>4388728</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="57">
+      <c r="A20" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="4" t="str">
+      <c r="C20" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D20" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="F20" s="3">
+        <v>180.35</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F17" s="4">
-        <v>180.35</v>
-      </c>
-      <c r="G17" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H17" s="4" t="s">
+      <c r="I20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="L17" s="4" t="s">
+      <c r="K20" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="N20" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="N17" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="57">
-      <c r="A18" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="4" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
-        <v>MOTOREDUTOR WEG CESTARI</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="4">
-        <v>180.35</v>
-      </c>
-      <c r="G18" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="57">
-      <c r="A19" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="4" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
-        <v>MOTOREDUTOR WEG CESTARI</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F19" s="4">
-        <v>180.35</v>
-      </c>
-      <c r="G19" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="2" t="s">
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" ht="57">
-      <c r="A20" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="4" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
-        <v>MOTOREDUTOR WEG CESTARI</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F20" s="4">
-        <v>180.35</v>
-      </c>
-      <c r="G20" s="4">
-        <v>1750</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="2" t="s">
-        <v>133</v>
+      <c r="R20" s="2">
+        <v>4388722</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="71.25">
+      <c r="A21" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I21" s="3">
+        <v>220</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="85.5">
+      <c r="A22" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I22" s="3">
+        <v>220</v>
+      </c>
+      <c r="J22" s="3">
+        <v>2</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="71.25">
+      <c r="A23" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I23" s="3">
+        <v>220</v>
+      </c>
+      <c r="J23" s="3">
+        <v>2</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="71.25">
+      <c r="A24" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I24" s="3">
+        <v>220</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="85.5">
+      <c r="A25" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I25" s="3">
+        <v>220</v>
+      </c>
+      <c r="J25" s="3">
+        <v>2</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="71.25">
+      <c r="A26" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I26" s="3">
+        <v>220</v>
+      </c>
+      <c r="J26" s="3">
+        <v>2</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="71.25">
+      <c r="A27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I27" s="3">
+        <v>220</v>
+      </c>
+      <c r="J27" s="3">
+        <v>2</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="71.25">
+      <c r="A28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I28" s="3">
+        <v>220</v>
+      </c>
+      <c r="J28" s="3">
+        <v>2</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="71.25">
+      <c r="A29" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I29" s="3">
+        <v>220</v>
+      </c>
+      <c r="J29" s="3">
+        <v>2</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="71.25">
+      <c r="A30" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I30" s="3">
+        <v>220</v>
+      </c>
+      <c r="J30" s="3">
+        <v>2</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="71.25">
+      <c r="A31" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C31" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I31" s="3">
+        <v>220</v>
+      </c>
+      <c r="J31" s="3">
+        <v>2</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="71.25">
+      <c r="A32" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I32" s="3">
+        <v>220</v>
+      </c>
+      <c r="J32" s="3">
+        <v>2</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="71.25">
+      <c r="A33" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C33" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G33" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I33" s="3">
+        <v>220</v>
+      </c>
+      <c r="J33" s="3">
+        <v>2</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="71.25">
+      <c r="A34" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I34" s="3">
+        <v>220</v>
+      </c>
+      <c r="J34" s="3">
+        <v>2</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="71.25">
+      <c r="A35" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I35" s="3">
+        <v>220</v>
+      </c>
+      <c r="J35" s="3">
+        <v>2</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="85.5">
+      <c r="A36" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR PROMOEN</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G36" s="3">
+        <v>1725</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I36" s="3">
+        <v>220</v>
+      </c>
+      <c r="J36" s="3">
+        <v>2</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B21:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q12:Q20">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  <conditionalFormatting sqref="B37:B1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R11">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="R2:R36">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -1942,10 +2905,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="5"/>
+      <c r="B1" s="4"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E733EA-C2FC-40E0-88B7-FECACB51AE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129863D4-EF65-400E-B251-EC8349C4D121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipamentos" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="194">
   <si>
     <t>TAG</t>
   </si>
@@ -604,6 +604,21 @@
   </si>
   <si>
     <t>RE-601035</t>
+  </si>
+  <si>
+    <t>RE-631517</t>
+  </si>
+  <si>
+    <t>MOTOREDUTOR</t>
+  </si>
+  <si>
+    <t>V09</t>
+  </si>
+  <si>
+    <t>OS Nº 5876 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR DA TRANSP. DE CORREIA TCD/48"  (ME631517) - CT-26</t>
   </si>
 </sst>
 </file>
@@ -632,7 +647,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -649,6 +664,12 @@
         <fgColor rgb="FFD4AF37"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -662,7 +683,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -675,6 +696,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -826,8 +853,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R36" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
-  <autoFilter ref="A1:R36" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R38" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+  <autoFilter ref="A1:R38" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Correia Transportadora - CT- 01"/>
+        <filter val="Correia Transportadora - CT- 02"/>
+        <filter val="Correia Transportadora - CT- 03"/>
+        <filter val="Correia Transportadora - CT- 04"/>
+        <filter val="Correia Transportadora - CT- 22"/>
+        <filter val="Correia Transportadora - CT- 23"/>
+        <filter val="Correia Transportadora - CT- 25"/>
+        <filter val="Correia Transportadora - CT-08"/>
+        <filter val="Correia Transportadora - CT-09"/>
+        <filter val="Correia Transportadora - CT-21"/>
+        <filter val="REDUTOR DA TRANSP. DE CORREIA TCD/48&quot; CT 26 (ME631517)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="21"/>
     <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="20"/>
@@ -1006,7 +1049,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
@@ -1615,7 +1658,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="57">
+    <row r="12" spans="1:18" ht="57" hidden="1">
       <c r="A12" s="3" t="s">
         <v>100</v>
       </c>
@@ -1668,7 +1711,7 @@
         <v>4388707</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="57">
+    <row r="13" spans="1:18" ht="57" hidden="1">
       <c r="A13" s="3" t="s">
         <v>101</v>
       </c>
@@ -1721,7 +1764,7 @@
         <v>4388753</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="57">
+    <row r="14" spans="1:18" ht="57" hidden="1">
       <c r="A14" s="3" t="s">
         <v>102</v>
       </c>
@@ -1774,7 +1817,7 @@
         <v>4388779</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="57">
+    <row r="15" spans="1:18" ht="57" hidden="1">
       <c r="A15" s="3" t="s">
         <v>103</v>
       </c>
@@ -1827,7 +1870,7 @@
         <v>4388718</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="57">
+    <row r="16" spans="1:18" ht="57" hidden="1">
       <c r="A16" s="3" t="s">
         <v>104</v>
       </c>
@@ -1880,7 +1923,7 @@
         <v>4388775</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="57">
+    <row r="17" spans="1:18" ht="57" hidden="1">
       <c r="A17" s="3" t="s">
         <v>105</v>
       </c>
@@ -1933,7 +1976,7 @@
         <v>4388796</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="57">
+    <row r="18" spans="1:18" ht="57" hidden="1">
       <c r="A18" s="3" t="s">
         <v>106</v>
       </c>
@@ -1986,7 +2029,7 @@
         <v>4390658</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="57">
+    <row r="19" spans="1:18" ht="57" hidden="1">
       <c r="A19" s="3" t="s">
         <v>107</v>
       </c>
@@ -2039,7 +2082,7 @@
         <v>4388728</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="57">
+    <row r="20" spans="1:18" ht="57" hidden="1">
       <c r="A20" s="3" t="s">
         <v>108</v>
       </c>
@@ -2092,7 +2135,7 @@
         <v>4388722</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="71.25">
+    <row r="21" spans="1:18" ht="71.25" hidden="1">
       <c r="A21" s="3" t="s">
         <v>173</v>
       </c>
@@ -2141,7 +2184,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="85.5">
+    <row r="22" spans="1:18" ht="71.25" hidden="1">
       <c r="A22" s="3" t="s">
         <v>174</v>
       </c>
@@ -2190,7 +2233,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="71.25">
+    <row r="23" spans="1:18" ht="71.25" hidden="1">
       <c r="A23" s="3" t="s">
         <v>175</v>
       </c>
@@ -2239,7 +2282,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="71.25">
+    <row r="24" spans="1:18" ht="71.25" hidden="1">
       <c r="A24" s="3" t="s">
         <v>176</v>
       </c>
@@ -2288,7 +2331,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="85.5">
+    <row r="25" spans="1:18" ht="71.25" hidden="1">
       <c r="A25" s="3" t="s">
         <v>177</v>
       </c>
@@ -2337,7 +2380,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="71.25">
+    <row r="26" spans="1:18" ht="71.25" hidden="1">
       <c r="A26" s="3" t="s">
         <v>178</v>
       </c>
@@ -2386,7 +2429,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="71.25">
+    <row r="27" spans="1:18" ht="71.25" hidden="1">
       <c r="A27" s="3" t="s">
         <v>179</v>
       </c>
@@ -2435,7 +2478,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="71.25">
+    <row r="28" spans="1:18" ht="71.25" hidden="1">
       <c r="A28" s="3" t="s">
         <v>180</v>
       </c>
@@ -2484,7 +2527,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="71.25">
+    <row r="29" spans="1:18" ht="71.25" hidden="1">
       <c r="A29" s="3" t="s">
         <v>181</v>
       </c>
@@ -2533,7 +2576,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="71.25">
+    <row r="30" spans="1:18" ht="71.25" hidden="1">
       <c r="A30" s="3" t="s">
         <v>182</v>
       </c>
@@ -2582,7 +2625,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="71.25">
+    <row r="31" spans="1:18" ht="71.25" hidden="1">
       <c r="A31" s="3" t="s">
         <v>183</v>
       </c>
@@ -2631,7 +2674,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="71.25">
+    <row r="32" spans="1:18" ht="71.25" hidden="1">
       <c r="A32" s="3" t="s">
         <v>184</v>
       </c>
@@ -2680,7 +2723,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="71.25">
+    <row r="33" spans="1:18" ht="71.25" hidden="1">
       <c r="A33" s="3" t="s">
         <v>185</v>
       </c>
@@ -2729,7 +2772,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="71.25">
+    <row r="34" spans="1:18" ht="71.25" hidden="1">
       <c r="A34" s="3" t="s">
         <v>186</v>
       </c>
@@ -2778,7 +2821,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="71.25">
+    <row r="35" spans="1:18" ht="71.25" hidden="1">
       <c r="A35" s="3" t="s">
         <v>187</v>
       </c>
@@ -2827,7 +2870,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="85.5">
+    <row r="36" spans="1:18" ht="85.5" hidden="1">
       <c r="A36" s="3" t="s">
         <v>188</v>
       </c>
@@ -2876,16 +2919,90 @@
         <v>141</v>
       </c>
     </row>
+    <row r="37" spans="1:18" ht="85.5">
+      <c r="A37" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J37" s="3">
+        <v>20</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="R37" s="2">
+        <v>5876</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v xml:space="preserve">MOTOREDUTOR </v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B37:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+  <conditionalFormatting sqref="B39:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R36">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="R2:R38">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129863D4-EF65-400E-B251-EC8349C4D121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDEE5EF-93F3-4D36-87DC-39AF0882C1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipamentos" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="219">
   <si>
     <t>TAG</t>
   </si>
@@ -619,6 +619,81 @@
   </si>
   <si>
     <t>REDUTOR DA TRANSP. DE CORREIA TCD/48"  (ME631517) - CT-26</t>
+  </si>
+  <si>
+    <t>RE-601063</t>
+  </si>
+  <si>
+    <t>V 07</t>
+  </si>
+  <si>
+    <t>MOTOR 1.5 CV 4 POLOS</t>
+  </si>
+  <si>
+    <t>REDUTOR VÁLVULA ROTATIVA 8 - CSC 4</t>
+  </si>
+  <si>
+    <t>OS Nº 5920 - GOLD</t>
+  </si>
+  <si>
+    <t>CONCLUIDA</t>
+  </si>
+  <si>
+    <t>5920</t>
+  </si>
+  <si>
+    <t>Coluna1</t>
+  </si>
+  <si>
+    <t>Coluna2</t>
+  </si>
+  <si>
+    <t>RE-601062</t>
+  </si>
+  <si>
+    <t>RE-601067</t>
+  </si>
+  <si>
+    <t>RE-601069</t>
+  </si>
+  <si>
+    <t>REDUTOR VÁLVULA ROTATIVA 1 - FEIXE 1</t>
+  </si>
+  <si>
+    <t>OS Nº 5903 - GOLD</t>
+  </si>
+  <si>
+    <t>5903</t>
+  </si>
+  <si>
+    <t>REDUTOR VÁLVULA ROTATIVA 6 - CSC 2</t>
+  </si>
+  <si>
+    <t>OS Nº 5898 - GOLD</t>
+  </si>
+  <si>
+    <t>5898</t>
+  </si>
+  <si>
+    <t>OS Nº 5924 - GOLD</t>
+  </si>
+  <si>
+    <t>5924</t>
+  </si>
+  <si>
+    <t>RE- 601068</t>
+  </si>
+  <si>
+    <t>REDUTOR VÁLVULA ROTATIVA 7 - CSC 3</t>
+  </si>
+  <si>
+    <t>OS Nº 5936 - GOLD</t>
+  </si>
+  <si>
+    <t>5936</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/lista-pecas-V07 -ROTATIVAS.pdf</t>
   </si>
 </sst>
 </file>
@@ -647,7 +722,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -664,12 +739,6 @@
         <fgColor rgb="FFD4AF37"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -683,7 +752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -697,17 +766,33 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="30">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -853,8 +938,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R38" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
-  <autoFilter ref="A1:R38" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:T42" headerRowDxfId="29" dataDxfId="28" totalsRowDxfId="27">
+  <autoFilter ref="A1:T42" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="10">
       <filters>
         <filter val="Correia Transportadora - CT- 01"/>
@@ -871,27 +956,29 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="21"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="19">
+  <tableColumns count="20">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="26"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="24">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Certificado" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Certificado" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="11"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{7BF229F1-8AF5-4349-856B-C68DFF7DB7CD}" name="Coluna1" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{9CF6539B-87FB-401A-974C-86AFB904B9CB}" name="Coluna2" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1049,7 +1136,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
@@ -1072,7 +1159,7 @@
     <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="24" customHeight="1">
+    <row r="1" spans="1:20" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1127,8 +1214,14 @@
       <c r="R1" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="57">
+      <c r="S1" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="57">
       <c r="A2" s="3" t="s">
         <v>39</v>
       </c>
@@ -1180,8 +1273,10 @@
       <c r="R2" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="57">
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+    </row>
+    <row r="3" spans="1:20" ht="57">
       <c r="A3" s="3" t="s">
         <v>40</v>
       </c>
@@ -1233,8 +1328,10 @@
       <c r="R3" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="57">
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+    </row>
+    <row r="4" spans="1:20" ht="57">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -1286,8 +1383,10 @@
       <c r="R4" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="57">
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+    </row>
+    <row r="5" spans="1:20" ht="57">
       <c r="A5" s="3" t="s">
         <v>42</v>
       </c>
@@ -1339,8 +1438,10 @@
       <c r="R5" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" ht="57">
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+    </row>
+    <row r="6" spans="1:20" ht="57">
       <c r="A6" s="3" t="s">
         <v>43</v>
       </c>
@@ -1392,8 +1493,10 @@
       <c r="R6" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="57">
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="1:20" ht="57">
       <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
@@ -1445,8 +1548,10 @@
       <c r="R7" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" ht="57">
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" spans="1:20" ht="57">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
@@ -1498,8 +1603,10 @@
       <c r="R8" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="57">
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" spans="1:20" ht="57">
       <c r="A9" s="3" t="s">
         <v>46</v>
       </c>
@@ -1551,8 +1658,10 @@
       <c r="R9" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="57">
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" spans="1:20" ht="57">
       <c r="A10" s="3" t="s">
         <v>82</v>
       </c>
@@ -1604,8 +1713,10 @@
       <c r="R10" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="57">
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" spans="1:20" ht="57">
       <c r="A11" s="3" t="s">
         <v>87</v>
       </c>
@@ -1657,8 +1768,10 @@
       <c r="R11" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" ht="57" hidden="1">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" ht="57" hidden="1">
       <c r="A12" s="3" t="s">
         <v>100</v>
       </c>
@@ -1710,8 +1823,10 @@
       <c r="R12" s="2">
         <v>4388707</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="57" hidden="1">
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:20" ht="57" hidden="1">
       <c r="A13" s="3" t="s">
         <v>101</v>
       </c>
@@ -1763,8 +1878,10 @@
       <c r="R13" s="2">
         <v>4388753</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" ht="57" hidden="1">
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:20" ht="57" hidden="1">
       <c r="A14" s="3" t="s">
         <v>102</v>
       </c>
@@ -1816,8 +1933,10 @@
       <c r="R14" s="2">
         <v>4388779</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" ht="57" hidden="1">
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:20" ht="57" hidden="1">
       <c r="A15" s="3" t="s">
         <v>103</v>
       </c>
@@ -1869,8 +1988,10 @@
       <c r="R15" s="2">
         <v>4388718</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" ht="57" hidden="1">
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:20" ht="57" hidden="1">
       <c r="A16" s="3" t="s">
         <v>104</v>
       </c>
@@ -1922,8 +2043,10 @@
       <c r="R16" s="2">
         <v>4388775</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" ht="57" hidden="1">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="1:20" ht="57" hidden="1">
       <c r="A17" s="3" t="s">
         <v>105</v>
       </c>
@@ -1975,8 +2098,10 @@
       <c r="R17" s="2">
         <v>4388796</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" ht="57" hidden="1">
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="1:20" ht="57" hidden="1">
       <c r="A18" s="3" t="s">
         <v>106</v>
       </c>
@@ -2028,8 +2153,10 @@
       <c r="R18" s="2">
         <v>4390658</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" ht="57" hidden="1">
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="1:20" ht="57" hidden="1">
       <c r="A19" s="3" t="s">
         <v>107</v>
       </c>
@@ -2081,8 +2208,10 @@
       <c r="R19" s="2">
         <v>4388728</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" ht="57" hidden="1">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="1:20" ht="57" hidden="1">
       <c r="A20" s="3" t="s">
         <v>108</v>
       </c>
@@ -2134,8 +2263,10 @@
       <c r="R20" s="2">
         <v>4388722</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" ht="71.25" hidden="1">
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="1:20" ht="71.25" hidden="1">
       <c r="A21" s="3" t="s">
         <v>173</v>
       </c>
@@ -2183,8 +2314,10 @@
       <c r="R21" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" ht="71.25" hidden="1">
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="1:20" ht="71.25" hidden="1">
       <c r="A22" s="3" t="s">
         <v>174</v>
       </c>
@@ -2232,8 +2365,10 @@
       <c r="R22" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" ht="71.25" hidden="1">
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="1:20" ht="71.25" hidden="1">
       <c r="A23" s="3" t="s">
         <v>175</v>
       </c>
@@ -2281,8 +2416,10 @@
       <c r="R23" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" ht="71.25" hidden="1">
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+    </row>
+    <row r="24" spans="1:20" ht="71.25" hidden="1">
       <c r="A24" s="3" t="s">
         <v>176</v>
       </c>
@@ -2330,8 +2467,10 @@
       <c r="R24" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" ht="71.25" hidden="1">
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+    </row>
+    <row r="25" spans="1:20" ht="71.25" hidden="1">
       <c r="A25" s="3" t="s">
         <v>177</v>
       </c>
@@ -2379,8 +2518,10 @@
       <c r="R25" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" ht="71.25" hidden="1">
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+    </row>
+    <row r="26" spans="1:20" ht="71.25" hidden="1">
       <c r="A26" s="3" t="s">
         <v>178</v>
       </c>
@@ -2428,8 +2569,10 @@
       <c r="R26" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" ht="71.25" hidden="1">
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+    </row>
+    <row r="27" spans="1:20" ht="71.25" hidden="1">
       <c r="A27" s="3" t="s">
         <v>179</v>
       </c>
@@ -2477,8 +2620,10 @@
       <c r="R27" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" ht="71.25" hidden="1">
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+    </row>
+    <row r="28" spans="1:20" ht="71.25" hidden="1">
       <c r="A28" s="3" t="s">
         <v>180</v>
       </c>
@@ -2526,8 +2671,10 @@
       <c r="R28" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" ht="71.25" hidden="1">
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+    </row>
+    <row r="29" spans="1:20" ht="71.25" hidden="1">
       <c r="A29" s="3" t="s">
         <v>181</v>
       </c>
@@ -2575,8 +2722,10 @@
       <c r="R29" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" ht="71.25" hidden="1">
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+    </row>
+    <row r="30" spans="1:20" ht="71.25" hidden="1">
       <c r="A30" s="3" t="s">
         <v>182</v>
       </c>
@@ -2624,8 +2773,10 @@
       <c r="R30" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" ht="71.25" hidden="1">
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+    </row>
+    <row r="31" spans="1:20" ht="71.25" hidden="1">
       <c r="A31" s="3" t="s">
         <v>183</v>
       </c>
@@ -2673,8 +2824,10 @@
       <c r="R31" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" ht="71.25" hidden="1">
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+    </row>
+    <row r="32" spans="1:20" ht="71.25" hidden="1">
       <c r="A32" s="3" t="s">
         <v>184</v>
       </c>
@@ -2722,8 +2875,10 @@
       <c r="R32" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" ht="71.25" hidden="1">
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+    </row>
+    <row r="33" spans="1:20" ht="71.25" hidden="1">
       <c r="A33" s="3" t="s">
         <v>185</v>
       </c>
@@ -2771,8 +2926,10 @@
       <c r="R33" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" ht="71.25" hidden="1">
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+    </row>
+    <row r="34" spans="1:20" ht="71.25" hidden="1">
       <c r="A34" s="3" t="s">
         <v>186</v>
       </c>
@@ -2820,8 +2977,10 @@
       <c r="R34" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" ht="71.25" hidden="1">
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+    </row>
+    <row r="35" spans="1:20" ht="71.25" hidden="1">
       <c r="A35" s="3" t="s">
         <v>187</v>
       </c>
@@ -2869,8 +3028,10 @@
       <c r="R35" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" ht="85.5" hidden="1">
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+    </row>
+    <row r="36" spans="1:20" ht="85.5" hidden="1">
       <c r="A36" s="3" t="s">
         <v>188</v>
       </c>
@@ -2918,8 +3079,10 @@
       <c r="R36" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" ht="85.5">
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+    </row>
+    <row r="37" spans="1:20" ht="85.5">
       <c r="A37" s="3" t="s">
         <v>189</v>
       </c>
@@ -2970,39 +3133,309 @@
       <c r="R37" s="2">
         <v>5876</v>
       </c>
-    </row>
-    <row r="38" spans="1:18">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="3" t="str">
-        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
-        <v xml:space="preserve">MOTOREDUTOR </v>
-      </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="3"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+    </row>
+    <row r="38" spans="1:20" ht="85.5">
+      <c r="A38" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F38" s="3">
+        <v>151</v>
+      </c>
+      <c r="G38" s="3">
+        <v>1720</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J38" s="3">
+        <v>5.75</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O38" s="3">
+        <v>928373</v>
+      </c>
       <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
+      <c r="Q38" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="85.5">
+      <c r="A39" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F39" s="3">
+        <v>151</v>
+      </c>
+      <c r="G39" s="3">
+        <v>1720</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J39" s="3">
+        <v>5.75</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O39" s="3">
+        <v>928875</v>
+      </c>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="85.5">
+      <c r="A40" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F40" s="3">
+        <v>151</v>
+      </c>
+      <c r="G40" s="3">
+        <v>1720</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J40" s="3">
+        <v>5.75</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O40" s="3">
+        <v>928369</v>
+      </c>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="85.5">
+      <c r="A41" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F41" s="3">
+        <v>151</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1720</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J41" s="3">
+        <v>5.75</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O41" s="3">
+        <v>928374</v>
+      </c>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="85.5">
+      <c r="A42" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F42" s="3">
+        <v>151</v>
+      </c>
+      <c r="G42" s="3">
+        <v>1720</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J42" s="3">
+        <v>5.75</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O42" s="3">
+        <v>928371</v>
+      </c>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3" t="s">
+        <v>217</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B39:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
+  <conditionalFormatting sqref="B43:B1048576">
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R38">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="R2:R42">
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDEE5EF-93F3-4D36-87DC-39AF0882C1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0427CB-294B-4CDA-90C6-7EC175356F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipamentos" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="256">
   <si>
     <t>TAG</t>
   </si>
@@ -639,15 +639,6 @@
     <t>CONCLUIDA</t>
   </si>
   <si>
-    <t>5920</t>
-  </si>
-  <si>
-    <t>Coluna1</t>
-  </si>
-  <si>
-    <t>Coluna2</t>
-  </si>
-  <si>
     <t>RE-601062</t>
   </si>
   <si>
@@ -663,24 +654,15 @@
     <t>OS Nº 5903 - GOLD</t>
   </si>
   <si>
-    <t>5903</t>
-  </si>
-  <si>
     <t>REDUTOR VÁLVULA ROTATIVA 6 - CSC 2</t>
   </si>
   <si>
     <t>OS Nº 5898 - GOLD</t>
   </si>
   <si>
-    <t>5898</t>
-  </si>
-  <si>
     <t>OS Nº 5924 - GOLD</t>
   </si>
   <si>
-    <t>5924</t>
-  </si>
-  <si>
     <t>RE- 601068</t>
   </si>
   <si>
@@ -690,17 +672,146 @@
     <t>OS Nº 5936 - GOLD</t>
   </si>
   <si>
-    <t>5936</t>
-  </si>
-  <si>
     <t xml:space="preserve"> assets/pdf/lista-pecas-V07 -ROTATIVAS.pdf</t>
+  </si>
+  <si>
+    <t>ME - 601049</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> V58</t>
+  </si>
+  <si>
+    <t>MOTOR 3 CV 4 POLOS</t>
+  </si>
+  <si>
+    <t>REDUTOR ROSCA TRANSPORTADORA DE FULIGEM 3 - MULTICICLONE</t>
+  </si>
+  <si>
+    <t>OS Nº 6056 - GOLD</t>
+  </si>
+  <si>
+    <t>PENDENTE</t>
+  </si>
+  <si>
+    <t>ME - 601050</t>
+  </si>
+  <si>
+    <t>REDUTOR ROSCA TRANSPORTADORA DE FULIGEM 4 - MULTICICLONE</t>
+  </si>
+  <si>
+    <t>OS Nº 6040 - GOLD</t>
+  </si>
+  <si>
+    <t>ME - 601051</t>
+  </si>
+  <si>
+    <t>V58</t>
+  </si>
+  <si>
+    <t>REDUTOR ROSCA TRANSPORTADORA DE FULIGEM 5 - MULTICICLONE</t>
+  </si>
+  <si>
+    <t>OS Nº 6025 - GOLD</t>
+  </si>
+  <si>
+    <t>ME - 601052</t>
+  </si>
+  <si>
+    <t>REDUTOR ROSCA TRANSPORTADORA DE FULIGEM 6 - MULTICICLONE</t>
+  </si>
+  <si>
+    <t>OS Nº 6047 - GOLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/REDUTOR V58.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LISTA PROMEM.pdf</t>
+  </si>
+  <si>
+    <t>ME-601243</t>
+  </si>
+  <si>
+    <t>SEW</t>
+  </si>
+  <si>
+    <t>FA 77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	REDUTOR DA ROSCA TRANSPORTADORAS 02</t>
+  </si>
+  <si>
+    <t>OS Nº 5931 - GOLD</t>
+  </si>
+  <si>
+    <t>ME-601244</t>
+  </si>
+  <si>
+    <t>REDUTOR DA ROSCA TRANSPORTADORAS 03</t>
+  </si>
+  <si>
+    <t>OS Nº 5929 - GOLD</t>
+  </si>
+  <si>
+    <t>RE-601070</t>
+  </si>
+  <si>
+    <t>MOTOR 5 CV 4 POLOS SEW</t>
+  </si>
+  <si>
+    <t>REDUTOR VÁLVULA ROTATIVA 9 - CSC 5</t>
+  </si>
+  <si>
+    <t>OS Nº 5938 - GOLD</t>
+  </si>
+  <si>
+    <t>RE-601242</t>
+  </si>
+  <si>
+    <t>OS Nº 5962 - GOLD</t>
+  </si>
+  <si>
+    <t>MOTOR 20 CV 4 POLOS SEW</t>
+  </si>
+  <si>
+    <t>REDUTOR DA ROSCA TRANSPORTADORAS CINZAS 01 ALIMENTAÇÃO</t>
+  </si>
+  <si>
+    <t>OS Nº 6030 - GOLD</t>
+  </si>
+  <si>
+    <t>assets/img/FA77.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LISTA PÇS FA77.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/BOOK SEW.pdf</t>
+  </si>
+  <si>
+    <t>ME-601252</t>
+  </si>
+  <si>
+    <t>FA87</t>
+  </si>
+  <si>
+    <t>MOTOR 4 CV - 4 POLOS</t>
+  </si>
+  <si>
+    <t>REDUTOR DO MOTOR TRANSPORTADOR HELICOIDAL RETIRADA CINZAS PARA MOEGA CALDEIRA 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LISTA PÇS FA87.pdf</t>
+  </si>
+  <si>
+    <t>OS Nº 5934 - GOLD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -721,8 +832,13 @@
       <sz val="8"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -739,8 +855,26 @@
         <fgColor rgb="FFD4AF37"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -748,11 +882,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -766,33 +944,53 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -938,47 +1136,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:T42" headerRowDxfId="29" dataDxfId="28" totalsRowDxfId="27">
-  <autoFilter ref="A1:T42" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
-    <filterColumn colId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R46" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+  <autoFilter ref="A1:R46" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="1">
       <filters>
-        <filter val="Correia Transportadora - CT- 01"/>
-        <filter val="Correia Transportadora - CT- 02"/>
-        <filter val="Correia Transportadora - CT- 03"/>
-        <filter val="Correia Transportadora - CT- 04"/>
-        <filter val="Correia Transportadora - CT- 22"/>
-        <filter val="Correia Transportadora - CT- 23"/>
-        <filter val="Correia Transportadora - CT- 25"/>
-        <filter val="Correia Transportadora - CT-08"/>
-        <filter val="Correia Transportadora - CT-09"/>
-        <filter val="Correia Transportadora - CT-21"/>
-        <filter val="REDUTOR DA TRANSP. DE CORREIA TCD/48&quot; CT 26 (ME631517)"/>
+        <filter val="WEG CESTARI"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="V58"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="26"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="24">
+  <tableColumns count="18">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="21"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="19">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Certificado" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{7BF229F1-8AF5-4349-856B-C68DFF7DB7CD}" name="Coluna1" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{9CF6539B-87FB-401A-974C-86AFB904B9CB}" name="Coluna2" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Certificado" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1136,7 +1327,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T42"/>
+  <dimension ref="A1:R52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
@@ -1153,13 +1344,14 @@
     <col min="12" max="12" width="9.25" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.125" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="2.375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="9.125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="8.125" style="2" customWidth="1"/>
     <col min="17" max="17" width="20.125" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="32" style="2" customWidth="1"/>
     <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="24" customHeight="1">
+    <row r="1" spans="1:18" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1214,14 +1406,8 @@
       <c r="R1" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="S1" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="57">
+    </row>
+    <row r="2" spans="1:18" ht="57" hidden="1">
       <c r="A2" s="3" t="s">
         <v>39</v>
       </c>
@@ -1273,10 +1459,8 @@
       <c r="R2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-    </row>
-    <row r="3" spans="1:20" ht="57">
+    </row>
+    <row r="3" spans="1:18" ht="57" hidden="1">
       <c r="A3" s="3" t="s">
         <v>40</v>
       </c>
@@ -1328,10 +1512,8 @@
       <c r="R3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-    </row>
-    <row r="4" spans="1:20" ht="57">
+    </row>
+    <row r="4" spans="1:18" ht="57" hidden="1">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -1383,10 +1565,8 @@
       <c r="R4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-    </row>
-    <row r="5" spans="1:20" ht="57">
+    </row>
+    <row r="5" spans="1:18" ht="57" hidden="1">
       <c r="A5" s="3" t="s">
         <v>42</v>
       </c>
@@ -1438,10 +1618,8 @@
       <c r="R5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-    </row>
-    <row r="6" spans="1:20" ht="57">
+    </row>
+    <row r="6" spans="1:18" ht="57" hidden="1">
       <c r="A6" s="3" t="s">
         <v>43</v>
       </c>
@@ -1493,10 +1671,8 @@
       <c r="R6" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-    </row>
-    <row r="7" spans="1:20" ht="57">
+    </row>
+    <row r="7" spans="1:18" ht="57" hidden="1">
       <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
@@ -1548,10 +1724,8 @@
       <c r="R7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-    </row>
-    <row r="8" spans="1:20" ht="57">
+    </row>
+    <row r="8" spans="1:18" ht="57" hidden="1">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
@@ -1603,10 +1777,8 @@
       <c r="R8" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-    </row>
-    <row r="9" spans="1:20" ht="57">
+    </row>
+    <row r="9" spans="1:18" ht="57" hidden="1">
       <c r="A9" s="3" t="s">
         <v>46</v>
       </c>
@@ -1658,10 +1830,8 @@
       <c r="R9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-    </row>
-    <row r="10" spans="1:20" ht="57">
+    </row>
+    <row r="10" spans="1:18" ht="57" hidden="1">
       <c r="A10" s="3" t="s">
         <v>82</v>
       </c>
@@ -1713,10 +1883,8 @@
       <c r="R10" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-    </row>
-    <row r="11" spans="1:20" ht="57">
+    </row>
+    <row r="11" spans="1:18" ht="57" hidden="1">
       <c r="A11" s="3" t="s">
         <v>87</v>
       </c>
@@ -1768,10 +1936,8 @@
       <c r="R11" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" ht="57" hidden="1">
+    </row>
+    <row r="12" spans="1:18" ht="57" hidden="1">
       <c r="A12" s="3" t="s">
         <v>100</v>
       </c>
@@ -1823,10 +1989,8 @@
       <c r="R12" s="2">
         <v>4388707</v>
       </c>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-    </row>
-    <row r="13" spans="1:20" ht="57" hidden="1">
+    </row>
+    <row r="13" spans="1:18" ht="57" hidden="1">
       <c r="A13" s="3" t="s">
         <v>101</v>
       </c>
@@ -1878,10 +2042,8 @@
       <c r="R13" s="2">
         <v>4388753</v>
       </c>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-    </row>
-    <row r="14" spans="1:20" ht="57" hidden="1">
+    </row>
+    <row r="14" spans="1:18" ht="57" hidden="1">
       <c r="A14" s="3" t="s">
         <v>102</v>
       </c>
@@ -1933,10 +2095,8 @@
       <c r="R14" s="2">
         <v>4388779</v>
       </c>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-    </row>
-    <row r="15" spans="1:20" ht="57" hidden="1">
+    </row>
+    <row r="15" spans="1:18" ht="57" hidden="1">
       <c r="A15" s="3" t="s">
         <v>103</v>
       </c>
@@ -1988,10 +2148,8 @@
       <c r="R15" s="2">
         <v>4388718</v>
       </c>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-    </row>
-    <row r="16" spans="1:20" ht="57" hidden="1">
+    </row>
+    <row r="16" spans="1:18" ht="57" hidden="1">
       <c r="A16" s="3" t="s">
         <v>104</v>
       </c>
@@ -2043,10 +2201,8 @@
       <c r="R16" s="2">
         <v>4388775</v>
       </c>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="1:20" ht="57" hidden="1">
+    </row>
+    <row r="17" spans="1:18" ht="57" hidden="1">
       <c r="A17" s="3" t="s">
         <v>105</v>
       </c>
@@ -2098,10 +2254,8 @@
       <c r="R17" s="2">
         <v>4388796</v>
       </c>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-    </row>
-    <row r="18" spans="1:20" ht="57" hidden="1">
+    </row>
+    <row r="18" spans="1:18" ht="57" hidden="1">
       <c r="A18" s="3" t="s">
         <v>106</v>
       </c>
@@ -2153,10 +2307,8 @@
       <c r="R18" s="2">
         <v>4390658</v>
       </c>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-    </row>
-    <row r="19" spans="1:20" ht="57" hidden="1">
+    </row>
+    <row r="19" spans="1:18" ht="57" hidden="1">
       <c r="A19" s="3" t="s">
         <v>107</v>
       </c>
@@ -2208,10 +2360,8 @@
       <c r="R19" s="2">
         <v>4388728</v>
       </c>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="1:20" ht="57" hidden="1">
+    </row>
+    <row r="20" spans="1:18" ht="57" hidden="1">
       <c r="A20" s="3" t="s">
         <v>108</v>
       </c>
@@ -2263,10 +2413,8 @@
       <c r="R20" s="2">
         <v>4388722</v>
       </c>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-    </row>
-    <row r="21" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="21" spans="1:18" ht="71.25" hidden="1">
       <c r="A21" s="3" t="s">
         <v>173</v>
       </c>
@@ -2304,7 +2452,9 @@
       <c r="L21" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M21" s="3"/>
+      <c r="M21" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -2314,10 +2464,8 @@
       <c r="R21" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-    </row>
-    <row r="22" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="22" spans="1:18" ht="85.5" hidden="1">
       <c r="A22" s="3" t="s">
         <v>174</v>
       </c>
@@ -2355,7 +2503,9 @@
       <c r="L22" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M22" s="3"/>
+      <c r="M22" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -2365,10 +2515,8 @@
       <c r="R22" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-    </row>
-    <row r="23" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="23" spans="1:18" ht="71.25" hidden="1">
       <c r="A23" s="3" t="s">
         <v>175</v>
       </c>
@@ -2406,7 +2554,9 @@
       <c r="L23" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M23" s="3"/>
+      <c r="M23" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -2416,10 +2566,8 @@
       <c r="R23" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-    </row>
-    <row r="24" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="24" spans="1:18" ht="71.25" hidden="1">
       <c r="A24" s="3" t="s">
         <v>176</v>
       </c>
@@ -2457,7 +2605,9 @@
       <c r="L24" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M24" s="3"/>
+      <c r="M24" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -2467,10 +2617,8 @@
       <c r="R24" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-    </row>
-    <row r="25" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="25" spans="1:18" ht="85.5" hidden="1">
       <c r="A25" s="3" t="s">
         <v>177</v>
       </c>
@@ -2508,7 +2656,9 @@
       <c r="L25" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M25" s="3"/>
+      <c r="M25" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
@@ -2518,10 +2668,8 @@
       <c r="R25" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-    </row>
-    <row r="26" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="26" spans="1:18" ht="71.25" hidden="1">
       <c r="A26" s="3" t="s">
         <v>178</v>
       </c>
@@ -2559,7 +2707,9 @@
       <c r="L26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M26" s="3"/>
+      <c r="M26" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -2569,10 +2719,8 @@
       <c r="R26" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-    </row>
-    <row r="27" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="27" spans="1:18" ht="71.25" hidden="1">
       <c r="A27" s="3" t="s">
         <v>179</v>
       </c>
@@ -2610,7 +2758,9 @@
       <c r="L27" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M27" s="3"/>
+      <c r="M27" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -2620,10 +2770,8 @@
       <c r="R27" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-    </row>
-    <row r="28" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="28" spans="1:18" ht="71.25" hidden="1">
       <c r="A28" s="3" t="s">
         <v>180</v>
       </c>
@@ -2661,7 +2809,9 @@
       <c r="L28" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M28" s="3"/>
+      <c r="M28" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -2671,10 +2821,8 @@
       <c r="R28" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-    </row>
-    <row r="29" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="29" spans="1:18" ht="71.25" hidden="1">
       <c r="A29" s="3" t="s">
         <v>181</v>
       </c>
@@ -2712,7 +2860,9 @@
       <c r="L29" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M29" s="3"/>
+      <c r="M29" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -2722,10 +2872,8 @@
       <c r="R29" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
-    </row>
-    <row r="30" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="30" spans="1:18" ht="71.25" hidden="1">
       <c r="A30" s="3" t="s">
         <v>182</v>
       </c>
@@ -2763,7 +2911,9 @@
       <c r="L30" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M30" s="3"/>
+      <c r="M30" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -2773,10 +2923,8 @@
       <c r="R30" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S30" s="3"/>
-      <c r="T30" s="3"/>
-    </row>
-    <row r="31" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="31" spans="1:18" ht="71.25" hidden="1">
       <c r="A31" s="3" t="s">
         <v>183</v>
       </c>
@@ -2814,7 +2962,9 @@
       <c r="L31" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M31" s="3"/>
+      <c r="M31" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
@@ -2824,10 +2974,8 @@
       <c r="R31" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
-    </row>
-    <row r="32" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="32" spans="1:18" ht="71.25" hidden="1">
       <c r="A32" s="3" t="s">
         <v>184</v>
       </c>
@@ -2865,7 +3013,9 @@
       <c r="L32" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M32" s="3"/>
+      <c r="M32" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -2875,10 +3025,8 @@
       <c r="R32" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
-    </row>
-    <row r="33" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="33" spans="1:18" ht="71.25" hidden="1">
       <c r="A33" s="3" t="s">
         <v>185</v>
       </c>
@@ -2916,7 +3064,9 @@
       <c r="L33" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M33" s="3"/>
+      <c r="M33" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
@@ -2926,10 +3076,8 @@
       <c r="R33" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
-    </row>
-    <row r="34" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="34" spans="1:18" ht="71.25" hidden="1">
       <c r="A34" s="3" t="s">
         <v>186</v>
       </c>
@@ -2967,7 +3115,9 @@
       <c r="L34" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M34" s="3"/>
+      <c r="M34" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
@@ -2977,10 +3127,8 @@
       <c r="R34" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
-    </row>
-    <row r="35" spans="1:20" ht="71.25" hidden="1">
+    </row>
+    <row r="35" spans="1:18" ht="71.25" hidden="1">
       <c r="A35" s="3" t="s">
         <v>187</v>
       </c>
@@ -3018,7 +3166,9 @@
       <c r="L35" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M35" s="3"/>
+      <c r="M35" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
@@ -3028,10 +3178,8 @@
       <c r="R35" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
-    </row>
-    <row r="36" spans="1:20" ht="85.5" hidden="1">
+    </row>
+    <row r="36" spans="1:18" ht="85.5" hidden="1">
       <c r="A36" s="3" t="s">
         <v>188</v>
       </c>
@@ -3069,7 +3217,9 @@
       <c r="L36" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="M36" s="3"/>
+      <c r="M36" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
@@ -3079,10 +3229,8 @@
       <c r="R36" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-    </row>
-    <row r="37" spans="1:20" ht="85.5">
+    </row>
+    <row r="37" spans="1:18" ht="85.5" hidden="1">
       <c r="A37" s="3" t="s">
         <v>189</v>
       </c>
@@ -3133,10 +3281,8 @@
       <c r="R37" s="2">
         <v>5876</v>
       </c>
-      <c r="S37" s="3"/>
-      <c r="T37" s="3"/>
-    </row>
-    <row r="38" spans="1:20" ht="85.5">
+    </row>
+    <row r="38" spans="1:18" ht="57" hidden="1">
       <c r="A38" s="3" t="s">
         <v>194</v>
       </c>
@@ -3174,7 +3320,7 @@
         <v>99</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="N38" s="3" t="s">
         <v>38</v>
@@ -3189,14 +3335,10 @@
       <c r="R38" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="S38" s="3"/>
-      <c r="T38" s="3" t="s">
+    </row>
+    <row r="39" spans="1:18" ht="57" hidden="1">
+      <c r="A39" s="3" t="s">
         <v>200</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="85.5">
-      <c r="A39" s="3" t="s">
-        <v>203</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>36</v>
@@ -3226,13 +3368,13 @@
         <v>5.75</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>99</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="N39" s="3" t="s">
         <v>38</v>
@@ -3242,19 +3384,15 @@
       </c>
       <c r="P39" s="3"/>
       <c r="Q39" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="R39" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="S39" s="3"/>
-      <c r="T39" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" ht="85.5">
+    </row>
+    <row r="40" spans="1:18" ht="57" hidden="1">
       <c r="A40" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>36</v>
@@ -3284,13 +3422,13 @@
         <v>5.75</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>99</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>38</v>
@@ -3300,19 +3438,15 @@
       </c>
       <c r="P40" s="3"/>
       <c r="Q40" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="R40" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" ht="85.5">
+    </row>
+    <row r="41" spans="1:18" ht="57" hidden="1">
       <c r="A41" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>36</v>
@@ -3348,7 +3482,7 @@
         <v>99</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>38</v>
@@ -3358,19 +3492,15 @@
       </c>
       <c r="P41" s="3"/>
       <c r="Q41" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="R41" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" ht="85.5">
+    </row>
+    <row r="42" spans="1:18" ht="57" hidden="1">
       <c r="A42" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>36</v>
@@ -3400,13 +3530,13 @@
         <v>5.75</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>99</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>38</v>
@@ -3416,26 +3546,521 @@
       </c>
       <c r="P42" s="3"/>
       <c r="Q42" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="R42" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="S42" s="3"/>
-      <c r="T42" s="3" t="s">
+    </row>
+    <row r="43" spans="1:18" ht="85.5">
+      <c r="A43" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F43" s="5">
+        <v>118.3</v>
+      </c>
+      <c r="G43" s="5">
+        <v>1750</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J43" s="5">
+        <v>9</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="N43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="R43" s="10" t="s">
         <v>217</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="85.5">
+      <c r="A44" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="F44" s="7">
+        <v>118.3</v>
+      </c>
+      <c r="G44" s="7">
+        <v>1750</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J44" s="7">
+        <v>9</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="N44" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="O44" s="7"/>
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="R44" s="11" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="85.5">
+      <c r="A45" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F45" s="5">
+        <v>118.3</v>
+      </c>
+      <c r="G45" s="5">
+        <v>1750</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J45" s="5">
+        <v>9</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="N45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="R45" s="10" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="85.5">
+      <c r="A46" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="F46" s="14">
+        <v>118.3</v>
+      </c>
+      <c r="G46" s="14">
+        <v>1750</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J46" s="14">
+        <v>9</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="L46" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="M46" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="N46" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="O46" s="14"/>
+      <c r="P46" s="14"/>
+      <c r="Q46" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="R46" s="16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="57">
+      <c r="A47" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="F47" s="18">
+        <v>72.5</v>
+      </c>
+      <c r="G47" s="18">
+        <v>1750</v>
+      </c>
+      <c r="H47" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="I47" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="J47" s="18">
+        <v>5.9</v>
+      </c>
+      <c r="K47" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="M47" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="N47" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="O47" s="18"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="R47" s="18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="57">
+      <c r="A48" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="F48" s="18">
+        <v>72.5</v>
+      </c>
+      <c r="G48" s="18">
+        <v>1750</v>
+      </c>
+      <c r="H48" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="I48" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="J48" s="18">
+        <v>5.9</v>
+      </c>
+      <c r="K48" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="L48" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="N48" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="O48" s="18"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="R48" s="18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="57">
+      <c r="A49" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="J49" s="18">
+        <v>5.9</v>
+      </c>
+      <c r="K49" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="L49" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="N49" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="O49" s="18"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="R49" s="18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="57">
+      <c r="A50" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="J50" s="18">
+        <v>5.9</v>
+      </c>
+      <c r="K50" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="L50" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="N50" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="O50" s="18"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="R50" s="18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="71.25">
+      <c r="A51" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="F51" s="18">
+        <v>15.64</v>
+      </c>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51" s="18">
+        <v>5.9</v>
+      </c>
+      <c r="K51" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="N51" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="O51" s="18"/>
+      <c r="P51" s="18"/>
+      <c r="Q51" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="R51" s="18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="114">
+      <c r="A52" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F52" s="7">
+        <v>97.89</v>
+      </c>
+      <c r="G52" s="7">
+        <v>1752</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J52" s="7">
+        <v>11</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="L52" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q52" s="7" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B43:B1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+  <conditionalFormatting sqref="B53:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R42">
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+  <conditionalFormatting sqref="R2:R46">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0427CB-294B-4CDA-90C6-7EC175356F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8697E200-3190-40C0-AD30-7902FCDF0B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="265">
   <si>
     <t>TAG</t>
   </si>
@@ -81,9 +81,6 @@
     <t>Manual</t>
   </si>
   <si>
-    <t>Certificado</t>
-  </si>
-  <si>
     <t>Fotos_Adicionais</t>
   </si>
   <si>
@@ -198,36 +195,24 @@
     <t>OS Nº 5863 - GOLD</t>
   </si>
   <si>
-    <t>5863</t>
-  </si>
-  <si>
     <t>Correia Transportadora - CT- 02</t>
   </si>
   <si>
     <t>OS Nº 5874 - GOLD</t>
   </si>
   <si>
-    <t>5874</t>
-  </si>
-  <si>
     <t>Correia Transportadora - CT- 03</t>
   </si>
   <si>
     <t>OS Nº 5880 - GOLD</t>
   </si>
   <si>
-    <t>5880</t>
-  </si>
-  <si>
     <t>Correia Transportadora - CT- 04</t>
   </si>
   <si>
     <t>OS Nº 5882 - GOLD</t>
   </si>
   <si>
-    <t>5882</t>
-  </si>
-  <si>
     <t xml:space="preserve">WCG20 - V/F12 </t>
   </si>
   <si>
@@ -243,18 +228,12 @@
     <t>OS Nº 5865 - GOLD</t>
   </si>
   <si>
-    <t>5865</t>
-  </si>
-  <si>
     <t>Correia Transportadora - CT-09</t>
   </si>
   <si>
     <t>OS Nº 5870 - GOLD</t>
   </si>
   <si>
-    <t>5870</t>
-  </si>
-  <si>
     <t>WCG20 F10 3</t>
   </si>
   <si>
@@ -267,9 +246,6 @@
     <t>OS Nº 5878 - GOLD</t>
   </si>
   <si>
-    <t>5878</t>
-  </si>
-  <si>
     <t>WCG20 V/F12 3</t>
   </si>
   <si>
@@ -282,9 +258,6 @@
     <t>OS Nº 5861 - GOLD</t>
   </si>
   <si>
-    <t>5861</t>
-  </si>
-  <si>
     <t>RE-631514</t>
   </si>
   <si>
@@ -297,9 +270,6 @@
     <t>OS Nº 5867 - GOLD</t>
   </si>
   <si>
-    <t>5867</t>
-  </si>
-  <si>
     <t>RE-631516</t>
   </si>
   <si>
@@ -309,9 +279,6 @@
     <t>OS Nº 5872 - GOLD</t>
   </si>
   <si>
-    <t>5872</t>
-  </si>
-  <si>
     <t>assets/img/CT-01.jpg</t>
   </si>
   <si>
@@ -462,9 +429,6 @@
     <t>OS Nº 5995 - GOLD</t>
   </si>
   <si>
-    <t>EM FASE DE CONCLUSÃO</t>
-  </si>
-  <si>
     <t>REDUTOR SOPRADOR DE FULIGEM RETRÁTIL SF-01 LD - SUPER SEC</t>
   </si>
   <si>
@@ -636,9 +600,6 @@
     <t>OS Nº 5920 - GOLD</t>
   </si>
   <si>
-    <t>CONCLUIDA</t>
-  </si>
-  <si>
     <t>RE-601062</t>
   </si>
   <si>
@@ -690,9 +651,6 @@
     <t>OS Nº 6056 - GOLD</t>
   </si>
   <si>
-    <t>PENDENTE</t>
-  </si>
-  <si>
     <t>ME - 601050</t>
   </si>
   <si>
@@ -805,6 +763,75 @@
   </si>
   <si>
     <t>OS Nº 5934 - GOLD</t>
+  </si>
+  <si>
+    <t>RELATORIO FINAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5874.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5874.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5863.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5863.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5880.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5880.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5882.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5882.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5865.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5865.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5870.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5870.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5878.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5878.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5861.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5861.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5867.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5867.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5872.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5872.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5876.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5876.pdf</t>
   </si>
 </sst>
 </file>
@@ -930,7 +957,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -941,13 +968,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -980,27 +1001,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1136,40 +1156,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R46" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
-  <autoFilter ref="A1:R46" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="WEG CESTARI"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="V58"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R52" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
+  <autoFilter ref="A1:R52" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="21"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="18">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Certificado" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1344,8 +1353,8 @@
     <col min="12" max="12" width="9.25" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.125" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="8.125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="11.875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="10.625" style="2" customWidth="1"/>
     <col min="17" max="17" width="20.125" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="32" style="2" customWidth="1"/>
     <col min="19" max="16384" width="9" style="2"/>
@@ -1395,34 +1404,34 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="R1" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="57" hidden="1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="71.25">
       <c r="A2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="F2" s="3">
         <v>41.4</v>
@@ -1431,51 +1440,52 @@
         <v>1750</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="O2" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="57" hidden="1">
+    </row>
+    <row r="3" spans="1:18" ht="71.25">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="F3" s="3">
         <v>41.4</v>
@@ -1484,51 +1494,52 @@
         <v>1750</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="K3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
+      <c r="O3" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="Q3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="57" hidden="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="57">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="F4" s="3">
         <v>41.4</v>
@@ -1537,51 +1548,52 @@
         <v>1750</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="K4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
+      <c r="O4" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>248</v>
+      </c>
       <c r="Q4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="57" hidden="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="57">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="F5" s="3">
         <v>41.4</v>
@@ -1590,51 +1602,52 @@
         <v>1750</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="K5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
+      <c r="O5" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="Q5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="57" hidden="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="57">
       <c r="A6" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F6" s="3">
         <v>43.65</v>
@@ -1643,51 +1656,52 @@
         <v>1750</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
+      <c r="O6" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="Q6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="57" hidden="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="57">
       <c r="A7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F7" s="3">
         <v>43.65</v>
@@ -1696,51 +1710,52 @@
         <v>1750</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
+      <c r="O7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>254</v>
+      </c>
       <c r="Q7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="57" hidden="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="57">
       <c r="A8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F8" s="3">
         <v>41.4</v>
@@ -1749,51 +1764,52 @@
         <v>1750</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="K8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
+      <c r="O8" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>256</v>
+      </c>
       <c r="Q8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="57" hidden="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="57">
       <c r="A9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F9" s="3">
         <v>43.65</v>
@@ -1802,51 +1818,52 @@
         <v>1750</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
+      <c r="O9" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>258</v>
+      </c>
       <c r="Q9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="57" hidden="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="57">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3">
         <v>43.65</v>
@@ -1855,51 +1872,52 @@
         <v>1750</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
+      <c r="O10" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>260</v>
+      </c>
       <c r="Q10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="57" hidden="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="57">
       <c r="A11" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F11" s="3">
         <v>41.4</v>
@@ -1908,51 +1926,52 @@
         <v>1750</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="K11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="N11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
+      <c r="O11" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="Q11" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="57">
+      <c r="A12" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="R11" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="57" hidden="1">
-      <c r="A12" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="B12" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F12" s="3">
         <v>180.35</v>
@@ -1961,51 +1980,48 @@
         <v>1750</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="R12" s="2">
-        <v>4388707</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="57" hidden="1">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="57">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F13" s="3">
         <v>180.35</v>
@@ -2014,51 +2030,48 @@
         <v>1750</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="R13" s="2">
-        <v>4388753</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="57" hidden="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="57">
       <c r="A14" s="3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F14" s="3">
         <v>180.35</v>
@@ -2067,51 +2080,48 @@
         <v>1750</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="R14" s="2">
-        <v>4388779</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="57" hidden="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="57">
       <c r="A15" s="3" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F15" s="3">
         <v>180.35</v>
@@ -2120,51 +2130,48 @@
         <v>1750</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="R15" s="2">
-        <v>4388718</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="57" hidden="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="57">
       <c r="A16" s="3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F16" s="3">
         <v>180.35</v>
@@ -2173,51 +2180,48 @@
         <v>1750</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="R16" s="2">
-        <v>4388775</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="57" hidden="1">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="57">
       <c r="A17" s="3" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F17" s="3">
         <v>180.35</v>
@@ -2226,51 +2230,48 @@
         <v>1750</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="R17" s="2">
-        <v>4388796</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="57" hidden="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="57">
       <c r="A18" s="3" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F18" s="3">
         <v>180.35</v>
@@ -2279,51 +2280,48 @@
         <v>1750</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="L18" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="R18" s="2">
-        <v>4390658</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="57" hidden="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="57">
       <c r="A19" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F19" s="3">
         <v>180.35</v>
@@ -2332,51 +2330,48 @@
         <v>1750</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="L19" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="R19" s="2">
-        <v>4388728</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="57" hidden="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="57">
       <c r="A20" s="3" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F20" s="3">
         <v>180.35</v>
@@ -2385,60 +2380,57 @@
         <v>1750</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="R20" s="2">
-        <v>4388722</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="71.25" hidden="1">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="71.25">
       <c r="A21" s="3" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C21" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G21" s="3">
         <v>1725</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I21" s="3">
         <v>220</v>
@@ -2447,49 +2439,46 @@
         <v>2</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="85.5" hidden="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="71.25">
       <c r="A22" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C22" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G22" s="3">
         <v>1725</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I22" s="3">
         <v>220</v>
@@ -2498,49 +2487,46 @@
         <v>2</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="71.25" hidden="1">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="71.25">
       <c r="A23" s="3" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C23" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G23" s="3">
         <v>1725</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I23" s="3">
         <v>220</v>
@@ -2549,49 +2535,46 @@
         <v>2</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="71.25" hidden="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="71.25">
       <c r="A24" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C24" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3">
         <v>1725</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I24" s="3">
         <v>220</v>
@@ -2600,49 +2583,46 @@
         <v>2</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="85.5" hidden="1">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="71.25">
       <c r="A25" s="3" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C25" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G25" s="3">
         <v>1725</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I25" s="3">
         <v>220</v>
@@ -2651,49 +2631,46 @@
         <v>2</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="71.25" hidden="1">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="71.25">
       <c r="A26" s="3" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C26" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G26" s="3">
         <v>1725</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I26" s="3">
         <v>220</v>
@@ -2702,49 +2679,46 @@
         <v>2</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="71.25" hidden="1">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="71.25">
       <c r="A27" s="3" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C27" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G27" s="3">
         <v>1725</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I27" s="3">
         <v>220</v>
@@ -2753,49 +2727,46 @@
         <v>2</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="R27" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="71.25" hidden="1">
+    <row r="28" spans="1:17" ht="71.25">
       <c r="A28" s="3" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C28" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G28" s="3">
         <v>1725</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I28" s="3">
         <v>220</v>
@@ -2804,49 +2775,46 @@
         <v>2</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="71.25" hidden="1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="71.25">
       <c r="A29" s="3" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C29" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G29" s="3">
         <v>1725</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I29" s="3">
         <v>220</v>
@@ -2855,49 +2823,46 @@
         <v>2</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="R29" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="71.25" hidden="1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="71.25">
       <c r="A30" s="3" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C30" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G30" s="3">
         <v>1725</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I30" s="3">
         <v>220</v>
@@ -2906,49 +2871,46 @@
         <v>2</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="71.25" hidden="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="71.25">
       <c r="A31" s="3" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C31" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G31" s="3">
         <v>1725</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I31" s="3">
         <v>220</v>
@@ -2957,49 +2919,46 @@
         <v>2</v>
       </c>
       <c r="K31" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="L31" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="M31" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="71.25" hidden="1">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="71.25">
       <c r="A32" s="3" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C32" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G32" s="3">
         <v>1725</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I32" s="3">
         <v>220</v>
@@ -3008,49 +2967,46 @@
         <v>2</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="R32" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="71.25" hidden="1">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="71.25">
       <c r="A33" s="3" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C33" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G33" s="3">
         <v>1725</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I33" s="3">
         <v>220</v>
@@ -3059,49 +3015,46 @@
         <v>2</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
       <c r="Q33" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="R33" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="71.25" hidden="1">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="71.25">
       <c r="A34" s="3" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C34" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G34" s="3">
         <v>1725</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I34" s="3">
         <v>220</v>
@@ -3110,49 +3063,46 @@
         <v>2</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="R34" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="71.25" hidden="1">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="71.25">
       <c r="A35" s="3" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C35" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G35" s="3">
         <v>1725</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I35" s="3">
         <v>220</v>
@@ -3161,49 +3111,46 @@
         <v>2</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
       <c r="Q35" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="85.5" hidden="1">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="85.5">
       <c r="A36" s="3" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C36" s="3" t="str">
         <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
         <v>MOTOREDUTOR PROMOEN</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G36" s="3">
         <v>1725</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I36" s="3">
         <v>220</v>
@@ -3212,91 +3159,89 @@
         <v>2</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
       <c r="Q36" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="R36" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="85.5" hidden="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="85.5">
       <c r="A37" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G37" s="3">
         <v>1750</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J37" s="3">
         <v>20</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>264</v>
+      </c>
       <c r="Q37" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="R37" s="2">
-        <v>5876</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="57" hidden="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="57">
       <c r="A38" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F38" s="3">
         <v>151</v>
@@ -3305,52 +3250,47 @@
         <v>1720</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J38" s="3">
         <v>5.75</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O38" s="3">
-        <v>928373</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="O38" s="3"/>
       <c r="P38" s="3"/>
       <c r="Q38" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="57" hidden="1">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="57">
       <c r="A39" s="3" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F39" s="3">
         <v>151</v>
@@ -3359,52 +3299,47 @@
         <v>1720</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J39" s="3">
         <v>5.75</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O39" s="3">
-        <v>928875</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="R39" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="57" hidden="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="57">
       <c r="A40" s="3" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F40" s="3">
         <v>151</v>
@@ -3413,52 +3348,47 @@
         <v>1720</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J40" s="3">
         <v>5.75</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O40" s="3">
-        <v>928369</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="R40" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" ht="57" hidden="1">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="57">
       <c r="A41" s="3" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F41" s="3">
         <v>151</v>
@@ -3467,52 +3397,47 @@
         <v>1720</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J41" s="3">
         <v>5.75</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O41" s="3">
-        <v>928374</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="O41" s="3"/>
       <c r="P41" s="3"/>
       <c r="Q41" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="R41" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="57" hidden="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="57">
       <c r="A42" s="3" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F42" s="3">
         <v>151</v>
@@ -3521,535 +3446,515 @@
         <v>1720</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J42" s="3">
         <v>5.75</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O42" s="3">
-        <v>928371</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="O42" s="3"/>
       <c r="P42" s="3"/>
       <c r="Q42" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="85.5">
+      <c r="A43" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F43" s="4">
+        <v>118.3</v>
+      </c>
+      <c r="G43" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J43" s="4">
+        <v>9</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="R43" s="8"/>
+    </row>
+    <row r="44" spans="1:18" ht="85.5">
+      <c r="A44" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F44" s="5">
+        <v>118.3</v>
+      </c>
+      <c r="G44" s="5">
+        <v>1750</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J44" s="5">
+        <v>9</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="N44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="R44" s="9"/>
+    </row>
+    <row r="45" spans="1:18" ht="85.5">
+      <c r="A45" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F45" s="4">
+        <v>118.3</v>
+      </c>
+      <c r="G45" s="4">
+        <v>1750</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J45" s="4">
+        <v>9</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="R42" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="85.5">
-      <c r="A43" s="8" t="s">
+      <c r="R45" s="8"/>
+    </row>
+    <row r="46" spans="1:18" ht="85.5">
+      <c r="A46" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F46" s="12">
+        <v>118.3</v>
+      </c>
+      <c r="G46" s="12">
+        <v>1750</v>
+      </c>
+      <c r="H46" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J46" s="12">
+        <v>9</v>
+      </c>
+      <c r="K46" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="L46" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="M46" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O46" s="12"/>
+      <c r="P46" s="12"/>
+      <c r="Q46" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="R46" s="14"/>
+    </row>
+    <row r="47" spans="1:18" ht="57">
+      <c r="A47" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="F47" s="15">
+        <v>72.5</v>
+      </c>
+      <c r="G47" s="15">
+        <v>1750</v>
+      </c>
+      <c r="H47" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="I47" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="F43" s="5">
-        <v>118.3</v>
-      </c>
-      <c r="G43" s="5">
+      <c r="J47" s="15">
+        <v>5.9</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O47" s="15"/>
+      <c r="P47" s="15"/>
+      <c r="Q47" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="R47" s="16"/>
+    </row>
+    <row r="48" spans="1:18" ht="57">
+      <c r="A48" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="F48" s="15">
+        <v>72.5</v>
+      </c>
+      <c r="G48" s="15">
         <v>1750</v>
       </c>
-      <c r="H43" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J43" s="5">
-        <v>9</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="L43" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="M43" s="5" t="s">
+      <c r="H48" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="I48" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="J48" s="15">
+        <v>5.9</v>
+      </c>
+      <c r="K48" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O48" s="15"/>
+      <c r="P48" s="15"/>
+      <c r="Q48" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="R48" s="16"/>
+    </row>
+    <row r="49" spans="1:18" ht="57">
+      <c r="A49" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="J49" s="15">
+        <v>5.9</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="R49" s="16"/>
+    </row>
+    <row r="50" spans="1:18" ht="57">
+      <c r="A50" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="N43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="R43" s="10" t="s">
+      <c r="B50" s="7" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" ht="85.5">
-      <c r="A44" s="8" t="s">
+      <c r="C50" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D50" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="E50" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="F44" s="7">
-        <v>118.3</v>
-      </c>
-      <c r="G44" s="7">
-        <v>1750</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J44" s="7">
-        <v>9</v>
-      </c>
-      <c r="K44" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="L44" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="M44" s="5" t="s">
+      <c r="J50" s="15">
+        <v>5.9</v>
+      </c>
+      <c r="K50" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O50" s="15"/>
+      <c r="P50" s="15"/>
+      <c r="Q50" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="R50" s="16"/>
+    </row>
+    <row r="51" spans="1:18" ht="71.25">
+      <c r="A51" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="N44" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="O44" s="7"/>
-      <c r="P44" s="7"/>
-      <c r="Q44" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="R44" s="11" t="s">
+      <c r="B51" s="7" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" ht="85.5">
-      <c r="A45" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="B45" s="9" t="s">
+      <c r="C51" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="F51" s="15">
+        <v>15.64</v>
+      </c>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="F45" s="5">
-        <v>118.3</v>
-      </c>
-      <c r="G45" s="5">
-        <v>1750</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J45" s="5">
-        <v>9</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="L45" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="M45" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="N45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O45" s="5"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="R45" s="10" t="s">
+      <c r="J51" s="15">
+        <v>5.9</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O51" s="15"/>
+      <c r="P51" s="15"/>
+      <c r="Q51" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="R51" s="16"/>
+    </row>
+    <row r="52" spans="1:18" ht="114">
+      <c r="A52" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B52" s="11" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" ht="85.5">
-      <c r="A46" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="B46" s="13" t="s">
+      <c r="C52" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="F52" s="12">
+        <v>97.89</v>
+      </c>
+      <c r="G52" s="12">
+        <v>1752</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="I52" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C46" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="F46" s="14">
-        <v>118.3</v>
-      </c>
-      <c r="G46" s="14">
-        <v>1750</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="I46" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J46" s="14">
-        <v>9</v>
-      </c>
-      <c r="K46" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="L46" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="M46" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="N46" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="O46" s="14"/>
-      <c r="P46" s="14"/>
-      <c r="Q46" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="R46" s="16" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="57">
-      <c r="A47" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="B47" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="C47" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="F47" s="18">
-        <v>72.5</v>
-      </c>
-      <c r="G47" s="18">
-        <v>1750</v>
-      </c>
-      <c r="H47" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="I47" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="J47" s="18">
-        <v>5.9</v>
-      </c>
-      <c r="K47" s="18" t="s">
+      <c r="J52" s="12">
+        <v>11</v>
+      </c>
+      <c r="K52" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="L52" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="L47" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="M47" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="N47" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="O47" s="18"/>
-      <c r="P47" s="18"/>
-      <c r="Q47" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="R47" s="18" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="57">
-      <c r="A48" s="17" t="s">
+      <c r="M52" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="N52" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="B48" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="C48" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="F48" s="18">
-        <v>72.5</v>
-      </c>
-      <c r="G48" s="18">
-        <v>1750</v>
-      </c>
-      <c r="H48" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="I48" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="J48" s="18">
-        <v>5.9</v>
-      </c>
-      <c r="K48" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="L48" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="M48" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="N48" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="O48" s="18"/>
-      <c r="P48" s="18"/>
-      <c r="Q48" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="R48" s="18" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" ht="57">
-      <c r="A49" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="B49" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="C49" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="D49" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="J49" s="18">
-        <v>5.9</v>
-      </c>
-      <c r="K49" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="L49" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="M49" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="N49" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="O49" s="18"/>
-      <c r="P49" s="18"/>
-      <c r="Q49" s="18" t="s">
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="R49" s="18" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" ht="57">
-      <c r="A50" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18"/>
-      <c r="I50" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="J50" s="18">
-        <v>5.9</v>
-      </c>
-      <c r="K50" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="L50" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="M50" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="N50" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="O50" s="18"/>
-      <c r="P50" s="18"/>
-      <c r="Q50" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="R50" s="18" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="71.25">
-      <c r="A51" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="B51" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="C51" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="D51" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="E51" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="F51" s="18">
-        <v>15.64</v>
-      </c>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="I51" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="J51" s="18">
-        <v>5.9</v>
-      </c>
-      <c r="K51" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="L51" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="M51" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="N51" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="O51" s="18"/>
-      <c r="P51" s="18"/>
-      <c r="Q51" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="R51" s="18" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" ht="114">
-      <c r="A52" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="F52" s="7">
-        <v>97.89</v>
-      </c>
-      <c r="G52" s="7">
-        <v>1752</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J52" s="7">
-        <v>11</v>
-      </c>
-      <c r="K52" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="L52" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="M52" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="N52" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q52" s="7" t="s">
-        <v>255</v>
-      </c>
+      <c r="R52" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -4059,7 +3964,7 @@
   <conditionalFormatting sqref="R1">
     <cfRule type="duplicateValues" dxfId="1" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R46">
+  <conditionalFormatting sqref="R2:R52">
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4080,83 +3985,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15">
-      <c r="A1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="4"/>
+      <c r="A1" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="19"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
         <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
         <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
         <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
         <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
         <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
         <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
         <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8697E200-3190-40C0-AD30-7902FCDF0B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E7A630-A5C6-459B-BDB8-C530B7E38144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="283">
   <si>
     <t>TAG</t>
   </si>
@@ -832,6 +832,60 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/OS5876.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5900.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5900.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5922.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5922.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5942.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5942.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5894.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5894.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5852.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5852.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5946.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5946.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5904.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5904.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5913.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5913.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5941.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5941.pdf</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1211,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R52" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
-  <autoFilter ref="A1:R52" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+  <autoFilter ref="A1:R52" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="C10 - 3"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="20"/>
     <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="19"/>
@@ -1416,7 +1476,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="71.25">
+    <row r="2" spans="1:18" ht="57" hidden="1">
       <c r="A2" s="3" t="s">
         <v>38</v>
       </c>
@@ -1470,7 +1530,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="71.25">
+    <row r="3" spans="1:18" ht="57" hidden="1">
       <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
@@ -1524,7 +1584,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="57">
+    <row r="4" spans="1:18" ht="57" hidden="1">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
@@ -1578,7 +1638,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="57">
+    <row r="5" spans="1:18" ht="57" hidden="1">
       <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
@@ -1632,7 +1692,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="57">
+    <row r="6" spans="1:18" ht="57" hidden="1">
       <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
@@ -1686,7 +1746,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="57">
+    <row r="7" spans="1:18" ht="57" hidden="1">
       <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
@@ -1740,7 +1800,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="57">
+    <row r="8" spans="1:18" ht="57" hidden="1">
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
@@ -1794,7 +1854,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="57">
+    <row r="9" spans="1:18" ht="57" hidden="1">
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
@@ -1848,7 +1908,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="57">
+    <row r="10" spans="1:18" ht="57" hidden="1">
       <c r="A10" s="3" t="s">
         <v>73</v>
       </c>
@@ -1902,7 +1962,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="57">
+    <row r="11" spans="1:18" ht="57" hidden="1">
       <c r="A11" s="3" t="s">
         <v>77</v>
       </c>
@@ -2000,8 +2060,12 @@
       <c r="N12" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
+      <c r="O12" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="Q12" s="3" t="s">
         <v>122</v>
       </c>
@@ -2050,8 +2114,12 @@
       <c r="N13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
+      <c r="O13" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>268</v>
+      </c>
       <c r="Q13" s="3" t="s">
         <v>114</v>
       </c>
@@ -2100,8 +2168,12 @@
       <c r="N14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
+      <c r="O14" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>270</v>
+      </c>
       <c r="Q14" s="3" t="s">
         <v>115</v>
       </c>
@@ -2150,8 +2222,12 @@
       <c r="N15" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
+      <c r="O15" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="Q15" s="3" t="s">
         <v>116</v>
       </c>
@@ -2200,8 +2276,12 @@
       <c r="N16" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
+      <c r="O16" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="Q16" s="3" t="s">
         <v>117</v>
       </c>
@@ -2250,8 +2330,12 @@
       <c r="N17" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
+      <c r="O17" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="Q17" s="3" t="s">
         <v>118</v>
       </c>
@@ -2300,8 +2384,12 @@
       <c r="N18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
+      <c r="O18" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>278</v>
+      </c>
       <c r="Q18" s="3" t="s">
         <v>119</v>
       </c>
@@ -2350,8 +2438,12 @@
       <c r="N19" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
+      <c r="O19" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>280</v>
+      </c>
       <c r="Q19" s="3" t="s">
         <v>120</v>
       </c>
@@ -2400,13 +2492,17 @@
       <c r="N20" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
+      <c r="O20" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>282</v>
+      </c>
       <c r="Q20" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="71.25">
+    <row r="21" spans="1:17" ht="71.25" hidden="1">
       <c r="A21" s="3" t="s">
         <v>161</v>
       </c>
@@ -2454,7 +2550,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="71.25">
+    <row r="22" spans="1:17" ht="71.25" hidden="1">
       <c r="A22" s="3" t="s">
         <v>162</v>
       </c>
@@ -2502,7 +2598,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="71.25">
+    <row r="23" spans="1:17" ht="71.25" hidden="1">
       <c r="A23" s="3" t="s">
         <v>163</v>
       </c>
@@ -2550,7 +2646,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="71.25">
+    <row r="24" spans="1:17" ht="71.25" hidden="1">
       <c r="A24" s="3" t="s">
         <v>164</v>
       </c>
@@ -2598,7 +2694,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="71.25">
+    <row r="25" spans="1:17" ht="71.25" hidden="1">
       <c r="A25" s="3" t="s">
         <v>165</v>
       </c>
@@ -2646,7 +2742,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="71.25">
+    <row r="26" spans="1:17" ht="71.25" hidden="1">
       <c r="A26" s="3" t="s">
         <v>166</v>
       </c>
@@ -2694,7 +2790,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="71.25">
+    <row r="27" spans="1:17" ht="71.25" hidden="1">
       <c r="A27" s="3" t="s">
         <v>167</v>
       </c>
@@ -2742,7 +2838,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="71.25">
+    <row r="28" spans="1:17" ht="71.25" hidden="1">
       <c r="A28" s="3" t="s">
         <v>168</v>
       </c>
@@ -2790,7 +2886,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="71.25">
+    <row r="29" spans="1:17" ht="71.25" hidden="1">
       <c r="A29" s="3" t="s">
         <v>169</v>
       </c>
@@ -2838,7 +2934,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="71.25">
+    <row r="30" spans="1:17" ht="71.25" hidden="1">
       <c r="A30" s="3" t="s">
         <v>170</v>
       </c>
@@ -2886,7 +2982,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="71.25">
+    <row r="31" spans="1:17" ht="71.25" hidden="1">
       <c r="A31" s="3" t="s">
         <v>171</v>
       </c>
@@ -2934,7 +3030,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="71.25">
+    <row r="32" spans="1:17" ht="71.25" hidden="1">
       <c r="A32" s="3" t="s">
         <v>172</v>
       </c>
@@ -2982,7 +3078,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="71.25">
+    <row r="33" spans="1:18" ht="71.25" hidden="1">
       <c r="A33" s="3" t="s">
         <v>173</v>
       </c>
@@ -3030,7 +3126,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="71.25">
+    <row r="34" spans="1:18" ht="71.25" hidden="1">
       <c r="A34" s="3" t="s">
         <v>174</v>
       </c>
@@ -3078,7 +3174,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="71.25">
+    <row r="35" spans="1:18" ht="71.25" hidden="1">
       <c r="A35" s="3" t="s">
         <v>175</v>
       </c>
@@ -3126,7 +3222,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="85.5">
+    <row r="36" spans="1:18" ht="85.5" hidden="1">
       <c r="A36" s="3" t="s">
         <v>176</v>
       </c>
@@ -3174,7 +3270,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="85.5">
+    <row r="37" spans="1:18" ht="85.5" hidden="1">
       <c r="A37" s="3" t="s">
         <v>177</v>
       </c>
@@ -3227,7 +3323,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="57">
+    <row r="38" spans="1:18" ht="57" hidden="1">
       <c r="A38" s="3" t="s">
         <v>182</v>
       </c>
@@ -3276,7 +3372,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="57">
+    <row r="39" spans="1:18" ht="57" hidden="1">
       <c r="A39" s="3" t="s">
         <v>187</v>
       </c>
@@ -3325,7 +3421,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="57">
+    <row r="40" spans="1:18" ht="57" hidden="1">
       <c r="A40" s="3" t="s">
         <v>188</v>
       </c>
@@ -3374,7 +3470,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="57">
+    <row r="41" spans="1:18" ht="57" hidden="1">
       <c r="A41" s="3" t="s">
         <v>189</v>
       </c>
@@ -3423,7 +3519,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="57">
+    <row r="42" spans="1:18" ht="57" hidden="1">
       <c r="A42" s="3" t="s">
         <v>195</v>
       </c>
@@ -3472,7 +3568,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="85.5">
+    <row r="43" spans="1:18" ht="85.5" hidden="1">
       <c r="A43" s="6" t="s">
         <v>199</v>
       </c>
@@ -3522,7 +3618,7 @@
       </c>
       <c r="R43" s="8"/>
     </row>
-    <row r="44" spans="1:18" ht="85.5">
+    <row r="44" spans="1:18" ht="85.5" hidden="1">
       <c r="A44" s="6" t="s">
         <v>204</v>
       </c>
@@ -3572,7 +3668,7 @@
       </c>
       <c r="R44" s="9"/>
     </row>
-    <row r="45" spans="1:18" ht="85.5">
+    <row r="45" spans="1:18" ht="85.5" hidden="1">
       <c r="A45" s="6" t="s">
         <v>207</v>
       </c>
@@ -3622,7 +3718,7 @@
       </c>
       <c r="R45" s="8"/>
     </row>
-    <row r="46" spans="1:18" ht="85.5">
+    <row r="46" spans="1:18" ht="85.5" hidden="1">
       <c r="A46" s="10" t="s">
         <v>211</v>
       </c>
@@ -3672,7 +3768,7 @@
       </c>
       <c r="R46" s="14"/>
     </row>
-    <row r="47" spans="1:18" ht="57">
+    <row r="47" spans="1:18" ht="57" hidden="1">
       <c r="A47" s="6" t="s">
         <v>216</v>
       </c>
@@ -3722,7 +3818,7 @@
       </c>
       <c r="R47" s="16"/>
     </row>
-    <row r="48" spans="1:18" ht="57">
+    <row r="48" spans="1:18" ht="57" hidden="1">
       <c r="A48" s="6" t="s">
         <v>221</v>
       </c>
@@ -3772,7 +3868,7 @@
       </c>
       <c r="R48" s="16"/>
     </row>
-    <row r="49" spans="1:18" ht="57">
+    <row r="49" spans="1:18" ht="57" hidden="1">
       <c r="A49" s="6" t="s">
         <v>224</v>
       </c>
@@ -3816,7 +3912,7 @@
       </c>
       <c r="R49" s="16"/>
     </row>
-    <row r="50" spans="1:18" ht="57">
+    <row r="50" spans="1:18" ht="57" hidden="1">
       <c r="A50" s="6" t="s">
         <v>228</v>
       </c>
@@ -3860,7 +3956,7 @@
       </c>
       <c r="R50" s="16"/>
     </row>
-    <row r="51" spans="1:18" ht="71.25">
+    <row r="51" spans="1:18" ht="71.25" hidden="1">
       <c r="A51" s="6" t="s">
         <v>228</v>
       </c>
@@ -3906,7 +4002,7 @@
       </c>
       <c r="R51" s="16"/>
     </row>
-    <row r="52" spans="1:18" ht="114">
+    <row r="52" spans="1:18" ht="114" hidden="1">
       <c r="A52" s="10" t="s">
         <v>236</v>
       </c>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E7A630-A5C6-459B-BDB8-C530B7E38144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2756424-C882-45AB-8DB1-2C979D463E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="323">
   <si>
     <t>TAG</t>
   </si>
@@ -886,6 +886,126 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/OS5941.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5993.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5993.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5995.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5995.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5991.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5991.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5989.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5989.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5987.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5987.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5985.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5985.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5983.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5983.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5981.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5981.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5979.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5979.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5977.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5977.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5975.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5975.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5973.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5973.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5971.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5971.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5969.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5969.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5967.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5967.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5965.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5965.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6056.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6056.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6040.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6040.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6025.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6025.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6047.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6047.pdf</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1025,20 +1145,11 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1051,9 +1162,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1212,10 +1320,18 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R52" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
   <autoFilter ref="A1:R52" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="WEG CESTARI"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="3">
       <filters>
-        <filter val="C10 - 3"/>
+        <filter val="V58"/>
       </filters>
+    </filterColumn>
+    <filterColumn colId="14">
+      <filters blank="1"/>
     </filterColumn>
   </autoFilter>
   <tableColumns count="18">
@@ -1399,7 +1515,7 @@
   <dimension ref="A1:R52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="16.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.125" style="2" customWidth="1"/>
@@ -2016,7 +2132,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="57">
+    <row r="12" spans="1:18" ht="57" hidden="1">
       <c r="A12" s="3" t="s">
         <v>89</v>
       </c>
@@ -2070,7 +2186,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="57">
+    <row r="13" spans="1:18" ht="57" hidden="1">
       <c r="A13" s="3" t="s">
         <v>90</v>
       </c>
@@ -2124,7 +2240,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="57">
+    <row r="14" spans="1:18" ht="57" hidden="1">
       <c r="A14" s="3" t="s">
         <v>91</v>
       </c>
@@ -2178,7 +2294,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="57">
+    <row r="15" spans="1:18" ht="57" hidden="1">
       <c r="A15" s="3" t="s">
         <v>92</v>
       </c>
@@ -2232,7 +2348,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="57">
+    <row r="16" spans="1:18" ht="57" hidden="1">
       <c r="A16" s="3" t="s">
         <v>93</v>
       </c>
@@ -2286,7 +2402,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="57">
+    <row r="17" spans="1:17" ht="57" hidden="1">
       <c r="A17" s="3" t="s">
         <v>94</v>
       </c>
@@ -2340,7 +2456,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="57">
+    <row r="18" spans="1:17" ht="57" hidden="1">
       <c r="A18" s="3" t="s">
         <v>95</v>
       </c>
@@ -2394,7 +2510,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="57">
+    <row r="19" spans="1:17" ht="57" hidden="1">
       <c r="A19" s="3" t="s">
         <v>96</v>
       </c>
@@ -2448,7 +2564,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="57">
+    <row r="20" spans="1:17" ht="57" hidden="1">
       <c r="A20" s="3" t="s">
         <v>97</v>
       </c>
@@ -2544,13 +2660,17 @@
         <v>215</v>
       </c>
       <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
+      <c r="O21" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>286</v>
+      </c>
       <c r="Q21" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="71.25" hidden="1">
+    <row r="22" spans="1:17" ht="85.5" hidden="1">
       <c r="A22" s="3" t="s">
         <v>162</v>
       </c>
@@ -2592,8 +2712,12 @@
         <v>215</v>
       </c>
       <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
+      <c r="O22" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="Q22" s="3" t="s">
         <v>131</v>
       </c>
@@ -2640,8 +2764,12 @@
         <v>215</v>
       </c>
       <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
+      <c r="O23" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>288</v>
+      </c>
       <c r="Q23" s="3" t="s">
         <v>133</v>
       </c>
@@ -2688,13 +2816,17 @@
         <v>215</v>
       </c>
       <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
+      <c r="O24" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>290</v>
+      </c>
       <c r="Q24" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="71.25" hidden="1">
+    <row r="25" spans="1:17" ht="85.5" hidden="1">
       <c r="A25" s="3" t="s">
         <v>165</v>
       </c>
@@ -2736,8 +2868,12 @@
         <v>215</v>
       </c>
       <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
+      <c r="O25" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>292</v>
+      </c>
       <c r="Q25" s="3" t="s">
         <v>137</v>
       </c>
@@ -2784,8 +2920,12 @@
         <v>215</v>
       </c>
       <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
+      <c r="O26" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>294</v>
+      </c>
       <c r="Q26" s="3" t="s">
         <v>139</v>
       </c>
@@ -2832,8 +2972,12 @@
         <v>215</v>
       </c>
       <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
+      <c r="O27" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="Q27" s="3" t="s">
         <v>141</v>
       </c>
@@ -2880,8 +3024,12 @@
         <v>215</v>
       </c>
       <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
+      <c r="O28" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="Q28" s="3" t="s">
         <v>143</v>
       </c>
@@ -2928,8 +3076,12 @@
         <v>215</v>
       </c>
       <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
+      <c r="O29" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="Q29" s="3" t="s">
         <v>145</v>
       </c>
@@ -2976,8 +3128,12 @@
         <v>215</v>
       </c>
       <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
+      <c r="O30" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="Q30" s="3" t="s">
         <v>147</v>
       </c>
@@ -3024,8 +3180,12 @@
         <v>215</v>
       </c>
       <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
+      <c r="O31" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>304</v>
+      </c>
       <c r="Q31" s="3" t="s">
         <v>149</v>
       </c>
@@ -3072,8 +3232,12 @@
         <v>215</v>
       </c>
       <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
+      <c r="O32" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>306</v>
+      </c>
       <c r="Q32" s="3" t="s">
         <v>151</v>
       </c>
@@ -3120,8 +3284,12 @@
         <v>215</v>
       </c>
       <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
+      <c r="O33" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>308</v>
+      </c>
       <c r="Q33" s="3" t="s">
         <v>153</v>
       </c>
@@ -3168,8 +3336,12 @@
         <v>215</v>
       </c>
       <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
+      <c r="O34" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>310</v>
+      </c>
       <c r="Q34" s="3" t="s">
         <v>155</v>
       </c>
@@ -3216,8 +3388,12 @@
         <v>215</v>
       </c>
       <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
+      <c r="O35" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>312</v>
+      </c>
       <c r="Q35" s="3" t="s">
         <v>157</v>
       </c>
@@ -3264,8 +3440,12 @@
         <v>215</v>
       </c>
       <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
+      <c r="O36" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>314</v>
+      </c>
       <c r="Q36" s="3" t="s">
         <v>159</v>
       </c>
@@ -3568,238 +3748,250 @@
         <v>197</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="85.5" hidden="1">
-      <c r="A43" s="6" t="s">
+    <row r="43" spans="1:18" ht="85.5">
+      <c r="A43" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="3">
         <v>118.3</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G43" s="3">
         <v>1750</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H43" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I43" s="4" t="s">
+      <c r="I43" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J43" s="4">
+      <c r="J43" s="3">
         <v>9</v>
       </c>
-      <c r="K43" s="4" t="s">
+      <c r="K43" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="L43" s="4" t="s">
+      <c r="L43" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M43" s="4" t="s">
+      <c r="M43" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="N43" s="4" t="s">
+      <c r="N43" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4" t="s">
+      <c r="O43" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q43" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="R43" s="8"/>
-    </row>
-    <row r="44" spans="1:18" ht="85.5" hidden="1">
-      <c r="A44" s="6" t="s">
+    </row>
+    <row r="44" spans="1:18" ht="85.5">
+      <c r="A44" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="3">
         <v>118.3</v>
       </c>
-      <c r="G44" s="5">
+      <c r="G44" s="3">
         <v>1750</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H44" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I44" s="5" t="s">
+      <c r="I44" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J44" s="5">
+      <c r="J44" s="3">
         <v>9</v>
       </c>
-      <c r="K44" s="5" t="s">
+      <c r="K44" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="L44" s="4" t="s">
+      <c r="L44" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M44" s="4" t="s">
+      <c r="M44" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="N44" s="5" t="s">
+      <c r="N44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5" t="s">
+      <c r="O44" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q44" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="R44" s="9"/>
-    </row>
-    <row r="45" spans="1:18" ht="85.5" hidden="1">
-      <c r="A45" s="6" t="s">
+    </row>
+    <row r="45" spans="1:18" ht="85.5">
+      <c r="A45" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="3">
         <v>118.3</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G45" s="3">
         <v>1750</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="H45" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I45" s="4" t="s">
+      <c r="I45" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J45" s="4">
+      <c r="J45" s="3">
         <v>9</v>
       </c>
-      <c r="K45" s="4" t="s">
+      <c r="K45" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="L45" s="4" t="s">
+      <c r="L45" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M45" s="4" t="s">
+      <c r="M45" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="N45" s="4" t="s">
+      <c r="N45" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="4" t="s">
+      <c r="O45" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q45" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="R45" s="8"/>
-    </row>
-    <row r="46" spans="1:18" ht="85.5" hidden="1">
-      <c r="A46" s="10" t="s">
+    </row>
+    <row r="46" spans="1:18" ht="85.5">
+      <c r="A46" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="3">
         <v>118.3</v>
       </c>
-      <c r="G46" s="12">
+      <c r="G46" s="3">
         <v>1750</v>
       </c>
-      <c r="H46" s="12" t="s">
+      <c r="H46" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I46" s="12" t="s">
+      <c r="I46" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J46" s="12">
+      <c r="J46" s="3">
         <v>9</v>
       </c>
-      <c r="K46" s="12" t="s">
+      <c r="K46" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="L46" s="13" t="s">
+      <c r="L46" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M46" s="13" t="s">
+      <c r="M46" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="N46" s="12" t="s">
+      <c r="N46" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O46" s="12"/>
-      <c r="P46" s="12"/>
-      <c r="Q46" s="12" t="s">
+      <c r="O46" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q46" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="R46" s="14"/>
     </row>
     <row r="47" spans="1:18" ht="57" hidden="1">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="15" t="s">
+      <c r="E47" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="F47" s="15">
+      <c r="F47" s="11">
         <v>72.5</v>
       </c>
-      <c r="G47" s="15">
+      <c r="G47" s="11">
         <v>1750</v>
       </c>
-      <c r="H47" s="15" t="s">
+      <c r="H47" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="I47" s="15" t="s">
+      <c r="I47" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="J47" s="15">
+      <c r="J47" s="11">
         <v>5.9</v>
       </c>
-      <c r="K47" s="15" t="s">
+      <c r="K47" s="11" t="s">
         <v>219</v>
       </c>
       <c r="L47" s="4" t="s">
@@ -3811,45 +4003,45 @@
       <c r="N47" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="O47" s="15"/>
-      <c r="P47" s="15"/>
-      <c r="Q47" s="15" t="s">
+      <c r="O47" s="11"/>
+      <c r="P47" s="11"/>
+      <c r="Q47" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="R47" s="16"/>
+      <c r="R47" s="12"/>
     </row>
     <row r="48" spans="1:18" ht="57" hidden="1">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="F48" s="15">
+      <c r="F48" s="11">
         <v>72.5</v>
       </c>
-      <c r="G48" s="15">
+      <c r="G48" s="11">
         <v>1750</v>
       </c>
-      <c r="H48" s="15" t="s">
+      <c r="H48" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="I48" s="15" t="s">
+      <c r="I48" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="J48" s="15">
+      <c r="J48" s="11">
         <v>5.9</v>
       </c>
-      <c r="K48" s="15" t="s">
+      <c r="K48" s="11" t="s">
         <v>222</v>
       </c>
       <c r="L48" s="4" t="s">
@@ -3861,39 +4053,39 @@
       <c r="N48" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="O48" s="15"/>
-      <c r="P48" s="15"/>
-      <c r="Q48" s="15" t="s">
+      <c r="O48" s="11"/>
+      <c r="P48" s="11"/>
+      <c r="Q48" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="R48" s="16"/>
+      <c r="R48" s="12"/>
     </row>
     <row r="49" spans="1:18" ht="57" hidden="1">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="D49" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E49" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15" t="s">
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="J49" s="15">
+      <c r="J49" s="11">
         <v>5.9</v>
       </c>
-      <c r="K49" s="15" t="s">
+      <c r="K49" s="11" t="s">
         <v>226</v>
       </c>
       <c r="L49" s="4" t="s">
@@ -3905,39 +4097,39 @@
       <c r="N49" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="O49" s="15"/>
-      <c r="P49" s="15"/>
-      <c r="Q49" s="15" t="s">
+      <c r="O49" s="11"/>
+      <c r="P49" s="11"/>
+      <c r="Q49" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="R49" s="16"/>
+      <c r="R49" s="12"/>
     </row>
     <row r="50" spans="1:18" ht="57" hidden="1">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D50" s="15" t="s">
+      <c r="D50" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15" t="s">
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="J50" s="15">
+      <c r="J50" s="11">
         <v>5.9</v>
       </c>
-      <c r="K50" s="15" t="s">
+      <c r="K50" s="11" t="s">
         <v>226</v>
       </c>
       <c r="L50" s="4" t="s">
@@ -3949,41 +4141,41 @@
       <c r="N50" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="O50" s="15"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="15" t="s">
+      <c r="O50" s="11"/>
+      <c r="P50" s="11"/>
+      <c r="Q50" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="R50" s="16"/>
+      <c r="R50" s="12"/>
     </row>
     <row r="51" spans="1:18" ht="71.25" hidden="1">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D51" s="15" t="s">
+      <c r="D51" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="F51" s="15">
+      <c r="F51" s="11">
         <v>15.64</v>
       </c>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15" t="s">
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="J51" s="15">
+      <c r="J51" s="11">
         <v>5.9</v>
       </c>
-      <c r="K51" s="15" t="s">
+      <c r="K51" s="11" t="s">
         <v>231</v>
       </c>
       <c r="L51" s="4" t="s">
@@ -3995,62 +4187,62 @@
       <c r="N51" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="15" t="s">
+      <c r="O51" s="11"/>
+      <c r="P51" s="11"/>
+      <c r="Q51" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="R51" s="16"/>
+      <c r="R51" s="12"/>
     </row>
     <row r="52" spans="1:18" ht="114" hidden="1">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F52" s="12">
+      <c r="F52" s="9">
         <v>97.89</v>
       </c>
-      <c r="G52" s="12">
+      <c r="G52" s="9">
         <v>1752</v>
       </c>
-      <c r="H52" s="12" t="s">
+      <c r="H52" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="I52" s="12" t="s">
+      <c r="I52" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J52" s="12">
+      <c r="J52" s="9">
         <v>11</v>
       </c>
-      <c r="K52" s="12" t="s">
+      <c r="K52" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="L52" s="13" t="s">
+      <c r="L52" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="M52" s="13" t="s">
+      <c r="M52" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="N52" s="13" t="s">
+      <c r="N52" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="12" t="s">
+      <c r="O52" s="13"/>
+      <c r="P52" s="13"/>
+      <c r="Q52" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="R52" s="18"/>
+      <c r="R52" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -4081,10 +4273,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="15"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2756424-C882-45AB-8DB1-2C979D463E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75631603-72A6-4EC7-8742-6D5C10FC3BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="333">
   <si>
     <t>TAG</t>
   </si>
@@ -1006,6 +1006,36 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/OS6047.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5920.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LOS5920.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5903.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LOS5903.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5898.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LOS5898.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5924.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LOS5924.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5936.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LOS5936.pdf</t>
   </si>
 </sst>
 </file>
@@ -1325,12 +1355,7 @@
         <filter val="WEG CESTARI"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="V58"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="14">
+    <filterColumn colId="15">
       <filters blank="1"/>
     </filterColumn>
   </autoFilter>
@@ -2670,7 +2695,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="85.5" hidden="1">
+    <row r="22" spans="1:17" ht="71.25" hidden="1">
       <c r="A22" s="3" t="s">
         <v>162</v>
       </c>
@@ -2826,7 +2851,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="85.5" hidden="1">
+    <row r="25" spans="1:17" ht="71.25" hidden="1">
       <c r="A25" s="3" t="s">
         <v>165</v>
       </c>
@@ -3503,7 +3528,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="57" hidden="1">
+    <row r="38" spans="1:18" ht="57">
       <c r="A38" s="3" t="s">
         <v>182</v>
       </c>
@@ -3546,13 +3571,17 @@
       <c r="N38" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O38" s="3"/>
-      <c r="P38" s="3"/>
+      <c r="O38" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="Q38" s="3" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="57" hidden="1">
+    <row r="39" spans="1:18" ht="57">
       <c r="A39" s="3" t="s">
         <v>187</v>
       </c>
@@ -3595,13 +3624,17 @@
       <c r="N39" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
+      <c r="O39" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>326</v>
+      </c>
       <c r="Q39" s="3" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="57" hidden="1">
+    <row r="40" spans="1:18" ht="57">
       <c r="A40" s="3" t="s">
         <v>188</v>
       </c>
@@ -3644,13 +3677,17 @@
       <c r="N40" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
+      <c r="O40" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>328</v>
+      </c>
       <c r="Q40" s="3" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="57" hidden="1">
+    <row r="41" spans="1:18" ht="57">
       <c r="A41" s="3" t="s">
         <v>189</v>
       </c>
@@ -3693,13 +3730,17 @@
       <c r="N41" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
+      <c r="O41" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="Q41" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="57" hidden="1">
+    <row r="42" spans="1:18" ht="57">
       <c r="A42" s="3" t="s">
         <v>195</v>
       </c>
@@ -3742,13 +3783,17 @@
       <c r="N42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
+      <c r="O42" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>332</v>
+      </c>
       <c r="Q42" s="3" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="85.5">
+    <row r="43" spans="1:18" ht="85.5" hidden="1">
       <c r="A43" s="3" t="s">
         <v>199</v>
       </c>
@@ -3801,7 +3846,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="85.5">
+    <row r="44" spans="1:18" ht="85.5" hidden="1">
       <c r="A44" s="3" t="s">
         <v>204</v>
       </c>
@@ -3854,7 +3899,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="85.5">
+    <row r="45" spans="1:18" ht="85.5" hidden="1">
       <c r="A45" s="3" t="s">
         <v>207</v>
       </c>
@@ -3907,7 +3952,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="85.5">
+    <row r="46" spans="1:18" ht="85.5" hidden="1">
       <c r="A46" s="3" t="s">
         <v>211</v>
       </c>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75631603-72A6-4EC7-8742-6D5C10FC3BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E152319-6D68-4B79-B903-5E907CDA0DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="346">
   <si>
     <t>TAG</t>
   </si>
@@ -1036,6 +1036,45 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/LOS5936.pdf</t>
+  </si>
+  <si>
+    <t>RE-631506</t>
+  </si>
+  <si>
+    <t>BREVINI</t>
+  </si>
+  <si>
+    <t>REDUTOR PLANETARIO</t>
+  </si>
+  <si>
+    <t>SC 12004</t>
+  </si>
+  <si>
+    <t>MOTOR 75 CV 4 POLOS</t>
+  </si>
+  <si>
+    <t>REDUTOR TRANSPORTADORA REDLER TARD/2000 - (TRR631506)</t>
+  </si>
+  <si>
+    <t>assets/img/BREVINI.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LISTABREVINI.pdf</t>
+  </si>
+  <si>
+    <t>OS Nº 5964 - GOLD</t>
+  </si>
+  <si>
+    <t>JÁ ENVIADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/MANUALBREVINI.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5964.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5964.pdf</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1108,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1101,6 +1140,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1161,7 +1206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1208,11 +1253,27 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1348,38 +1409,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R52" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
-  <autoFilter ref="A1:R52" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R53" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+  <autoFilter ref="A1:R53" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="WEG CESTARI"/>
+        <filter val="BREVINI"/>
       </filters>
-    </filterColumn>
-    <filterColumn colId="15">
-      <filters blank="1"/>
     </filterColumn>
   </autoFilter>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="18">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="21"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="19">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1537,7 +1595,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R52"/>
+  <dimension ref="A1:R53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
@@ -3528,7 +3586,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="57">
+    <row r="38" spans="1:18" ht="57" hidden="1">
       <c r="A38" s="3" t="s">
         <v>182</v>
       </c>
@@ -3581,7 +3639,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="57">
+    <row r="39" spans="1:18" ht="57" hidden="1">
       <c r="A39" s="3" t="s">
         <v>187</v>
       </c>
@@ -3634,7 +3692,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="57">
+    <row r="40" spans="1:18" ht="57" hidden="1">
       <c r="A40" s="3" t="s">
         <v>188</v>
       </c>
@@ -3687,7 +3745,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="57">
+    <row r="41" spans="1:18" ht="57" hidden="1">
       <c r="A41" s="3" t="s">
         <v>189</v>
       </c>
@@ -3740,7 +3798,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="57">
+    <row r="42" spans="1:18" ht="57" hidden="1">
       <c r="A42" s="3" t="s">
         <v>195</v>
       </c>
@@ -4289,16 +4347,66 @@
       </c>
       <c r="R52" s="14"/>
     </row>
+    <row r="53" spans="1:18" ht="71.25">
+      <c r="A53" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="F53" s="16">
+        <v>337.3</v>
+      </c>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="J53" s="16"/>
+      <c r="K53" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="M53" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="N53" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="O53" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q53" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="R53" s="17" t="s">
+        <v>342</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B53:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
+  <conditionalFormatting sqref="B54:B1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R52">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  <conditionalFormatting sqref="R2:R53">
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E152319-6D68-4B79-B903-5E907CDA0DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3C25A1-3802-48AB-A1ED-F2BF9C9EF1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="360">
   <si>
     <t>TAG</t>
   </si>
@@ -1047,9 +1047,6 @@
     <t>REDUTOR PLANETARIO</t>
   </si>
   <si>
-    <t>SC 12004</t>
-  </si>
-  <si>
     <t>MOTOR 75 CV 4 POLOS</t>
   </si>
   <si>
@@ -1075,6 +1072,51 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/RELATFINALOS5964.pdf</t>
+  </si>
+  <si>
+    <t>BREVINI - SC 12004</t>
+  </si>
+  <si>
+    <t>RE-601129</t>
+  </si>
+  <si>
+    <t>V 06</t>
+  </si>
+  <si>
+    <t>MOTOR 1 CV 4 POLOS</t>
+  </si>
+  <si>
+    <t>REDUTOR DO MOTOR DA VALVULA ROTATIVA 13 - MULTICICLONE</t>
+  </si>
+  <si>
+    <t>OS Nº 6049 - GOLD</t>
+  </si>
+  <si>
+    <t>ME - 601073</t>
+  </si>
+  <si>
+    <t>V56</t>
+  </si>
+  <si>
+    <t>OS Nº 6034 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR VÁLVULA ROTATIVA 12 - PRÉ/ECO 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6034.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6034.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6049.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6049.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/PEÇAS V6I.pdf</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +1248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1259,11 +1301,47 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1409,35 +1487,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R53" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
-  <autoFilter ref="A1:R53" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="BREVINI"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R55" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
+  <autoFilter ref="A1:R55" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="21"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="24"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="22">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="9"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="8"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1595,7 +1667,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
@@ -1675,7 +1747,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="57" hidden="1">
+    <row r="2" spans="1:18" ht="57">
       <c r="A2" s="3" t="s">
         <v>38</v>
       </c>
@@ -1729,7 +1801,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="57" hidden="1">
+    <row r="3" spans="1:18" ht="57">
       <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
@@ -1783,7 +1855,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="57" hidden="1">
+    <row r="4" spans="1:18" ht="57">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
@@ -1837,7 +1909,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="57" hidden="1">
+    <row r="5" spans="1:18" ht="57">
       <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
@@ -1891,7 +1963,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="57" hidden="1">
+    <row r="6" spans="1:18" ht="57">
       <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
@@ -1945,7 +2017,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="57" hidden="1">
+    <row r="7" spans="1:18" ht="57">
       <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
@@ -1999,7 +2071,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="57" hidden="1">
+    <row r="8" spans="1:18" ht="57">
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
@@ -2053,7 +2125,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="57" hidden="1">
+    <row r="9" spans="1:18" ht="57">
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
@@ -2107,7 +2179,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="57" hidden="1">
+    <row r="10" spans="1:18" ht="57">
       <c r="A10" s="3" t="s">
         <v>73</v>
       </c>
@@ -2161,7 +2233,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="57" hidden="1">
+    <row r="11" spans="1:18" ht="57">
       <c r="A11" s="3" t="s">
         <v>77</v>
       </c>
@@ -2215,7 +2287,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="57" hidden="1">
+    <row r="12" spans="1:18" ht="57">
       <c r="A12" s="3" t="s">
         <v>89</v>
       </c>
@@ -2269,7 +2341,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="57" hidden="1">
+    <row r="13" spans="1:18" ht="57">
       <c r="A13" s="3" t="s">
         <v>90</v>
       </c>
@@ -2323,7 +2395,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="57" hidden="1">
+    <row r="14" spans="1:18" ht="57">
       <c r="A14" s="3" t="s">
         <v>91</v>
       </c>
@@ -2377,7 +2449,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="57" hidden="1">
+    <row r="15" spans="1:18" ht="57">
       <c r="A15" s="3" t="s">
         <v>92</v>
       </c>
@@ -2431,7 +2503,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="57" hidden="1">
+    <row r="16" spans="1:18" ht="57">
       <c r="A16" s="3" t="s">
         <v>93</v>
       </c>
@@ -2485,7 +2557,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="57" hidden="1">
+    <row r="17" spans="1:17" ht="57">
       <c r="A17" s="3" t="s">
         <v>94</v>
       </c>
@@ -2539,7 +2611,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="57" hidden="1">
+    <row r="18" spans="1:17" ht="57">
       <c r="A18" s="3" t="s">
         <v>95</v>
       </c>
@@ -2593,7 +2665,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="57" hidden="1">
+    <row r="19" spans="1:17" ht="57">
       <c r="A19" s="3" t="s">
         <v>96</v>
       </c>
@@ -2647,7 +2719,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="57" hidden="1">
+    <row r="20" spans="1:17" ht="57">
       <c r="A20" s="3" t="s">
         <v>97</v>
       </c>
@@ -2701,7 +2773,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="71.25" hidden="1">
+    <row r="21" spans="1:17" ht="71.25">
       <c r="A21" s="3" t="s">
         <v>161</v>
       </c>
@@ -2753,7 +2825,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="71.25" hidden="1">
+    <row r="22" spans="1:17" ht="71.25">
       <c r="A22" s="3" t="s">
         <v>162</v>
       </c>
@@ -2805,7 +2877,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="71.25" hidden="1">
+    <row r="23" spans="1:17" ht="71.25">
       <c r="A23" s="3" t="s">
         <v>163</v>
       </c>
@@ -2857,7 +2929,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="71.25" hidden="1">
+    <row r="24" spans="1:17" ht="71.25">
       <c r="A24" s="3" t="s">
         <v>164</v>
       </c>
@@ -2909,7 +2981,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="71.25" hidden="1">
+    <row r="25" spans="1:17" ht="71.25">
       <c r="A25" s="3" t="s">
         <v>165</v>
       </c>
@@ -2961,7 +3033,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="71.25" hidden="1">
+    <row r="26" spans="1:17" ht="71.25">
       <c r="A26" s="3" t="s">
         <v>166</v>
       </c>
@@ -3013,7 +3085,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="71.25" hidden="1">
+    <row r="27" spans="1:17" ht="71.25">
       <c r="A27" s="3" t="s">
         <v>167</v>
       </c>
@@ -3065,7 +3137,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="71.25" hidden="1">
+    <row r="28" spans="1:17" ht="71.25">
       <c r="A28" s="3" t="s">
         <v>168</v>
       </c>
@@ -3117,7 +3189,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="71.25" hidden="1">
+    <row r="29" spans="1:17" ht="71.25">
       <c r="A29" s="3" t="s">
         <v>169</v>
       </c>
@@ -3169,7 +3241,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="71.25" hidden="1">
+    <row r="30" spans="1:17" ht="71.25">
       <c r="A30" s="3" t="s">
         <v>170</v>
       </c>
@@ -3221,7 +3293,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="71.25" hidden="1">
+    <row r="31" spans="1:17" ht="71.25">
       <c r="A31" s="3" t="s">
         <v>171</v>
       </c>
@@ -3273,7 +3345,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="71.25" hidden="1">
+    <row r="32" spans="1:17" ht="71.25">
       <c r="A32" s="3" t="s">
         <v>172</v>
       </c>
@@ -3325,7 +3397,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="71.25" hidden="1">
+    <row r="33" spans="1:18" ht="71.25">
       <c r="A33" s="3" t="s">
         <v>173</v>
       </c>
@@ -3377,7 +3449,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="71.25" hidden="1">
+    <row r="34" spans="1:18" ht="71.25">
       <c r="A34" s="3" t="s">
         <v>174</v>
       </c>
@@ -3429,7 +3501,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="71.25" hidden="1">
+    <row r="35" spans="1:18" ht="71.25">
       <c r="A35" s="3" t="s">
         <v>175</v>
       </c>
@@ -3481,7 +3553,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="85.5" hidden="1">
+    <row r="36" spans="1:18" ht="85.5">
       <c r="A36" s="3" t="s">
         <v>176</v>
       </c>
@@ -3533,7 +3605,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="85.5" hidden="1">
+    <row r="37" spans="1:18" ht="85.5">
       <c r="A37" s="3" t="s">
         <v>177</v>
       </c>
@@ -3586,7 +3658,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="57" hidden="1">
+    <row r="38" spans="1:18" ht="57">
       <c r="A38" s="3" t="s">
         <v>182</v>
       </c>
@@ -3639,7 +3711,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="57" hidden="1">
+    <row r="39" spans="1:18" ht="57">
       <c r="A39" s="3" t="s">
         <v>187</v>
       </c>
@@ -3692,7 +3764,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="57" hidden="1">
+    <row r="40" spans="1:18" ht="57">
       <c r="A40" s="3" t="s">
         <v>188</v>
       </c>
@@ -3745,7 +3817,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="57" hidden="1">
+    <row r="41" spans="1:18" ht="57">
       <c r="A41" s="3" t="s">
         <v>189</v>
       </c>
@@ -3798,7 +3870,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="57" hidden="1">
+    <row r="42" spans="1:18" ht="57">
       <c r="A42" s="3" t="s">
         <v>195</v>
       </c>
@@ -3851,7 +3923,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="85.5" hidden="1">
+    <row r="43" spans="1:18" ht="85.5">
       <c r="A43" s="3" t="s">
         <v>199</v>
       </c>
@@ -3904,7 +3976,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="85.5" hidden="1">
+    <row r="44" spans="1:18" ht="85.5">
       <c r="A44" s="3" t="s">
         <v>204</v>
       </c>
@@ -3957,7 +4029,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="85.5" hidden="1">
+    <row r="45" spans="1:18" ht="85.5">
       <c r="A45" s="3" t="s">
         <v>207</v>
       </c>
@@ -4010,7 +4082,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="85.5" hidden="1">
+    <row r="46" spans="1:18" ht="85.5">
       <c r="A46" s="3" t="s">
         <v>211</v>
       </c>
@@ -4063,7 +4135,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="57" hidden="1">
+    <row r="47" spans="1:18" ht="57">
       <c r="A47" s="5" t="s">
         <v>216</v>
       </c>
@@ -4113,7 +4185,7 @@
       </c>
       <c r="R47" s="12"/>
     </row>
-    <row r="48" spans="1:18" ht="57" hidden="1">
+    <row r="48" spans="1:18" ht="57">
       <c r="A48" s="5" t="s">
         <v>221</v>
       </c>
@@ -4163,7 +4235,7 @@
       </c>
       <c r="R48" s="12"/>
     </row>
-    <row r="49" spans="1:18" ht="57" hidden="1">
+    <row r="49" spans="1:18" ht="57">
       <c r="A49" s="5" t="s">
         <v>224</v>
       </c>
@@ -4207,7 +4279,7 @@
       </c>
       <c r="R49" s="12"/>
     </row>
-    <row r="50" spans="1:18" ht="57" hidden="1">
+    <row r="50" spans="1:18" ht="57">
       <c r="A50" s="5" t="s">
         <v>228</v>
       </c>
@@ -4251,7 +4323,7 @@
       </c>
       <c r="R50" s="12"/>
     </row>
-    <row r="51" spans="1:18" ht="71.25" hidden="1">
+    <row r="51" spans="1:18" ht="71.25">
       <c r="A51" s="5" t="s">
         <v>228</v>
       </c>
@@ -4297,7 +4369,7 @@
       </c>
       <c r="R51" s="12"/>
     </row>
-    <row r="52" spans="1:18" ht="114" hidden="1">
+    <row r="52" spans="1:18" ht="114">
       <c r="A52" s="7" t="s">
         <v>236</v>
       </c>
@@ -4358,10 +4430,10 @@
         <v>335</v>
       </c>
       <c r="D53" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="E53" s="16" t="s">
         <v>336</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>337</v>
       </c>
       <c r="F53" s="16">
         <v>337.3</v>
@@ -4373,40 +4445,146 @@
       </c>
       <c r="J53" s="16"/>
       <c r="K53" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="L53" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="L53" s="10" t="s">
+      <c r="M53" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="M53" s="10" t="s">
+      <c r="N53" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="O53" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q53" s="16" t="s">
         <v>340</v>
       </c>
-      <c r="N53" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="O53" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="P53" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q53" s="16" t="s">
+      <c r="R53" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="R53" s="17" t="s">
-        <v>342</v>
+    </row>
+    <row r="54" spans="1:18" ht="71.25">
+      <c r="A54" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="F54" s="3">
+        <v>155.05000000000001</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J54" s="3">
+        <v>3</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="M54" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="P54" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="57">
+      <c r="A55" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F55" s="3">
+        <v>185</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J55" s="3">
+        <v>9</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q55" s="3" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B54:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
+  <conditionalFormatting sqref="B56:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R53">
-    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+  <conditionalFormatting sqref="R2:R55">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3C25A1-3802-48AB-A1ED-F2BF9C9EF1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7BF7E8-F198-45FD-825E-1AEA00529BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1098,6 +1098,9 @@
     <t>V56</t>
   </si>
   <si>
+    <t xml:space="preserve"> assets/pdf/lista-pecas-ME-601073.pdf</t>
+  </si>
+  <si>
     <t>OS Nº 6034 - GOLD</t>
   </si>
   <si>
@@ -1114,9 +1117,6 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/OS6049.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> assets/pdf/PEÇAS V6I.pdf</t>
   </si>
 </sst>
 </file>
@@ -4507,16 +4507,16 @@
         <v>88</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>37</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P54" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>350</v>
@@ -4554,7 +4554,7 @@
         <v>9</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>88</v>
@@ -4566,13 +4566,13 @@
         <v>37</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7BF7E8-F198-45FD-825E-1AEA00529BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20BDFD0-9980-4787-B6A8-517789CFD855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="361">
   <si>
     <t>TAG</t>
   </si>
@@ -1117,6 +1117,9 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/OS6049.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/PEÇAS V6.pdf</t>
   </si>
 </sst>
 </file>
@@ -4507,7 +4510,7 @@
         <v>88</v>
       </c>
       <c r="M54" s="10" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>37</v>
@@ -4559,8 +4562,8 @@
       <c r="L55" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M55" s="3" t="s">
-        <v>214</v>
+      <c r="M55" s="10" t="s">
+        <v>353</v>
       </c>
       <c r="N55" s="3" t="s">
         <v>37</v>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20BDFD0-9980-4787-B6A8-517789CFD855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36412D4E-A65D-453B-BB1E-C808369BB1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="370">
   <si>
     <t>TAG</t>
   </si>
@@ -1120,6 +1120,33 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/PEÇAS V6.pdf</t>
+  </si>
+  <si>
+    <t>RE- 601047</t>
+  </si>
+  <si>
+    <t>REDUTOR DUPLO</t>
+  </si>
+  <si>
+    <t>MOTOR 0,5 CV  - 04 POLOS</t>
+  </si>
+  <si>
+    <t>REDUTOR PLANETARIO ESPARGIDOR</t>
+  </si>
+  <si>
+    <t>REDUTOR PRINCIPAL - OS Nº 6028 - GOLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LISTAPECASESPARGIDOR.pdf</t>
+  </si>
+  <si>
+    <t>assets/img/ESPARGIDOR.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6028.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6028.pdf</t>
   </si>
 </sst>
 </file>
@@ -1314,7 +1341,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="29">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1490,29 +1527,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R55" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
-  <autoFilter ref="A1:R55" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R56" headerRowDxfId="28" dataDxfId="27" totalsRowDxfId="26">
+  <autoFilter ref="A1:R56" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="22">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="25"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="23">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="10"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="9"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="8"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1670,7 +1707,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
@@ -4578,16 +4615,67 @@
         <v>354</v>
       </c>
     </row>
+    <row r="56" spans="1:18" ht="57">
+      <c r="A56" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J56" s="3">
+        <v>3</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="P56" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q56" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B56:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
+  <conditionalFormatting sqref="B57:B1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R55">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  <conditionalFormatting sqref="R2:R56">
+    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36412D4E-A65D-453B-BB1E-C808369BB1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E2D87D-6E52-4F5C-AED3-8CB3D03B8DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="384">
   <si>
     <t>TAG</t>
   </si>
@@ -1147,13 +1147,55 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/OS6028.pdf</t>
+  </si>
+  <si>
+    <t>S/TAG</t>
+  </si>
+  <si>
+    <t>RE-631105</t>
+  </si>
+  <si>
+    <t>MOTOR 10 CV -  4 POLOS</t>
+  </si>
+  <si>
+    <t>REDUTOR ROSCA TRANSPORTADORA 01 (RT-01)</t>
+  </si>
+  <si>
+    <t>OS Nº 5927 - GOLD</t>
+  </si>
+  <si>
+    <t>RE-631107</t>
+  </si>
+  <si>
+    <t>REDUTOR ROSCA TRANSPORTADORA 02 (RT-02)</t>
+  </si>
+  <si>
+    <t>OS Nº 5954 - GOLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5927.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5927.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5954.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5954.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5934.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5934.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1174,13 +1216,8 @@
       <sz val="8"/>
       <name val="Carlito"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Carlito"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1197,32 +1234,8 @@
         <fgColor rgb="FFD4AF37"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1230,55 +1243,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1289,89 +1258,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="30">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1513,6 +1407,46 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1527,29 +1461,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R56" headerRowDxfId="28" dataDxfId="27" totalsRowDxfId="26">
-  <autoFilter ref="A1:R56" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R58" headerRowDxfId="25" dataDxfId="24" totalsRowDxfId="23">
+  <autoFilter ref="A1:R58" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="SEW"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="25"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="22"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="20">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1707,7 +1647,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
@@ -1787,7 +1727,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="57">
+    <row r="2" spans="1:18" ht="57" hidden="1">
       <c r="A2" s="3" t="s">
         <v>38</v>
       </c>
@@ -1841,7 +1781,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="57">
+    <row r="3" spans="1:18" ht="57" hidden="1">
       <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
@@ -1895,7 +1835,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="57">
+    <row r="4" spans="1:18" ht="57" hidden="1">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
@@ -1949,7 +1889,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="57">
+    <row r="5" spans="1:18" ht="57" hidden="1">
       <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
@@ -2003,7 +1943,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="57">
+    <row r="6" spans="1:18" ht="57" hidden="1">
       <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
@@ -2057,7 +1997,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="57">
+    <row r="7" spans="1:18" ht="57" hidden="1">
       <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
@@ -2111,7 +2051,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="57">
+    <row r="8" spans="1:18" ht="57" hidden="1">
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
@@ -2165,7 +2105,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="57">
+    <row r="9" spans="1:18" ht="57" hidden="1">
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
@@ -2219,7 +2159,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="57">
+    <row r="10" spans="1:18" ht="57" hidden="1">
       <c r="A10" s="3" t="s">
         <v>73</v>
       </c>
@@ -2273,7 +2213,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="57">
+    <row r="11" spans="1:18" ht="57" hidden="1">
       <c r="A11" s="3" t="s">
         <v>77</v>
       </c>
@@ -2327,7 +2267,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="57">
+    <row r="12" spans="1:18" ht="57" hidden="1">
       <c r="A12" s="3" t="s">
         <v>89</v>
       </c>
@@ -2381,7 +2321,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="57">
+    <row r="13" spans="1:18" ht="57" hidden="1">
       <c r="A13" s="3" t="s">
         <v>90</v>
       </c>
@@ -2435,7 +2375,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="57">
+    <row r="14" spans="1:18" ht="57" hidden="1">
       <c r="A14" s="3" t="s">
         <v>91</v>
       </c>
@@ -2489,7 +2429,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="57">
+    <row r="15" spans="1:18" ht="57" hidden="1">
       <c r="A15" s="3" t="s">
         <v>92</v>
       </c>
@@ -2543,7 +2483,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="57">
+    <row r="16" spans="1:18" ht="57" hidden="1">
       <c r="A16" s="3" t="s">
         <v>93</v>
       </c>
@@ -2597,7 +2537,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="57">
+    <row r="17" spans="1:17" ht="57" hidden="1">
       <c r="A17" s="3" t="s">
         <v>94</v>
       </c>
@@ -2651,7 +2591,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="57">
+    <row r="18" spans="1:17" ht="57" hidden="1">
       <c r="A18" s="3" t="s">
         <v>95</v>
       </c>
@@ -2705,7 +2645,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="57">
+    <row r="19" spans="1:17" ht="57" hidden="1">
       <c r="A19" s="3" t="s">
         <v>96</v>
       </c>
@@ -2759,7 +2699,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="57">
+    <row r="20" spans="1:17" ht="57" hidden="1">
       <c r="A20" s="3" t="s">
         <v>97</v>
       </c>
@@ -2813,7 +2753,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="71.25">
+    <row r="21" spans="1:17" ht="71.25" hidden="1">
       <c r="A21" s="3" t="s">
         <v>161</v>
       </c>
@@ -2865,7 +2805,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="71.25">
+    <row r="22" spans="1:17" ht="71.25" hidden="1">
       <c r="A22" s="3" t="s">
         <v>162</v>
       </c>
@@ -2917,7 +2857,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="71.25">
+    <row r="23" spans="1:17" ht="71.25" hidden="1">
       <c r="A23" s="3" t="s">
         <v>163</v>
       </c>
@@ -2969,7 +2909,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="71.25">
+    <row r="24" spans="1:17" ht="71.25" hidden="1">
       <c r="A24" s="3" t="s">
         <v>164</v>
       </c>
@@ -3021,7 +2961,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="71.25">
+    <row r="25" spans="1:17" ht="71.25" hidden="1">
       <c r="A25" s="3" t="s">
         <v>165</v>
       </c>
@@ -3073,7 +3013,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="71.25">
+    <row r="26" spans="1:17" ht="71.25" hidden="1">
       <c r="A26" s="3" t="s">
         <v>166</v>
       </c>
@@ -3125,7 +3065,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="71.25">
+    <row r="27" spans="1:17" ht="71.25" hidden="1">
       <c r="A27" s="3" t="s">
         <v>167</v>
       </c>
@@ -3177,7 +3117,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="71.25">
+    <row r="28" spans="1:17" ht="71.25" hidden="1">
       <c r="A28" s="3" t="s">
         <v>168</v>
       </c>
@@ -3229,7 +3169,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="71.25">
+    <row r="29" spans="1:17" ht="71.25" hidden="1">
       <c r="A29" s="3" t="s">
         <v>169</v>
       </c>
@@ -3281,7 +3221,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="71.25">
+    <row r="30" spans="1:17" ht="71.25" hidden="1">
       <c r="A30" s="3" t="s">
         <v>170</v>
       </c>
@@ -3333,7 +3273,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="71.25">
+    <row r="31" spans="1:17" ht="71.25" hidden="1">
       <c r="A31" s="3" t="s">
         <v>171</v>
       </c>
@@ -3385,7 +3325,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="71.25">
+    <row r="32" spans="1:17" ht="71.25" hidden="1">
       <c r="A32" s="3" t="s">
         <v>172</v>
       </c>
@@ -3437,7 +3377,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="71.25">
+    <row r="33" spans="1:17" ht="71.25" hidden="1">
       <c r="A33" s="3" t="s">
         <v>173</v>
       </c>
@@ -3489,7 +3429,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="71.25">
+    <row r="34" spans="1:17" ht="71.25" hidden="1">
       <c r="A34" s="3" t="s">
         <v>174</v>
       </c>
@@ -3541,7 +3481,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="71.25">
+    <row r="35" spans="1:17" ht="71.25" hidden="1">
       <c r="A35" s="3" t="s">
         <v>175</v>
       </c>
@@ -3593,7 +3533,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="85.5">
+    <row r="36" spans="1:17" ht="85.5" hidden="1">
       <c r="A36" s="3" t="s">
         <v>176</v>
       </c>
@@ -3645,7 +3585,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="85.5">
+    <row r="37" spans="1:17" ht="85.5" hidden="1">
       <c r="A37" s="3" t="s">
         <v>177</v>
       </c>
@@ -3698,7 +3638,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="57">
+    <row r="38" spans="1:17" ht="57" hidden="1">
       <c r="A38" s="3" t="s">
         <v>182</v>
       </c>
@@ -3751,7 +3691,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="57">
+    <row r="39" spans="1:17" ht="57" hidden="1">
       <c r="A39" s="3" t="s">
         <v>187</v>
       </c>
@@ -3804,7 +3744,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="57">
+    <row r="40" spans="1:17" ht="57" hidden="1">
       <c r="A40" s="3" t="s">
         <v>188</v>
       </c>
@@ -3857,7 +3797,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="57">
+    <row r="41" spans="1:17" ht="57" hidden="1">
       <c r="A41" s="3" t="s">
         <v>189</v>
       </c>
@@ -3910,7 +3850,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="57">
+    <row r="42" spans="1:17" ht="57" hidden="1">
       <c r="A42" s="3" t="s">
         <v>195</v>
       </c>
@@ -3963,7 +3903,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="85.5">
+    <row r="43" spans="1:17" ht="85.5" hidden="1">
       <c r="A43" s="3" t="s">
         <v>199</v>
       </c>
@@ -4016,7 +3956,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="85.5">
+    <row r="44" spans="1:17" ht="85.5" hidden="1">
       <c r="A44" s="3" t="s">
         <v>204</v>
       </c>
@@ -4069,7 +4009,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="85.5">
+    <row r="45" spans="1:17" ht="85.5" hidden="1">
       <c r="A45" s="3" t="s">
         <v>207</v>
       </c>
@@ -4122,7 +4062,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="85.5">
+    <row r="46" spans="1:17" ht="85.5" hidden="1">
       <c r="A46" s="3" t="s">
         <v>211</v>
       </c>
@@ -4175,345 +4115,343 @@
         <v>213</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="57">
-      <c r="A47" s="5" t="s">
+    <row r="47" spans="1:17" ht="85.5">
+      <c r="A47" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F47" s="3">
         <v>72.5</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="3">
         <v>1750</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I47" s="11" t="s">
+      <c r="I47" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J47" s="11">
+      <c r="J47" s="3">
         <v>5.9</v>
       </c>
-      <c r="K47" s="11" t="s">
+      <c r="K47" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="L47" s="4" t="s">
+      <c r="L47" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="M47" s="4" t="s">
+      <c r="M47" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="N47" s="4" t="s">
+      <c r="N47" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="O47" s="11"/>
-      <c r="P47" s="11"/>
-      <c r="Q47" s="11" t="s">
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="R47" s="12"/>
-    </row>
-    <row r="48" spans="1:18" ht="57">
-      <c r="A48" s="5" t="s">
+    </row>
+    <row r="48" spans="1:17" ht="85.5">
+      <c r="A48" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F48" s="3">
         <v>72.5</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="3">
         <v>1750</v>
       </c>
-      <c r="H48" s="11" t="s">
+      <c r="H48" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J48" s="11">
+      <c r="J48" s="3">
         <v>5.9</v>
       </c>
-      <c r="K48" s="11" t="s">
+      <c r="K48" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="L48" s="4" t="s">
+      <c r="L48" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="M48" s="4" t="s">
+      <c r="M48" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="N48" s="4" t="s">
+      <c r="N48" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="O48" s="11"/>
-      <c r="P48" s="11"/>
-      <c r="Q48" s="11" t="s">
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="R48" s="12"/>
-    </row>
-    <row r="49" spans="1:18" ht="57">
-      <c r="A49" s="5" t="s">
+    </row>
+    <row r="49" spans="1:18" ht="85.5">
+      <c r="A49" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
-      <c r="I49" s="11" t="s">
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J49" s="11">
+      <c r="J49" s="3">
         <v>5.9</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="K49" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="L49" s="4" t="s">
+      <c r="L49" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="M49" s="4" t="s">
+      <c r="M49" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="N49" s="4" t="s">
+      <c r="N49" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="O49" s="11"/>
-      <c r="P49" s="11"/>
-      <c r="Q49" s="11" t="s">
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="R49" s="12"/>
-    </row>
-    <row r="50" spans="1:18" ht="57">
-      <c r="A50" s="5" t="s">
+    </row>
+    <row r="50" spans="1:18" ht="85.5">
+      <c r="A50" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E50" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="11" t="s">
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J50" s="11">
+      <c r="J50" s="3">
         <v>5.9</v>
       </c>
-      <c r="K50" s="11" t="s">
+      <c r="K50" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="L50" s="4" t="s">
+      <c r="L50" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="M50" s="4" t="s">
+      <c r="M50" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="N50" s="4" t="s">
+      <c r="N50" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="O50" s="11"/>
-      <c r="P50" s="11"/>
-      <c r="Q50" s="11" t="s">
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="R50" s="12"/>
-    </row>
-    <row r="51" spans="1:18" ht="71.25">
-      <c r="A51" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B51" s="6" t="s">
+    </row>
+    <row r="51" spans="1:18" ht="85.5">
+      <c r="A51" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E51" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="F51" s="11">
+      <c r="F51" s="3">
         <v>15.64</v>
       </c>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11" t="s">
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J51" s="11">
+      <c r="J51" s="3">
         <v>5.9</v>
       </c>
-      <c r="K51" s="11" t="s">
+      <c r="K51" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="L51" s="4" t="s">
+      <c r="L51" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="M51" s="4" t="s">
+      <c r="M51" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="N51" s="4" t="s">
+      <c r="N51" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="O51" s="11"/>
-      <c r="P51" s="11"/>
-      <c r="Q51" s="11" t="s">
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="R51" s="12"/>
-    </row>
-    <row r="52" spans="1:18" ht="114">
-      <c r="A52" s="7" t="s">
+    </row>
+    <row r="52" spans="1:18" ht="85.5">
+      <c r="A52" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52" s="3">
         <v>97.89</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="3">
         <v>1752</v>
       </c>
-      <c r="H52" s="9" t="s">
+      <c r="H52" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I52" s="9" t="s">
+      <c r="I52" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J52" s="9">
+      <c r="J52" s="3">
         <v>11</v>
       </c>
-      <c r="K52" s="9" t="s">
+      <c r="K52" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="L52" s="10" t="s">
+      <c r="L52" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="M52" s="10" t="s">
+      <c r="M52" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="N52" s="10" t="s">
+      <c r="N52" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="O52" s="13"/>
-      <c r="P52" s="13"/>
-      <c r="Q52" s="9" t="s">
+      <c r="O52" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q52" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="R52" s="14"/>
-    </row>
-    <row r="53" spans="1:18" ht="71.25">
-      <c r="A53" s="7" t="s">
+    </row>
+    <row r="53" spans="1:18" ht="85.5">
+      <c r="A53" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C53" s="16" t="s">
+      <c r="C53" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="E53" s="16" t="s">
+      <c r="E53" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="F53" s="16">
+      <c r="F53" s="3">
         <v>337.3</v>
       </c>
-      <c r="G53" s="16"/>
-      <c r="H53" s="16"/>
-      <c r="I53" s="16" t="s">
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J53" s="16"/>
-      <c r="K53" s="16" t="s">
+      <c r="J53" s="3"/>
+      <c r="K53" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="L53" s="10" t="s">
+      <c r="L53" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="M53" s="10" t="s">
+      <c r="M53" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="N53" s="10" t="s">
+      <c r="N53" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="O53" s="10" t="s">
+      <c r="O53" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="P53" s="10" t="s">
+      <c r="P53" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="Q53" s="16" t="s">
+      <c r="Q53" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="R53" s="17" t="s">
+      <c r="R53" s="2" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="71.25">
-      <c r="A54" s="18" t="s">
+    <row r="54" spans="1:18" ht="85.5">
+      <c r="A54" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C54" s="3" t="s">
@@ -4546,7 +4484,7 @@
       <c r="L54" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M54" s="10" t="s">
+      <c r="M54" s="3" t="s">
         <v>360</v>
       </c>
       <c r="N54" s="3" t="s">
@@ -4555,18 +4493,18 @@
       <c r="O54" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="P54" s="10" t="s">
+      <c r="P54" s="3" t="s">
         <v>359</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="57">
-      <c r="A55" s="18" t="s">
+    <row r="55" spans="1:18" ht="85.5">
+      <c r="A55" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C55" s="3" t="s">
@@ -4599,7 +4537,7 @@
       <c r="L55" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M55" s="10" t="s">
+      <c r="M55" s="3" t="s">
         <v>353</v>
       </c>
       <c r="N55" s="3" t="s">
@@ -4608,18 +4546,18 @@
       <c r="O55" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="P55" s="10" t="s">
+      <c r="P55" s="3" t="s">
         <v>357</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="57">
-      <c r="A56" s="18" t="s">
+    <row r="56" spans="1:18" ht="85.5">
+      <c r="A56" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="B56" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C56" s="3" t="s">
@@ -4659,23 +4597,129 @@
       <c r="O56" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="P56" s="10" t="s">
+      <c r="P56" s="3" t="s">
         <v>369</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>365</v>
       </c>
     </row>
+    <row r="57" spans="1:18" ht="85.5">
+      <c r="A57" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F57" s="3">
+        <v>35.19</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1760</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J57" s="3">
+        <v>11</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="85.5">
+      <c r="A58" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F58" s="3">
+        <v>35.19</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1760</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J58" s="3">
+        <v>11</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B57:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
+  <conditionalFormatting sqref="B59:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R56">
-    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
+  <conditionalFormatting sqref="R2:R58">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -4695,10 +4739,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="15"/>
+      <c r="B1" s="4"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E2D87D-6E52-4F5C-AED3-8CB3D03B8DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E95FB7C-2FEF-423C-87EA-08CECB12C50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="394">
   <si>
     <t>TAG</t>
   </si>
@@ -1189,6 +1189,36 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/OS5934.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5931.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5931.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5929.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5929.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5938.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5938.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5962.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5962.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6030.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6030.pdf</t>
   </si>
 </sst>
 </file>
@@ -1265,7 +1295,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="27">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1406,36 +1436,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4115,7 +4115,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="85.5">
+    <row r="47" spans="1:17" ht="57">
       <c r="A47" s="3" t="s">
         <v>216</v>
       </c>
@@ -4158,13 +4158,17 @@
       <c r="N47" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
+      <c r="O47" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>385</v>
+      </c>
       <c r="Q47" s="3" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="85.5">
+    <row r="48" spans="1:17" ht="57">
       <c r="A48" s="3" t="s">
         <v>221</v>
       </c>
@@ -4207,13 +4211,17 @@
       <c r="N48" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="O48" s="3"/>
-      <c r="P48" s="3"/>
+      <c r="O48" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>387</v>
+      </c>
       <c r="Q48" s="3" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="85.5">
+    <row r="49" spans="1:18" ht="57">
       <c r="A49" s="3" t="s">
         <v>224</v>
       </c>
@@ -4250,13 +4258,17 @@
       <c r="N49" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
+      <c r="O49" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>389</v>
+      </c>
       <c r="Q49" s="3" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="85.5">
+    <row r="50" spans="1:18" ht="57">
       <c r="A50" s="3" t="s">
         <v>228</v>
       </c>
@@ -4293,13 +4305,17 @@
       <c r="N50" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
+      <c r="O50" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>391</v>
+      </c>
       <c r="Q50" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="85.5">
+    <row r="51" spans="1:18" ht="71.25">
       <c r="A51" s="3" t="s">
         <v>370</v>
       </c>
@@ -4338,8 +4354,12 @@
       <c r="N51" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
+      <c r="O51" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>393</v>
+      </c>
       <c r="Q51" s="3" t="s">
         <v>232</v>
       </c>
@@ -4397,7 +4417,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="85.5">
+    <row r="53" spans="1:18" ht="85.5" hidden="1">
       <c r="A53" s="3" t="s">
         <v>333</v>
       </c>
@@ -4447,7 +4467,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="85.5">
+    <row r="54" spans="1:18" ht="85.5" hidden="1">
       <c r="A54" s="3" t="s">
         <v>346</v>
       </c>
@@ -4500,7 +4520,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="85.5">
+    <row r="55" spans="1:18" ht="85.5" hidden="1">
       <c r="A55" s="3" t="s">
         <v>351</v>
       </c>
@@ -4553,7 +4573,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="85.5">
+    <row r="56" spans="1:18" ht="85.5" hidden="1">
       <c r="A56" s="3" t="s">
         <v>361</v>
       </c>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E95FB7C-2FEF-423C-87EA-08CECB12C50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC2CD04-1F48-4FC0-A895-ADE1F9F2BAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC2CD04-1F48-4FC0-A895-ADE1F9F2BAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3050AE-4788-4B0C-A26A-0E760AF3AFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="407">
   <si>
     <t>TAG</t>
   </si>
@@ -1219,6 +1219,45 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/OS6030.pdf</t>
+  </si>
+  <si>
+    <t>RE-631515</t>
+  </si>
+  <si>
+    <t>KH87/T</t>
+  </si>
+  <si>
+    <t>MOTOR 12,5 CV 4 POLOS</t>
+  </si>
+  <si>
+    <t>REDUTOR DA PENEIRA CLAS. DE DISCOS PCDD/32 02</t>
+  </si>
+  <si>
+    <t>OS Nº 5957 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR PENEIRA CLAS. DE DISCOS PCDD/32 01 (ME631514)</t>
+  </si>
+  <si>
+    <t>OS Nº 5960 - GOLD</t>
+  </si>
+  <si>
+    <t>assets/img/REDUTORKH.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/KH87.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5957.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5957.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS5960.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS5960.pdf</t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1334,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="29">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1461,8 +1520,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R58" headerRowDxfId="25" dataDxfId="24" totalsRowDxfId="23">
-  <autoFilter ref="A1:R58" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R60" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
+  <autoFilter ref="A1:R60" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="1">
       <filters>
         <filter val="SEW"/>
@@ -1470,26 +1529,26 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="22"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="24"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="22">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="9"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="8"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1647,7 +1706,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R58"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
@@ -4730,16 +4789,133 @@
         <v>377</v>
       </c>
     </row>
+    <row r="59" spans="1:18" ht="57">
+      <c r="A59" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="F59" s="3">
+        <v>27.88</v>
+      </c>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J59" s="3">
+        <v>11</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="71.25">
+      <c r="A60" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="F60" s="3">
+        <v>27.88</v>
+      </c>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J60" s="3">
+        <v>11</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="85.5">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B59:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
+  <conditionalFormatting sqref="B62:B1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R58">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  <conditionalFormatting sqref="R2:R61">
+    <cfRule type="duplicateValues" dxfId="2" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3050AE-4788-4B0C-A26A-0E760AF3AFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A140DE-E228-4781-B9CC-C3C03A15E673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="423">
   <si>
     <t>TAG</t>
   </si>
@@ -1258,6 +1258,54 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/OS5960.pdf</t>
+  </si>
+  <si>
+    <t>RE -601245</t>
+  </si>
+  <si>
+    <t>PLANETARIO PPK2PH017/T - KAF77</t>
+  </si>
+  <si>
+    <t>MOTOR 6 CV - 04 POLOS SEW</t>
+  </si>
+  <si>
+    <t>REDUTOR PLANETARIO MOTOR TRANSP. CORRENTE RETIRADA CINZAS C601014</t>
+  </si>
+  <si>
+    <t>OS Nº 6013 - GOLD</t>
+  </si>
+  <si>
+    <t>RE-601248</t>
+  </si>
+  <si>
+    <t>KAF77</t>
+  </si>
+  <si>
+    <t>MOTOR 5 CV - 04 POLOS SEW</t>
+  </si>
+  <si>
+    <t>03 / 10</t>
+  </si>
+  <si>
+    <t>REDUTOR PLANETARIO DO MOTOR TRANSPORTADOR DE CINZAS PARA O ELEVADOR C-601015</t>
+  </si>
+  <si>
+    <t>OS Nº 6054 - GOLD</t>
+  </si>
+  <si>
+    <t>ISO VG 220/680</t>
+  </si>
+  <si>
+    <t>assets/img/PLANETARIOPEQ.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LISTAPECASKF77.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6054.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6054.pdf</t>
   </si>
 </sst>
 </file>
@@ -1334,7 +1382,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="28">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1496,16 +1544,6 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1520,8 +1558,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R60" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
-  <autoFilter ref="A1:R60" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R62" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
+  <autoFilter ref="A1:R62" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="1">
       <filters>
         <filter val="SEW"/>
@@ -1706,7 +1744,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
@@ -4869,7 +4907,7 @@
         <v>399</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>402</v>
@@ -4887,35 +4925,110 @@
         <v>400</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="85.5">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
+    <row r="61" spans="1:18" ht="99.75">
+      <c r="A61" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>409</v>
+      </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
-      <c r="O61" s="3"/>
-      <c r="P61" s="3"/>
-      <c r="Q61" s="3"/>
+      <c r="I61" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q61" s="3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="114">
+      <c r="A62" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>417</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B62:B1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
+  <conditionalFormatting sqref="B63:B1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="3" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R61">
-    <cfRule type="duplicateValues" dxfId="2" priority="20"/>
+  <conditionalFormatting sqref="R2:R62">
+    <cfRule type="duplicateValues" dxfId="3" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A140DE-E228-4781-B9CC-C3C03A15E673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD093E6-9D69-47E7-B86A-54396E12BC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4907,7 +4907,7 @@
         <v>399</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>402</v>
@@ -4954,7 +4954,7 @@
         <v>410</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="M61" s="3" t="s">
         <v>420</v>
@@ -5001,7 +5001,7 @@
         <v>416</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>420</v>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD093E6-9D69-47E7-B86A-54396E12BC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E93BC8-F838-4698-9AA9-13FC12305092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="455">
   <si>
     <t>TAG</t>
   </si>
@@ -1306,13 +1306,109 @@
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/OS6054.pdf</t>
+  </si>
+  <si>
+    <t>C06</t>
+  </si>
+  <si>
+    <t>ME-631105</t>
+  </si>
+  <si>
+    <t>MOTOR 2 CV 4 POLOS</t>
+  </si>
+  <si>
+    <t>ISSO 220</t>
+  </si>
+  <si>
+    <t>0,5 L</t>
+  </si>
+  <si>
+    <t>assets/img/CESTARII-C06.jpg</t>
+  </si>
+  <si>
+    <t>OS Nº 6109 - GOLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6109.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6109.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LISTA DE PEÇAS - WCG20 C06.pdf</t>
+  </si>
+  <si>
+    <t>ME-631106</t>
+  </si>
+  <si>
+    <t>ME-631107</t>
+  </si>
+  <si>
+    <t>ME-631110</t>
+  </si>
+  <si>
+    <t>ME-631103</t>
+  </si>
+  <si>
+    <t>C05</t>
+  </si>
+  <si>
+    <t>assets/img/CESTARII-C05.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LISTA DE PEÇAS - WCG20 C05.pdf</t>
+  </si>
+  <si>
+    <t>OS Nº 6110 - GOLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6110.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6110.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6116.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6116.pdf</t>
+  </si>
+  <si>
+    <t>OS Nº 6116 - GOLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6107.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6107.pdf</t>
+  </si>
+  <si>
+    <t>OS Nº 6107 - GOLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6105.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6105.pdf</t>
+  </si>
+  <si>
+    <t>OS Nº 6105 - GOLD</t>
+  </si>
+  <si>
+    <t>REDUTOR VÁLVULA ROTATIVA 02 (VR-02)</t>
+  </si>
+  <si>
+    <t>REDUTOR VÁLVULA ROTATIVA (VR-01)</t>
+  </si>
+  <si>
+    <t>REDUTOR ROSCA DE EXTRAÇÃO DO FILTRO (RT-03)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1333,8 +1429,12 @@
       <sz val="8"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1351,6 +1451,12 @@
         <fgColor rgb="FFD4AF37"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1364,7 +1470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1378,41 +1484,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1558,35 +1643,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R62" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
-  <autoFilter ref="A1:R62" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="SEW"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R67" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+  <autoFilter ref="A1:R67" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="22">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="21"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="19">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="10"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="9"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="8"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1744,7 +1823,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R62"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
@@ -1824,7 +1903,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="57" hidden="1">
+    <row r="2" spans="1:18" ht="57">
       <c r="A2" s="3" t="s">
         <v>38</v>
       </c>
@@ -1878,7 +1957,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="57" hidden="1">
+    <row r="3" spans="1:18" ht="57">
       <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
@@ -1932,7 +2011,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="57" hidden="1">
+    <row r="4" spans="1:18" ht="57">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
@@ -1986,7 +2065,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="57" hidden="1">
+    <row r="5" spans="1:18" ht="57">
       <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
@@ -2040,7 +2119,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="57" hidden="1">
+    <row r="6" spans="1:18" ht="57">
       <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
@@ -2094,7 +2173,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="57" hidden="1">
+    <row r="7" spans="1:18" ht="57">
       <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
@@ -2148,7 +2227,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="57" hidden="1">
+    <row r="8" spans="1:18" ht="57">
       <c r="A8" s="3" t="s">
         <v>44</v>
       </c>
@@ -2202,7 +2281,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="57" hidden="1">
+    <row r="9" spans="1:18" ht="57">
       <c r="A9" s="3" t="s">
         <v>45</v>
       </c>
@@ -2256,7 +2335,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="57" hidden="1">
+    <row r="10" spans="1:18" ht="57">
       <c r="A10" s="3" t="s">
         <v>73</v>
       </c>
@@ -2310,7 +2389,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="57" hidden="1">
+    <row r="11" spans="1:18" ht="57">
       <c r="A11" s="3" t="s">
         <v>77</v>
       </c>
@@ -2364,7 +2443,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="57" hidden="1">
+    <row r="12" spans="1:18" ht="57">
       <c r="A12" s="3" t="s">
         <v>89</v>
       </c>
@@ -2418,7 +2497,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="57" hidden="1">
+    <row r="13" spans="1:18" ht="57">
       <c r="A13" s="3" t="s">
         <v>90</v>
       </c>
@@ -2472,7 +2551,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="57" hidden="1">
+    <row r="14" spans="1:18" ht="57">
       <c r="A14" s="3" t="s">
         <v>91</v>
       </c>
@@ -2526,7 +2605,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="57" hidden="1">
+    <row r="15" spans="1:18" ht="57">
       <c r="A15" s="3" t="s">
         <v>92</v>
       </c>
@@ -2580,7 +2659,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="57" hidden="1">
+    <row r="16" spans="1:18" ht="57">
       <c r="A16" s="3" t="s">
         <v>93</v>
       </c>
@@ -2634,7 +2713,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="57" hidden="1">
+    <row r="17" spans="1:17" ht="57">
       <c r="A17" s="3" t="s">
         <v>94</v>
       </c>
@@ -2688,7 +2767,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="57" hidden="1">
+    <row r="18" spans="1:17" ht="57">
       <c r="A18" s="3" t="s">
         <v>95</v>
       </c>
@@ -2742,7 +2821,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="57" hidden="1">
+    <row r="19" spans="1:17" ht="57">
       <c r="A19" s="3" t="s">
         <v>96</v>
       </c>
@@ -2796,7 +2875,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="57" hidden="1">
+    <row r="20" spans="1:17" ht="57">
       <c r="A20" s="3" t="s">
         <v>97</v>
       </c>
@@ -2850,7 +2929,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="71.25" hidden="1">
+    <row r="21" spans="1:17" ht="71.25">
       <c r="A21" s="3" t="s">
         <v>161</v>
       </c>
@@ -2902,7 +2981,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="71.25" hidden="1">
+    <row r="22" spans="1:17" ht="71.25">
       <c r="A22" s="3" t="s">
         <v>162</v>
       </c>
@@ -2954,7 +3033,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="71.25" hidden="1">
+    <row r="23" spans="1:17" ht="71.25">
       <c r="A23" s="3" t="s">
         <v>163</v>
       </c>
@@ -3006,7 +3085,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="71.25" hidden="1">
+    <row r="24" spans="1:17" ht="71.25">
       <c r="A24" s="3" t="s">
         <v>164</v>
       </c>
@@ -3058,7 +3137,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="71.25" hidden="1">
+    <row r="25" spans="1:17" ht="71.25">
       <c r="A25" s="3" t="s">
         <v>165</v>
       </c>
@@ -3110,7 +3189,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="71.25" hidden="1">
+    <row r="26" spans="1:17" ht="71.25">
       <c r="A26" s="3" t="s">
         <v>166</v>
       </c>
@@ -3162,7 +3241,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="71.25" hidden="1">
+    <row r="27" spans="1:17" ht="71.25">
       <c r="A27" s="3" t="s">
         <v>167</v>
       </c>
@@ -3214,7 +3293,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="71.25" hidden="1">
+    <row r="28" spans="1:17" ht="71.25">
       <c r="A28" s="3" t="s">
         <v>168</v>
       </c>
@@ -3266,7 +3345,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="71.25" hidden="1">
+    <row r="29" spans="1:17" ht="71.25">
       <c r="A29" s="3" t="s">
         <v>169</v>
       </c>
@@ -3318,7 +3397,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="71.25" hidden="1">
+    <row r="30" spans="1:17" ht="71.25">
       <c r="A30" s="3" t="s">
         <v>170</v>
       </c>
@@ -3370,7 +3449,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="71.25" hidden="1">
+    <row r="31" spans="1:17" ht="71.25">
       <c r="A31" s="3" t="s">
         <v>171</v>
       </c>
@@ -3422,7 +3501,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="71.25" hidden="1">
+    <row r="32" spans="1:17" ht="71.25">
       <c r="A32" s="3" t="s">
         <v>172</v>
       </c>
@@ -3474,7 +3553,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="71.25" hidden="1">
+    <row r="33" spans="1:17" ht="71.25">
       <c r="A33" s="3" t="s">
         <v>173</v>
       </c>
@@ -3526,7 +3605,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="71.25" hidden="1">
+    <row r="34" spans="1:17" ht="71.25">
       <c r="A34" s="3" t="s">
         <v>174</v>
       </c>
@@ -3578,7 +3657,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="71.25" hidden="1">
+    <row r="35" spans="1:17" ht="71.25">
       <c r="A35" s="3" t="s">
         <v>175</v>
       </c>
@@ -3630,7 +3709,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="85.5" hidden="1">
+    <row r="36" spans="1:17" ht="85.5">
       <c r="A36" s="3" t="s">
         <v>176</v>
       </c>
@@ -3682,7 +3761,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="85.5" hidden="1">
+    <row r="37" spans="1:17" ht="85.5">
       <c r="A37" s="3" t="s">
         <v>177</v>
       </c>
@@ -3735,7 +3814,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="57" hidden="1">
+    <row r="38" spans="1:17" ht="57">
       <c r="A38" s="3" t="s">
         <v>182</v>
       </c>
@@ -3788,7 +3867,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="57" hidden="1">
+    <row r="39" spans="1:17" ht="57">
       <c r="A39" s="3" t="s">
         <v>187</v>
       </c>
@@ -3841,7 +3920,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="57" hidden="1">
+    <row r="40" spans="1:17" ht="57">
       <c r="A40" s="3" t="s">
         <v>188</v>
       </c>
@@ -3894,7 +3973,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="57" hidden="1">
+    <row r="41" spans="1:17" ht="57">
       <c r="A41" s="3" t="s">
         <v>189</v>
       </c>
@@ -3947,7 +4026,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="57" hidden="1">
+    <row r="42" spans="1:17" ht="57">
       <c r="A42" s="3" t="s">
         <v>195</v>
       </c>
@@ -4000,7 +4079,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="85.5" hidden="1">
+    <row r="43" spans="1:17" ht="85.5">
       <c r="A43" s="3" t="s">
         <v>199</v>
       </c>
@@ -4053,7 +4132,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="85.5" hidden="1">
+    <row r="44" spans="1:17" ht="85.5">
       <c r="A44" s="3" t="s">
         <v>204</v>
       </c>
@@ -4106,7 +4185,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="85.5" hidden="1">
+    <row r="45" spans="1:17" ht="85.5">
       <c r="A45" s="3" t="s">
         <v>207</v>
       </c>
@@ -4159,7 +4238,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="85.5" hidden="1">
+    <row r="46" spans="1:17" ht="85.5">
       <c r="A46" s="3" t="s">
         <v>211</v>
       </c>
@@ -4461,7 +4540,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="85.5">
+    <row r="52" spans="1:18" ht="114">
       <c r="A52" s="3" t="s">
         <v>236</v>
       </c>
@@ -4514,7 +4593,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="85.5" hidden="1">
+    <row r="53" spans="1:18" ht="71.25">
       <c r="A53" s="3" t="s">
         <v>333</v>
       </c>
@@ -4564,7 +4643,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="85.5" hidden="1">
+    <row r="54" spans="1:18" ht="71.25">
       <c r="A54" s="3" t="s">
         <v>346</v>
       </c>
@@ -4617,7 +4696,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="85.5" hidden="1">
+    <row r="55" spans="1:18" ht="57">
       <c r="A55" s="3" t="s">
         <v>351</v>
       </c>
@@ -4670,7 +4749,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="85.5" hidden="1">
+    <row r="56" spans="1:18" ht="57">
       <c r="A56" s="3" t="s">
         <v>361</v>
       </c>
@@ -4721,7 +4800,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="85.5">
+    <row r="57" spans="1:18" ht="57">
       <c r="A57" s="3" t="s">
         <v>371</v>
       </c>
@@ -4774,7 +4853,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="85.5">
+    <row r="58" spans="1:18" ht="57">
       <c r="A58" s="3" t="s">
         <v>375</v>
       </c>
@@ -5019,16 +5098,286 @@
         <v>417</v>
       </c>
     </row>
+    <row r="63" spans="1:18" ht="57">
+      <c r="A63" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C63" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F63" s="3">
+        <v>30.3</v>
+      </c>
+      <c r="G63" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q63" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="57">
+      <c r="A64" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C64" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F64" s="3">
+        <v>56.2</v>
+      </c>
+      <c r="G64" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q64" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" ht="57">
+      <c r="A65" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C65" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F65" s="3">
+        <v>30.3</v>
+      </c>
+      <c r="G65" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="Q65" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" ht="57">
+      <c r="A66" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C66" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F66" s="3">
+        <v>56.2</v>
+      </c>
+      <c r="G66" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" ht="57">
+      <c r="A67" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C67" s="3" t="str">
+        <f>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</f>
+        <v>MOTOREDUTOR WEG CESTARI</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F67" s="3">
+        <v>30.3</v>
+      </c>
+      <c r="G67" s="3">
+        <v>1750</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="P67" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="Q67" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B63:B1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R62">
-    <cfRule type="duplicateValues" dxfId="3" priority="20"/>
+  <conditionalFormatting sqref="R2:R67">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E93BC8-F838-4698-9AA9-13FC12305092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C93CA5-CF52-4DD7-A5AC-80248C4F63F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="454">
   <si>
     <t>TAG</t>
   </si>
@@ -1351,9 +1351,6 @@
   </si>
   <si>
     <t>C05</t>
-  </si>
-  <si>
-    <t>assets/img/CESTARII-C05.jpg</t>
   </si>
   <si>
     <t xml:space="preserve"> assets/pdf/LISTA DE PEÇAS - WCG20 C05.pdf</t>
@@ -1497,17 +1494,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1643,29 +1630,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R67" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R67" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
   <autoFilter ref="A1:R67" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="21"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="18">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5185,25 +5172,25 @@
         <v>427</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L64" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="M64" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>439</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>105</v>
       </c>
       <c r="O64" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="P64" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="P64" s="3" t="s">
-        <v>442</v>
-      </c>
       <c r="Q64" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="57">
@@ -5251,13 +5238,13 @@
         <v>105</v>
       </c>
       <c r="O65" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="P65" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="P65" s="3" t="s">
+      <c r="Q65" s="3" t="s">
         <v>444</v>
-      </c>
-      <c r="Q65" s="3" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="57">
@@ -5293,25 +5280,25 @@
         <v>427</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L66" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="M66" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>439</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>105</v>
       </c>
       <c r="O66" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="P66" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="P66" s="3" t="s">
+      <c r="Q66" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="57">
@@ -5347,7 +5334,7 @@
         <v>427</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>428</v>
@@ -5359,13 +5346,13 @@
         <v>105</v>
       </c>
       <c r="O67" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="P67" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="P67" s="3" t="s">
+      <c r="Q67" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="Q67" s="3" t="s">
-        <v>451</v>
       </c>
     </row>
   </sheetData>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C93CA5-CF52-4DD7-A5AC-80248C4F63F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4038E401-382E-4C03-9F72-D8DBDD174158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1323,9 +1323,6 @@
     <t>0,5 L</t>
   </si>
   <si>
-    <t>assets/img/CESTARII-C06.jpg</t>
-  </si>
-  <si>
     <t>OS Nº 6109 - GOLD</t>
   </si>
   <si>
@@ -1399,6 +1396,9 @@
   </si>
   <si>
     <t>REDUTOR ROSCA DE EXTRAÇÃO DO FILTRO (RT-03)</t>
+  </si>
+  <si>
+    <t>assets/img/C06.jpg</t>
   </si>
 </sst>
 </file>
@@ -5121,27 +5121,27 @@
         <v>373</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N63" s="3" t="s">
         <v>105</v>
       </c>
       <c r="O63" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="P63" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="P63" s="3" t="s">
-        <v>431</v>
-      </c>
       <c r="Q63" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="64" spans="1:18" ht="57">
       <c r="A64" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>35</v>
@@ -5151,7 +5151,7 @@
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>126</v>
@@ -5172,30 +5172,30 @@
         <v>427</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>105</v>
       </c>
       <c r="O64" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="P64" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="P64" s="3" t="s">
-        <v>441</v>
-      </c>
       <c r="Q64" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="57">
       <c r="A65" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>35</v>
@@ -5229,27 +5229,27 @@
         <v>376</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N65" s="3" t="s">
         <v>105</v>
       </c>
       <c r="O65" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="P65" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="P65" s="3" t="s">
+      <c r="Q65" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="Q65" s="3" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="57">
       <c r="A66" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>35</v>
@@ -5259,7 +5259,7 @@
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>126</v>
@@ -5280,30 +5280,30 @@
         <v>427</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>105</v>
       </c>
       <c r="O66" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="P66" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="P66" s="3" t="s">
+      <c r="Q66" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="57">
       <c r="A67" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>35</v>
@@ -5334,25 +5334,25 @@
         <v>427</v>
       </c>
       <c r="K67" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="L67" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="L67" s="3" t="s">
-        <v>428</v>
-      </c>
       <c r="M67" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N67" s="3" t="s">
         <v>105</v>
       </c>
       <c r="O67" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="P67" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="P67" s="3" t="s">
+      <c r="Q67" s="3" t="s">
         <v>449</v>
-      </c>
-      <c r="Q67" s="3" t="s">
-        <v>450</v>
       </c>
     </row>
   </sheetData>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4038E401-382E-4C03-9F72-D8DBDD174158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B046A4E-C9E3-4666-894F-D417987DCAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="474">
   <si>
     <t>TAG</t>
   </si>
@@ -1278,9 +1278,6 @@
     <t>RE-601248</t>
   </si>
   <si>
-    <t>KAF77</t>
-  </si>
-  <si>
     <t>MOTOR 5 CV - 04 POLOS SEW</t>
   </si>
   <si>
@@ -1399,13 +1396,76 @@
   </si>
   <si>
     <t>assets/img/C06.jpg</t>
+  </si>
+  <si>
+    <t>ME- 601078</t>
+  </si>
+  <si>
+    <t>PLANETARIO PHF022T / KF87</t>
+  </si>
+  <si>
+    <t>MOTOR 25 CV -  4 POLOS</t>
+  </si>
+  <si>
+    <t>REDUTOR PLANETARIO ESTEIRA TRANSPORTADORA DE CINZAS 03</t>
+  </si>
+  <si>
+    <t>assets/img/SEWPHF022T.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/PLANETARIO PHF022_KF87.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/PHF022T_PT.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6011.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6011.pdf</t>
+  </si>
+  <si>
+    <t>OS Nº 6011 - GOLD</t>
+  </si>
+  <si>
+    <t>ME- 601079</t>
+  </si>
+  <si>
+    <t>REDUTOR PLANETARIO ESTEIRA TRANSPORTADORA DE CINZAS 04</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6016.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6016.pdf</t>
+  </si>
+  <si>
+    <t>OS Nº 6016 - GOLD</t>
+  </si>
+  <si>
+    <t>ME- 601080</t>
+  </si>
+  <si>
+    <t>REDUTOR PLANETARIO ESTEIRA TRANSPORTADORA DE CINZAS 05</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6021.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6021.pdf</t>
+  </si>
+  <si>
+    <t>OS Nº 6021 - GOLD</t>
+  </si>
+  <si>
+    <t>ISO VG 220 / ISSO 680</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1426,12 +1486,8 @@
       <sz val="8"/>
       <name val="Carlito"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Carlito"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1454,6 +1510,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1467,7 +1529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1487,14 +1549,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1630,29 +1705,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R67" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
-  <autoFilter ref="A1:R67" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R70" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+  <autoFilter ref="A1:R70" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="18">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="21"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="19">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1810,7 +1885,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
@@ -5011,19 +5086,19 @@
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="K61" s="3" t="s">
         <v>410</v>
       </c>
       <c r="L61" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="M61" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="M61" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="N61" s="3" t="s">
         <v>235</v>
@@ -5049,47 +5124,47 @@
         <v>335</v>
       </c>
       <c r="D62" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>413</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>414</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="L62" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="L62" s="3" t="s">
+      <c r="M62" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>235</v>
       </c>
       <c r="O62" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="P62" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>422</v>
-      </c>
       <c r="Q62" s="3" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" ht="57">
-      <c r="A63" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="B63" s="6" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="99.75">
+      <c r="A63" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C63" s="3" t="str">
@@ -5097,10 +5172,10 @@
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F63" s="3">
         <v>30.3</v>
@@ -5112,38 +5187,38 @@
         <v>100</v>
       </c>
       <c r="I63" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="J63" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="J63" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="K63" s="7" t="s">
+      <c r="K63" s="3" t="s">
         <v>373</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N63" s="3" t="s">
         <v>105</v>
       </c>
       <c r="O63" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="P63" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="P63" s="3" t="s">
-        <v>430</v>
-      </c>
       <c r="Q63" s="3" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" ht="57">
-      <c r="A64" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="B64" s="6" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="114">
+      <c r="A64" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C64" s="3" t="str">
@@ -5151,7 +5226,7 @@
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>126</v>
@@ -5166,38 +5241,38 @@
         <v>100</v>
       </c>
       <c r="I64" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="J64" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="J64" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="K64" s="7" t="s">
-        <v>450</v>
+      <c r="K64" s="3" t="s">
+        <v>449</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>105</v>
       </c>
       <c r="O64" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="P64" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="P64" s="3" t="s">
-        <v>440</v>
-      </c>
       <c r="Q64" s="3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" ht="57">
-      <c r="A65" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="B65" s="6" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="99.75">
+      <c r="A65" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C65" s="3" t="str">
@@ -5205,10 +5280,10 @@
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F65" s="3">
         <v>30.3</v>
@@ -5220,38 +5295,38 @@
         <v>100</v>
       </c>
       <c r="I65" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="J65" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="J65" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="K65" s="7" t="s">
+      <c r="K65" s="3" t="s">
         <v>376</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N65" s="3" t="s">
         <v>105</v>
       </c>
       <c r="O65" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="P65" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="P65" s="3" t="s">
+      <c r="Q65" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="Q65" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" ht="57">
-      <c r="A66" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="B66" s="6" t="s">
+    </row>
+    <row r="66" spans="1:18" ht="114">
+      <c r="A66" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C66" s="3" t="str">
@@ -5259,7 +5334,7 @@
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>126</v>
@@ -5274,38 +5349,38 @@
         <v>100</v>
       </c>
       <c r="I66" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="J66" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="K66" s="7" t="s">
-        <v>451</v>
+      <c r="K66" s="3" t="s">
+        <v>450</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>105</v>
       </c>
       <c r="O66" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="P66" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="P66" s="3" t="s">
+      <c r="Q66" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" ht="57">
-      <c r="A67" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="B67" s="6" t="s">
+    </row>
+    <row r="67" spans="1:18" ht="99.75">
+      <c r="A67" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C67" s="3" t="str">
@@ -5313,10 +5388,10 @@
         <v>MOTOREDUTOR WEG CESTARI</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F67" s="3">
         <v>30.3</v>
@@ -5328,43 +5403,187 @@
         <v>100</v>
       </c>
       <c r="I67" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="J67" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="J67" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="K67" s="7" t="s">
+      <c r="K67" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="L67" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="L67" s="3" t="s">
-        <v>453</v>
-      </c>
       <c r="M67" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N67" s="3" t="s">
         <v>105</v>
       </c>
       <c r="O67" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="P67" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="P67" s="3" t="s">
+      <c r="Q67" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="Q67" s="3" t="s">
-        <v>449</v>
-      </c>
+    </row>
+    <row r="68" spans="1:18" ht="85.5">
+      <c r="A68" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="J68" s="7">
+        <v>12</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="M68" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="N68" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="O68" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="P68" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q68" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="R68" s="8"/>
+    </row>
+    <row r="69" spans="1:18" ht="85.5">
+      <c r="A69" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="J69" s="7">
+        <v>12</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="M69" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="N69" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="O69" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="P69" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q69" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="R69" s="8"/>
+    </row>
+    <row r="70" spans="1:18" ht="85.5">
+      <c r="A70" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="J70" s="7">
+        <v>12</v>
+      </c>
+      <c r="K70" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="L70" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="M70" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="N70" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="O70" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="P70" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q70" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="R70" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B63:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
+  <conditionalFormatting sqref="B71:B1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R67">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  <conditionalFormatting sqref="R2:R70">
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/dados_equipamentos.xlsx
+++ b/dados_equipamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre.santiago\Documents\MANUT REDUT INPASA 2026\teste python\DATABOOK_INPASA_EXCEL_GITHUB_COMPLETO\DATABOOK_INPASA_EXCEL_GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B046A4E-C9E3-4666-894F-D417987DCAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02A79C7-23D4-49E8-AF5C-EA118D7094D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="488">
   <si>
     <t>TAG</t>
   </si>
@@ -1459,6 +1459,48 @@
   </si>
   <si>
     <t>ISO VG 220 / ISSO 680</t>
+  </si>
+  <si>
+    <t>ME- 601241</t>
+  </si>
+  <si>
+    <t>MOTOR 15 CV -  4 POLOS</t>
+  </si>
+  <si>
+    <t>REDUTOR PLANETARIO MOTOR TRANSPORTADOR CORRENTE ALIMENTAÇÃO C601013</t>
+  </si>
+  <si>
+    <t>REDUTOR PLANETARIO DO MOTROR TRANSPORTADOR DE CORRENTE ALIMENTAÇÃO - C-601012</t>
+  </si>
+  <si>
+    <t>PLANETARIO PHF012T / KF87</t>
+  </si>
+  <si>
+    <t>ME - 601240</t>
+  </si>
+  <si>
+    <t>OS Nº 6020 - GOLD</t>
+  </si>
+  <si>
+    <t>OS Nº 6023 - GOLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/LP PFH012 SEW.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/MANUALPHF012_T.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6020.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6020.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/RELATFINALOS6023.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> assets/pdf/OS6023.pdf</t>
   </si>
 </sst>
 </file>
@@ -1487,7 +1529,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1513,6 +1555,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1552,14 +1600,44 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1705,29 +1783,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R70" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
-  <autoFilter ref="A1:R70" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaEquipamentos" displayName="TabelaEquipamentos" ref="A1:R72" headerRowDxfId="27" dataDxfId="26" totalsRowDxfId="25">
+  <autoFilter ref="A1:R72" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="21"/>
-    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TAG" dataDxfId="24"/>
+    <tableColumn id="19" xr3:uid="{726DCCAF-1417-462D-BD10-A9FED761ADBD}" name="Fabricante" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="22">
       <calculatedColumnFormula>CONCATENATE("MOTOREDUTOR"," ",TabelaEquipamentos[[#This Row],[Fabricante]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Modelo" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Potencia" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Relacao" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="RPM" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Montagem" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Lubrificante" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quantidade_Oleo" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Local" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Foto" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lista_Pecas" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Manual" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="RELATORIO FINAL" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Fotos_Adicionais" dataDxfId="9"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Observacoes" dataDxfId="8"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="TAG Nº" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1885,7 +1963,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R72"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.875" style="2" customWidth="1"/>
@@ -5268,7 +5346,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="99.75">
+    <row r="65" spans="1:17" ht="99.75">
       <c r="A65" s="3" t="s">
         <v>432</v>
       </c>
@@ -5322,7 +5400,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="114">
+    <row r="66" spans="1:17" ht="114">
       <c r="A66" s="3" t="s">
         <v>433</v>
       </c>
@@ -5376,7 +5454,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="99.75">
+    <row r="67" spans="1:17" ht="99.75">
       <c r="A67" s="3" t="s">
         <v>434</v>
       </c>
@@ -5430,160 +5508,255 @@
         <v>448</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="85.5">
-      <c r="A68" s="5" t="s">
+    <row r="68" spans="1:17" ht="114">
+      <c r="A68" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D68" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="E68" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7" t="s">
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="J68" s="7">
+      <c r="J68" s="3">
         <v>12</v>
       </c>
-      <c r="K68" s="7" t="s">
+      <c r="K68" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="L68" s="7" t="s">
+      <c r="L68" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="M68" s="7" t="s">
+      <c r="M68" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="N68" s="7" t="s">
+      <c r="N68" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="O68" s="7" t="s">
+      <c r="O68" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="P68" s="7" t="s">
+      <c r="P68" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="Q68" s="7" t="s">
+      <c r="Q68" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="R68" s="8"/>
-    </row>
-    <row r="69" spans="1:18" ht="85.5">
-      <c r="A69" s="5" t="s">
+    </row>
+    <row r="69" spans="1:17" ht="99.75">
+      <c r="A69" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="E69" s="7" t="s">
+      <c r="E69" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7" t="s">
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="J69" s="7">
+      <c r="J69" s="3">
         <v>12</v>
       </c>
-      <c r="K69" s="7" t="s">
+      <c r="K69" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="L69" s="7" t="s">
+      <c r="L69" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="M69" s="7" t="s">
+      <c r="M69" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="N69" s="7" t="s">
+      <c r="N69" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="O69" s="7" t="s">
+      <c r="O69" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="P69" s="7" t="s">
+      <c r="P69" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="Q69" s="7" t="s">
+      <c r="Q69" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="R69" s="8"/>
-    </row>
-    <row r="70" spans="1:18" ht="85.5">
-      <c r="A70" s="5" t="s">
+    </row>
+    <row r="70" spans="1:17" ht="114">
+      <c r="A70" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="E70" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7" t="s">
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="J70" s="7">
+      <c r="J70" s="3">
         <v>12</v>
       </c>
-      <c r="K70" s="7" t="s">
+      <c r="K70" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="L70" s="7" t="s">
+      <c r="L70" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="M70" s="7" t="s">
+      <c r="M70" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="N70" s="7" t="s">
+      <c r="N70" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="O70" s="7" t="s">
+      <c r="O70" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="P70" s="7" t="s">
+      <c r="P70" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="Q70" s="7" t="s">
+      <c r="Q70" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="R70" s="8"/>
+    </row>
+    <row r="71" spans="1:17" ht="99.75">
+      <c r="A71" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="F71" s="7">
+        <v>39.630000000000003</v>
+      </c>
+      <c r="G71" s="7"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="N71" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="P71" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q71" s="7" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" ht="114">
+      <c r="A72" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="F72" s="7">
+        <v>39.630000000000003</v>
+      </c>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="K72" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q72" s="7" t="s">
+        <v>481</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="B71:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
+  <conditionalFormatting sqref="B73:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R70">
-    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+  <conditionalFormatting sqref="R2:R72">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="47" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
